--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E8E4CE-A601-4F87-9EED-899F150A0FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32596631-58E5-45E9-98E1-0AB648C6DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="267">
   <si>
     <t>authors</t>
   </si>
@@ -411,21 +411,9 @@
     <t>in-review</t>
   </si>
   <si>
-    <t>Advancing new methods for understanding public sentiment  about educational reforms: The case of Twitter and the Next  Generation Science Standards </t>
-  </si>
-  <si>
     <t>under review</t>
   </si>
   <si>
-    <t>Rosenberg, J. M., Borchers, C., Dyer, E. B., Anderson, D., and Fischer, C.</t>
-  </si>
-  <si>
-    <t>Anderson, D., Gau, J. M., Beck, L., Unruh, D., Gioia, G., McCart, M., Davies, S. C., Slocumb, J., Gomez, D., and Glang, A. E.</t>
-  </si>
-  <si>
-    <t>Management of return to school following brain injury: An evaluation model</t>
-  </si>
-  <si>
     <t>10.4324/9780429260919</t>
   </si>
   <si>
@@ -802,6 +790,51 @@
   </si>
   <si>
     <t>November, 2016</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>QGIS Interface for SWAT-MODFLOW (QSWATMOD)</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW Tutorial Version 3 — Documentation for Preparing Model Simulations</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW Tutorial—Documentation for Preparing Model Simulations</t>
+  </si>
+  <si>
+    <t>Park, S. and Bailey, R.T.</t>
+  </si>
+  <si>
+    <t>Bailey, R.T. and Park, S.</t>
+  </si>
+  <si>
+    <t>Park, S., Bailey, R.T. and Bieger, K.</t>
+  </si>
+  <si>
+    <t>Blackland Research and Extension Center, Texas A&amp;M AgriLife Research, Temple, TX.</t>
+  </si>
+  <si>
+    <t>Department of Civil and Environmental Engineering, Colorado State University: Fort Collins, CO, United States.</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/qswatmod/raw/master/QSWATMOD%20Tutorial.pdf</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/qswatmod/blob/master/QSWATMOD%20Tutorial.pdf</t>
+  </si>
+  <si>
+    <t>https://swat.tamu.edu/software/swat-modflow/</t>
+  </si>
+  <si>
+    <t>https://swat.tamu.edu/media/115048/swat-modflow-tutorial.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assessment of snowmelt and groundwater-surface water dynamics in mountainous, foothill and plains regions in northern latitudes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zaremehrjardy, M., Victor, J., Park, S., Smerdon, B., Daniel, S. </t>
   </si>
 </sst>
 </file>
@@ -897,7 +930,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -951,6 +984,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1268,17 +1307,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="2" width="11" style="2"/>
     <col min="3" max="3" width="44.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="11" style="2"/>
     <col min="5" max="5" width="55.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17" style="2" customWidth="1"/>
-    <col min="7" max="10" width="11" style="2"/>
+    <col min="6" max="6" width="14.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.625" style="2" customWidth="1"/>
+    <col min="9" max="10" width="11" style="2"/>
     <col min="11" max="11" width="35.125" style="2" customWidth="1"/>
-    <col min="12" max="17" width="11" style="2"/>
+    <col min="12" max="12" width="11" style="2"/>
+    <col min="13" max="13" width="26" style="2" customWidth="1"/>
+    <col min="14" max="17" width="11" style="2"/>
     <col min="18" max="18" width="74" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="11" style="2"/>
   </cols>
@@ -1359,16 +1402,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D2" s="1">
         <v>2021</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G2" s="1">
         <v>134</v>
@@ -1377,10 +1420,10 @@
         <v>105093</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1399,29 +1442,29 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D3" s="1">
         <v>2020</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G3" s="1">
         <v>32</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1432,7 +1475,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="47.25">
+    <row r="4" spans="1:22" ht="63">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1440,16 +1483,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D4" s="1">
         <v>2020</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G4" s="1">
         <v>745</v>
@@ -1459,10 +1502,10 @@
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1481,16 +1524,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D5" s="6">
         <v>2020</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G5" s="6">
         <v>10</v>
@@ -1500,10 +1543,10 @@
         <v>503</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -1522,16 +1565,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D6" s="6">
         <v>2020</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G6" s="6">
         <v>126</v>
@@ -1541,10 +1584,10 @@
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -1563,16 +1606,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D7" s="6">
         <v>2020</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G7" s="6">
         <v>706</v>
@@ -1582,10 +1625,10 @@
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -1604,16 +1647,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D8" s="6">
         <v>2019</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G8" s="6">
         <v>9</v>
@@ -1623,10 +1666,10 @@
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -1645,16 +1688,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D9" s="6">
         <v>2019</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G9" s="6">
         <v>11</v>
@@ -1664,10 +1707,10 @@
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -1686,29 +1729,29 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D10" s="6">
         <v>2019</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -1727,29 +1770,29 @@
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D11" s="6">
         <v>2019</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G11" s="6">
         <v>111</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="15" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -1768,29 +1811,29 @@
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D12" s="6">
         <v>2019</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G12" s="6">
         <v>64</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -1864,7 +1907,7 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:22" ht="47.25">
+    <row r="16" spans="1:22" ht="31.5">
       <c r="A16" s="1" t="s">
         <v>124</v>
       </c>
@@ -1872,13 +1915,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>128</v>
+        <v>266</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>129</v>
+        <v>265</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1895,203 +1938,221 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:20" ht="31.5">
-      <c r="A17" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="17" spans="1:20" s="18" customFormat="1" ht="126">
+      <c r="A17" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17" s="17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="17">
+        <v>2019</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="S17" s="20" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="63">
+      <c r="A18" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B18" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-    </row>
-    <row r="18" spans="1:20" ht="78.75">
-      <c r="A18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="D18" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>2019</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>254</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>17</v>
+        <v>260</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
-      <c r="R18" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:20" ht="126">
+    <row r="19" spans="1:20" ht="63">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="B19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>256</v>
       </c>
       <c r="D19" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>2017</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>255</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
+      <c r="R19" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:20" s="18" customFormat="1" ht="78.75">
-      <c r="A20" s="17" t="s">
+    <row r="20" spans="1:20" ht="78.75">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S20" s="1"/>
+    </row>
+    <row r="21" spans="1:20" ht="126">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+    </row>
+    <row r="22" spans="1:20" s="18" customFormat="1" ht="78.75">
+      <c r="A22" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B22" s="17">
         <v>1</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="C22" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="N22" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="O22" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="N20" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="O20" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q20" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="T20" s="18" t="s">
+      <c r="Q22" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" s="18" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" s="8" customFormat="1" ht="63">
-      <c r="A21" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="6">
-        <v>2</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="O21" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q21" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" s="8" customFormat="1" ht="63">
-      <c r="A22" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="6">
-        <v>3</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="O22" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q22" s="8" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:20" s="8" customFormat="1" ht="63">
@@ -2099,25 +2160,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="O23" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="Q23" s="8" t="b">
         <v>0</v>
@@ -2128,25 +2189,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="O24" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="O24" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>207</v>
       </c>
       <c r="Q24" s="8" t="b">
         <v>0</v>
@@ -2157,25 +2218,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D25" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="O25" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="O25" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>207</v>
       </c>
       <c r="Q25" s="8" t="b">
         <v>0</v>
@@ -2186,25 +2247,25 @@
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="O26" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="O26" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>207</v>
       </c>
       <c r="Q26" s="8" t="b">
         <v>0</v>
@@ -2215,25 +2276,25 @@
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="O27" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="Q27" s="8" t="b">
         <v>0</v>
@@ -2244,25 +2305,25 @@
         <v>22</v>
       </c>
       <c r="B28" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="O28" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="Q28" s="8" t="b">
         <v>0</v>
@@ -2273,83 +2334,83 @@
         <v>22</v>
       </c>
       <c r="B29" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>66</v>
+        <v>212</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="O29" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="Q29" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" s="8" customFormat="1" ht="110.25">
+    <row r="30" spans="1:20" s="8" customFormat="1" ht="63">
       <c r="A30" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O30" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="Q30" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" s="8" customFormat="1" ht="110.25">
+    <row r="31" spans="1:20" s="8" customFormat="1" ht="63">
       <c r="A31" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O31" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="Q31" s="8" t="b">
         <v>0</v>
@@ -2360,295 +2421,283 @@
         <v>22</v>
       </c>
       <c r="B32" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O32" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q32" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="33" spans="1:19" s="8" customFormat="1" ht="110.25">
       <c r="A33" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="O33" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="Q33" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:19" s="8" customFormat="1" ht="47.25">
+    <row r="34" spans="1:19" s="8" customFormat="1" ht="110.25">
       <c r="A34" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>237</v>
+        <v>70</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="N34" s="8" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="O34" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P34" s="8" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="Q34" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="8" customFormat="1" ht="47.25">
+    <row r="35" spans="1:19" s="8" customFormat="1" ht="63">
       <c r="A35" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>242</v>
+        <v>27</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="O35" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="Q35" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="8" customFormat="1" ht="78.75">
+    <row r="36" spans="1:19" s="8" customFormat="1" ht="47.25">
       <c r="A36" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="N36" s="8" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="O36" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="Q36" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="37" spans="1:19" s="8" customFormat="1" ht="47.25">
       <c r="A37" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B37" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="O37" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="Q37" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="38" spans="1:19" s="8" customFormat="1" ht="78.75">
       <c r="A38" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B38" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>250</v>
       </c>
       <c r="D38" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="N38" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="O38" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="Q38" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="A39" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="6">
+        <v>17</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="O39" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q39" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="A40" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="6">
+        <v>18</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="O38" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q38" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" s="8" customFormat="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="1:19" ht="110.25">
-      <c r="A40" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="1">
-        <v>1</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S40" s="1"/>
-    </row>
-    <row r="41" spans="1:19" ht="110.25">
-      <c r="A41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="1">
-        <v>2</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="1">
-        <v>2013</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S41" s="1"/>
+      <c r="N40" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="O40" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q40" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" s="8" customFormat="1">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:19" ht="110.25">
       <c r="A42" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B42" s="1">
-        <v>3</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D42" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>58</v>
+        <v>2014</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -2657,7 +2706,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="11" t="s">
+      <c r="M42" s="1" t="s">
         <v>38</v>
       </c>
       <c r="N42" s="1"/>
@@ -2665,7 +2714,7 @@
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="S42" s="1"/>
     </row>
@@ -2674,16 +2723,16 @@
         <v>32</v>
       </c>
       <c r="B43" s="1">
-        <v>4</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D43" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>59</v>
+        <v>2013</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -2692,15 +2741,15 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
-      <c r="M43" s="11" t="s">
-        <v>38</v>
+      <c r="M43" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="S43" s="1"/>
     </row>
@@ -2709,16 +2758,16 @@
         <v>32</v>
       </c>
       <c r="B44" s="1">
-        <v>5</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>55</v>
+        <v>3</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="D44" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>40</v>
+        <v>2012</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2735,7 +2784,7 @@
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="S44" s="1"/>
     </row>
@@ -2744,16 +2793,16 @@
         <v>32</v>
       </c>
       <c r="B45" s="1">
-        <v>6</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>56</v>
+        <v>4</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="D45" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>60</v>
+        <v>2012</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2770,7 +2819,7 @@
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S45" s="1"/>
     </row>
@@ -2779,16 +2828,16 @@
         <v>32</v>
       </c>
       <c r="B46" s="1">
-        <v>7</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="D46" s="1">
         <v>2010</v>
       </c>
-      <c r="E46" s="10" t="s">
-        <v>61</v>
+      <c r="E46" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2805,7 +2854,7 @@
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S46" s="1"/>
     </row>
@@ -2814,16 +2863,16 @@
         <v>32</v>
       </c>
       <c r="B47" s="1">
-        <v>8</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="D47" s="1">
         <v>2010</v>
       </c>
-      <c r="E47" s="10" t="s">
-        <v>62</v>
+      <c r="E47" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2840,7 +2889,7 @@
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S47" s="1"/>
     </row>
@@ -2849,16 +2898,16 @@
         <v>32</v>
       </c>
       <c r="B48" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D48" s="1">
         <v>2010</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2875,7 +2924,7 @@
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S48" s="1"/>
     </row>
@@ -2884,16 +2933,16 @@
         <v>32</v>
       </c>
       <c r="B49" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D49" s="1">
         <v>2010</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2910,86 +2959,98 @@
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S49" s="1"/>
+    </row>
+    <row r="50" spans="1:22" ht="110.25">
+      <c r="A50" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" s="1">
+        <v>9</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S50" s="1"/>
+    </row>
+    <row r="51" spans="1:22" ht="110.25">
+      <c r="A51" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="1">
+        <v>10</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S49" s="1"/>
-    </row>
-    <row r="50" spans="1:22" ht="189">
-      <c r="A50" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="1">
-        <v>1</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T50" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" ht="63">
-      <c r="A51" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="1">
-        <v>2</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q51" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" ht="63">
+      <c r="S51" s="1"/>
+    </row>
+    <row r="52" spans="1:22" ht="189">
       <c r="A52" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B52" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>74</v>
@@ -2998,24 +3059,24 @@
         <v>0</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" ht="78.75">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="63">
       <c r="A53" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B53" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>73</v>
@@ -3027,105 +3088,114 @@
         <v>1</v>
       </c>
       <c r="T53" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="63">
+      <c r="A54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="1">
+        <v>3</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="78.75">
+      <c r="A55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="1">
+        <v>4</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="1:22" s="13" customFormat="1" ht="78.75">
-      <c r="A54" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B54" s="1">
-        <v>1</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D54" s="13">
-        <v>2020</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S54" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="U54" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="V54" s="13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" ht="63">
-      <c r="A55" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B55" s="1">
-        <v>2</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D55" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U55" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" ht="63">
+    <row r="56" spans="1:22" s="13" customFormat="1" ht="78.75">
       <c r="A56" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B56" s="1">
-        <v>3</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2">
-        <v>2018</v>
+        <v>1</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D56" s="13">
+        <v>2020</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" ht="78.75">
+        <v>84</v>
+      </c>
+      <c r="S56" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="U56" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="V56" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="63">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B57" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="D57" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V57" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="63">
@@ -3133,145 +3203,194 @@
         <v>83</v>
       </c>
       <c r="B58" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="U58" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="63">
+    <row r="59" spans="1:22" ht="78.75">
       <c r="A59" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B59" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U59" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="63">
+      <c r="A60" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B60" s="1">
+        <v>5</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2016</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U60" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="63">
+      <c r="A61" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B61" s="1">
+        <v>6</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2">
         <v>2015</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E61" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="S59" s="2" t="s">
+      <c r="S61" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="U59" s="12" t="s">
+      <c r="U61" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="78.75">
-      <c r="A60" s="1" t="s">
+    <row r="62" spans="1:22" ht="78.75">
+      <c r="A62" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B60" s="1">
-        <v>1</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D60" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R60" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U60" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="V60" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" ht="78.75">
-      <c r="A61" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B61" s="1">
-        <v>2</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D61" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="R61" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="S61" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U61" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="V61" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" ht="94.5">
-      <c r="A62" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="B62" s="1">
         <v>1</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D62" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>111</v>
+        <v>2018</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22">
+        <v>102</v>
+      </c>
+      <c r="U62" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="78.75">
       <c r="A63" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B63" s="1">
         <v>2</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R63" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U63" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" ht="94.5">
+      <c r="A64" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" s="1">
+        <v>1</v>
+      </c>
+      <c r="C64" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D64" s="2">
         <v>2019</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E64" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" s="1">
+        <v>2</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E65" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="R63" s="2" t="s">
+      <c r="R65" s="2" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3281,7 +3400,7 @@
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J18" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
+    <hyperlink ref="J20" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
     <hyperlink ref="K2" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
     <hyperlink ref="K3" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
     <hyperlink ref="K4" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
@@ -3293,8 +3412,12 @@
     <hyperlink ref="K10" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
     <hyperlink ref="K12" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
     <hyperlink ref="K11" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
+    <hyperlink ref="R17" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
+    <hyperlink ref="S17" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
+    <hyperlink ref="K18" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
+    <hyperlink ref="R19" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>
--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32596631-58E5-45E9-98E1-0AB648C6DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A2BAA0-9367-4AE0-BEFF-F52BA736750E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="6285" yWindow="4680" windowWidth="21600" windowHeight="11505" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2683,7 +2683,7 @@
       <c r="C41" s="6"/>
       <c r="E41" s="6"/>
     </row>
-    <row r="42" spans="1:19" ht="110.25">
+    <row r="42" spans="1:19" ht="47.25">
       <c r="A42" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19" ht="110.25">
+    <row r="43" spans="1:19" ht="47.25">
       <c r="A43" s="1" t="s">
         <v>32</v>
       </c>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:19" ht="110.25">
+    <row r="44" spans="1:19" ht="47.25">
       <c r="A44" s="1" t="s">
         <v>32</v>
       </c>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:19" ht="110.25">
+    <row r="45" spans="1:19" ht="47.25">
       <c r="A45" s="1" t="s">
         <v>32</v>
       </c>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:19" ht="110.25">
+    <row r="46" spans="1:19" ht="47.25">
       <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" spans="1:19" ht="110.25">
+    <row r="47" spans="1:19" ht="47.25">
       <c r="A47" s="1" t="s">
         <v>32</v>
       </c>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:19" ht="110.25">
+    <row r="48" spans="1:19" ht="47.25">
       <c r="A48" s="1" t="s">
         <v>32</v>
       </c>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="1:22" ht="110.25">
+    <row r="49" spans="1:22" ht="47.25">
       <c r="A49" s="1" t="s">
         <v>32</v>
       </c>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="S49" s="1"/>
     </row>
-    <row r="50" spans="1:22" ht="110.25">
+    <row r="50" spans="1:22" ht="47.25">
       <c r="A50" s="1" t="s">
         <v>32</v>
       </c>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="S50" s="1"/>
     </row>
-    <row r="51" spans="1:22" ht="110.25">
+    <row r="51" spans="1:22" ht="47.25">
       <c r="A51" s="1" t="s">
         <v>32</v>
       </c>

--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A2BAA0-9367-4AE0-BEFF-F52BA736750E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABFCD38-6A36-4225-AE93-B2D1B9229CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6285" yWindow="4680" windowWidth="21600" windowHeight="11505" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="273">
   <si>
     <t>authors</t>
   </si>
@@ -402,9 +402,6 @@
     <t>0.1.4</t>
   </si>
   <si>
-    <t>https://oregon-k-entry.netlify.app/pre-k-dashboard/</t>
-  </si>
-  <si>
     <t>https://cran.r-project.org/package=equatiomatic</t>
   </si>
   <si>
@@ -835,6 +832,27 @@
   </si>
   <si>
     <t xml:space="preserve">Zaremehrjardy, M., Victor, J., Park, S., Smerdon, B., Daniel, S. </t>
+  </si>
+  <si>
+    <t>youtube</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9OLHA5hhEek</t>
+  </si>
+  <si>
+    <t>https://scholarsarchive.byu.edu/cgi/viewcontent.cgi?article=4038&amp;context=iemssconference</t>
+  </si>
+  <si>
+    <t>https://scholarsarchive.byu.edu/cgi/viewcontent.cgi?article=4041&amp;context=iemssconference</t>
+  </si>
+  <si>
+    <t>https://scholarsarchive.byu.edu/cgi/viewcontent.cgi?article=4094&amp;context=iemssconference</t>
+  </si>
+  <si>
+    <t>https://ui.adsabs.harvard.edu/abs/2018AGUFM.H33N2261A/abstract</t>
+  </si>
+  <si>
+    <t>https://ui.adsabs.harvard.edu/abs/2019AGUFM.H32E..05A/abstract</t>
   </si>
 </sst>
 </file>
@@ -1307,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="2" width="11" style="2"/>
@@ -1326,7 +1344,7 @@
     <col min="19" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="31.5">
+    <row r="1" spans="1:23" ht="31.5">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1393,8 +1411,11 @@
       <c r="V1" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" ht="47.25">
+      <c r="W1" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="47.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1402,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D2" s="1">
         <v>2021</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="G2" s="1">
         <v>134</v>
@@ -1420,10 +1441,10 @@
         <v>105093</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1434,7 +1455,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="47.25">
+    <row r="3" spans="1:23" ht="47.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1442,29 +1463,29 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" s="1">
         <v>2020</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="G3" s="1">
         <v>32</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1475,7 +1496,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="63">
+    <row r="4" spans="1:23" ht="63">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1483,16 +1504,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4" s="1">
         <v>2020</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="G4" s="1">
         <v>745</v>
@@ -1502,10 +1523,10 @@
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1516,7 +1537,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:22" s="8" customFormat="1" ht="47.25">
+    <row r="5" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -1524,16 +1545,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="6">
         <v>2020</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G5" s="6">
         <v>10</v>
@@ -1543,10 +1564,10 @@
         <v>503</v>
       </c>
       <c r="J5" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>149</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -1557,7 +1578,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
     </row>
-    <row r="6" spans="1:22" s="8" customFormat="1" ht="47.25">
+    <row r="6" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
@@ -1565,16 +1586,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D6" s="6">
         <v>2020</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G6" s="6">
         <v>126</v>
@@ -1584,10 +1605,10 @@
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -1598,7 +1619,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
     </row>
-    <row r="7" spans="1:22" s="8" customFormat="1" ht="47.25">
+    <row r="7" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
@@ -1606,16 +1627,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D7" s="6">
         <v>2020</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="G7" s="6">
         <v>706</v>
@@ -1625,10 +1646,10 @@
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>156</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>157</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -1639,7 +1660,7 @@
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
     </row>
-    <row r="8" spans="1:22" s="8" customFormat="1" ht="47.25">
+    <row r="8" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -1647,16 +1668,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D8" s="6">
         <v>2019</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="G8" s="6">
         <v>9</v>
@@ -1666,10 +1687,10 @@
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>163</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -1680,7 +1701,7 @@
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
     </row>
-    <row r="9" spans="1:22" s="8" customFormat="1" ht="47.25">
+    <row r="9" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -1688,16 +1709,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D9" s="6">
         <v>2019</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="G9" s="6">
         <v>11</v>
@@ -1707,10 +1728,10 @@
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -1721,7 +1742,7 @@
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
     </row>
-    <row r="10" spans="1:22" s="8" customFormat="1" ht="47.25">
+    <row r="10" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
@@ -1729,29 +1750,29 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D10" s="6">
         <v>2019</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>173</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -1762,7 +1783,7 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
     </row>
-    <row r="11" spans="1:22" s="8" customFormat="1" ht="47.25">
+    <row r="11" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
@@ -1770,29 +1791,29 @@
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D11" s="6">
         <v>2019</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G11" s="6">
         <v>111</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -1803,7 +1824,7 @@
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
     </row>
-    <row r="12" spans="1:22" s="8" customFormat="1" ht="47.25">
+    <row r="12" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
@@ -1811,29 +1832,29 @@
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D12" s="6">
         <v>2019</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="G12" s="6">
         <v>64</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="J12" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="K12" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -1844,7 +1865,7 @@
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
     </row>
-    <row r="13" spans="1:22" s="8" customFormat="1">
+    <row r="13" spans="1:23" s="8" customFormat="1">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1865,7 +1886,7 @@
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
     </row>
-    <row r="14" spans="1:22" s="8" customFormat="1">
+    <row r="14" spans="1:23" s="8" customFormat="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1886,7 +1907,7 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:23">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1907,21 +1928,21 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:22" ht="31.5">
+    <row r="16" spans="1:23" ht="31.5">
       <c r="A16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1938,21 +1959,21 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:20" s="18" customFormat="1" ht="126">
+    <row r="17" spans="1:23" s="18" customFormat="1" ht="126">
       <c r="A17" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B17" s="17">
         <v>1</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D17" s="17">
         <v>2019</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
@@ -1962,34 +1983,34 @@
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
       <c r="Q17" s="17"/>
       <c r="R17" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="S17" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="S17" s="20" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="63">
+    </row>
+    <row r="18" spans="1:23" ht="63">
       <c r="A18" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D18" s="1">
         <v>2019</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1997,11 +2018,11 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -2010,21 +2031,21 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:20" ht="63">
+    <row r="19" spans="1:23" ht="63">
       <c r="A19" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D19" s="1">
         <v>2017</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -2034,18 +2055,18 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:20" ht="78.75">
+    <row r="20" spans="1:23" ht="78.75">
       <c r="A20" s="1" t="s">
         <v>13</v>
       </c>
@@ -2066,7 +2087,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>118</v>
@@ -2086,7 +2107,7 @@
       </c>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:20" ht="126">
+    <row r="21" spans="1:23" ht="126">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
@@ -2123,7 +2144,7 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:20" s="18" customFormat="1" ht="78.75">
+    <row r="22" spans="1:23" s="18" customFormat="1" ht="78.75">
       <c r="A22" s="17" t="s">
         <v>22</v>
       </c>
@@ -2131,31 +2152,31 @@
         <v>1</v>
       </c>
       <c r="C22" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="N22" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="O22" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="N22" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="O22" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="18" t="s">
-        <v>191</v>
-      </c>
       <c r="Q22" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="T22" s="18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" s="8" customFormat="1" ht="63">
+      <c r="W22" s="20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
@@ -2163,28 +2184,31 @@
         <v>2</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="N23" s="8" t="s">
+      <c r="O23" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="O23" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>195</v>
-      </c>
       <c r="Q23" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" s="8" customFormat="1" ht="63">
+      <c r="R23" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A24" s="6" t="s">
         <v>22</v>
       </c>
@@ -2192,28 +2216,28 @@
         <v>3</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="N24" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="N24" s="8" t="s">
-        <v>197</v>
-      </c>
       <c r="O24" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q24" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" s="8" customFormat="1" ht="63">
+    <row r="25" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A25" s="6" t="s">
         <v>22</v>
       </c>
@@ -2221,28 +2245,28 @@
         <v>4</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="O25" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="O25" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>203</v>
-      </c>
       <c r="Q25" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" s="8" customFormat="1" ht="63">
+    <row r="26" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A26" s="6" t="s">
         <v>22</v>
       </c>
@@ -2250,28 +2274,28 @@
         <v>5</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O26" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q26" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" s="8" customFormat="1" ht="63">
+    <row r="27" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A27" s="6" t="s">
         <v>22</v>
       </c>
@@ -2279,28 +2303,28 @@
         <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O27" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q27" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" s="8" customFormat="1" ht="63">
+    <row r="28" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A28" s="6" t="s">
         <v>22</v>
       </c>
@@ -2308,28 +2332,28 @@
         <v>7</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O28" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q28" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" s="8" customFormat="1" ht="63">
+    <row r="29" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A29" s="6" t="s">
         <v>22</v>
       </c>
@@ -2337,28 +2361,31 @@
         <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="N29" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N29" s="8" t="s">
+      <c r="O29" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="O29" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>214</v>
-      </c>
       <c r="Q29" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" s="8" customFormat="1" ht="63">
+      <c r="R29" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A30" s="6" t="s">
         <v>22</v>
       </c>
@@ -2366,28 +2393,28 @@
         <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>66</v>
       </c>
       <c r="E30" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="N30" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="N30" s="8" t="s">
-        <v>216</v>
-      </c>
       <c r="O30" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q30" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" s="8" customFormat="1" ht="63">
+    <row r="31" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A31" s="6" t="s">
         <v>22</v>
       </c>
@@ -2395,28 +2422,28 @@
         <v>9</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>66</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O31" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q31" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" s="8" customFormat="1" ht="110.25">
+    <row r="32" spans="1:23" s="8" customFormat="1" ht="110.25">
       <c r="A32" s="6" t="s">
         <v>22</v>
       </c>
@@ -2424,25 +2451,28 @@
         <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="N32" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="O32" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="O32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>223</v>
-      </c>
       <c r="Q32" s="8" t="b">
         <v>0</v>
+      </c>
+      <c r="R32" s="7" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:19" s="8" customFormat="1" ht="110.25">
@@ -2453,25 +2483,28 @@
         <v>11</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N33" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="O33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P33" s="8" t="s">
-        <v>223</v>
-      </c>
       <c r="Q33" s="8" t="b">
         <v>0</v>
+      </c>
+      <c r="R33" s="7" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="34" spans="1:19" s="8" customFormat="1" ht="110.25">
@@ -2482,25 +2515,28 @@
         <v>12</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N34" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O34" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="O34" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P34" s="8" t="s">
-        <v>223</v>
-      </c>
       <c r="Q34" s="8" t="b">
         <v>0</v>
+      </c>
+      <c r="R34" s="7" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:19" s="8" customFormat="1" ht="63">
@@ -2511,22 +2547,22 @@
         <v>13</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E35" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="N35" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="N35" s="8" t="s">
-        <v>228</v>
-      </c>
       <c r="O35" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q35" s="8" t="b">
         <v>0</v>
@@ -2540,22 +2576,22 @@
         <v>14</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="O36" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="O36" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P36" s="8" t="s">
-        <v>234</v>
       </c>
       <c r="Q36" s="8" t="b">
         <v>0</v>
@@ -2569,22 +2605,22 @@
         <v>15</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="E37" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="O37" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="8" t="s">
         <v>238</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="O37" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" s="8" t="s">
-        <v>239</v>
       </c>
       <c r="Q37" s="8" t="b">
         <v>0</v>
@@ -2598,22 +2634,22 @@
         <v>16</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>251</v>
-      </c>
       <c r="E38" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="N38" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="O38" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="O38" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>249</v>
       </c>
       <c r="Q38" s="8" t="b">
         <v>0</v>
@@ -2627,22 +2663,22 @@
         <v>17</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>244</v>
-      </c>
       <c r="E39" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="N39" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="N39" s="8" t="s">
+      <c r="O39" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="8" t="s">
         <v>241</v>
-      </c>
-      <c r="O39" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P39" s="8" t="s">
-        <v>242</v>
       </c>
       <c r="Q39" s="8" t="b">
         <v>0</v>
@@ -2656,22 +2692,22 @@
         <v>18</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D40" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>245</v>
-      </c>
       <c r="N40" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="O40" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="8" t="s">
         <v>241</v>
-      </c>
-      <c r="O40" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P40" s="8" t="s">
-        <v>242</v>
       </c>
       <c r="Q40" s="8" t="b">
         <v>0</v>
@@ -3157,7 +3193,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D56" s="13">
         <v>2020</v>
@@ -3172,7 +3208,7 @@
         <v>0.1</v>
       </c>
       <c r="V56" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="63">
@@ -3183,7 +3219,7 @@
         <v>2</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D57" s="2">
         <v>2019</v>
@@ -3416,8 +3452,14 @@
     <hyperlink ref="S17" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
     <hyperlink ref="K18" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
     <hyperlink ref="R19" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
+    <hyperlink ref="W22" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R34" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R33" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R32" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R29" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R23" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId23"/>
 </worksheet>
 </file>
--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABFCD38-6A36-4225-AE93-B2D1B9229CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B14ADDC-CC70-42AC-9E6F-6CCBB29F9A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="27165" yWindow="3120" windowWidth="22440" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="282">
   <si>
     <t>authors</t>
   </si>
@@ -853,6 +853,33 @@
   </si>
   <si>
     <t>https://ui.adsabs.harvard.edu/abs/2019AGUFM.H32E..05A/abstract</t>
+  </si>
+  <si>
+    <t>Bailey, R.T., Jeong, J., Park, S. and Green, C.H.</t>
+  </si>
+  <si>
+    <t>Simulating Salinity Transport in High-Desert Landscapes using APEX-MODFLOW-Salt</t>
+  </si>
+  <si>
+    <t>Journal of Hydrology</t>
+  </si>
+  <si>
+    <t>Development of a Field Scale, SWAT+ Modeling Framework for the Contiguous US</t>
+  </si>
+  <si>
+    <t>Mike White, Jeff Arnold, Katrin Bieger, Peter Allen, Jungang Gao, Natalja Cerkasova, Mauro DiLuzio, Marilyn Gambone, Park, S., David D. Bosch, Haw Yen</t>
+  </si>
+  <si>
+    <t>Journal of the American Water Resources Association</t>
+  </si>
+  <si>
+    <t>Spatio-temporal variation of water resource and fluxes in the Okavango basin</t>
+  </si>
+  <si>
+    <t>Park, S., Jaehak Jeong, Tracy Baker, Piotr Wolski, Tadesse Abitew, Mike Murray-Hudson, Sekgowa Motsumi, Colin Apse and Carlos Andrade</t>
+  </si>
+  <si>
+    <t>Water Resources Research</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="2" width="11" style="2"/>
@@ -1907,13 +1934,25 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
     </row>
-    <row r="15" spans="1:23">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+    <row r="15" spans="1:23" ht="47.25">
+      <c r="A15" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>281</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1933,18 +1972,20 @@
         <v>123</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F16" s="1"/>
+        <v>274</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>275</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1959,71 +2000,65 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:23" s="18" customFormat="1" ht="126">
-      <c r="A17" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="B17" s="17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="D17" s="17">
-        <v>2019</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="S17" s="20" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="63">
+    <row r="17" spans="1:23" ht="63">
+      <c r="A17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+    </row>
+    <row r="18" spans="1:23" ht="31.5">
       <c r="A18" s="1" t="s">
-        <v>251</v>
+        <v>123</v>
       </c>
       <c r="B18" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>265</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>275</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="3" t="s">
-        <v>262</v>
-      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="1" t="s">
-        <v>259</v>
-      </c>
+      <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -2031,210 +2066,221 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="63">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:23" s="18" customFormat="1" ht="126">
+      <c r="A19" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="B19" s="1">
-        <v>3</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="S19" s="1"/>
-    </row>
-    <row r="20" spans="1:23" ht="78.75">
+      <c r="B19" s="17">
+        <v>1</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="D19" s="17">
+        <v>2019</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="S19" s="20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="63">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>256</v>
       </c>
       <c r="D20" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>2019</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>253</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-      <c r="R20" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="R20" s="1"/>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:23" ht="126">
+    <row r="21" spans="1:23" ht="63">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="B21" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>255</v>
       </c>
       <c r="D21" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>57</v>
+        <v>2017</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>254</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
+      <c r="R21" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:23" s="18" customFormat="1" ht="78.75">
-      <c r="A22" s="17" t="s">
+    <row r="22" spans="1:23" ht="78.75">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S22" s="1"/>
+    </row>
+    <row r="23" spans="1:23" ht="126">
+      <c r="A23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+    </row>
+    <row r="24" spans="1:23" s="18" customFormat="1" ht="78.75">
+      <c r="A24" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B24" s="17">
         <v>1</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C24" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D24" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="N22" s="18" t="s">
+      <c r="N24" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="O22" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="18" t="s">
+      <c r="O24" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="Q22" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="20" t="s">
+      <c r="Q24" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24" s="20" t="s">
         <v>267</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A23" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="O23" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q23" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="6">
-        <v>3</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O24" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q24" s="8" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:23" s="8" customFormat="1" ht="63">
@@ -2242,28 +2288,31 @@
         <v>22</v>
       </c>
       <c r="B25" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O25" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Q25" s="8" t="b">
         <v>0</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:23" s="8" customFormat="1" ht="63">
@@ -2271,16 +2320,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="N26" s="8" t="s">
         <v>196</v>
@@ -2300,16 +2349,16 @@
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="N27" s="8" t="s">
         <v>196</v>
@@ -2329,16 +2378,16 @@
         <v>22</v>
       </c>
       <c r="B28" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N28" s="8" t="s">
         <v>196</v>
@@ -2358,31 +2407,28 @@
         <v>22</v>
       </c>
       <c r="B29" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="O29" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="Q29" s="8" t="b">
         <v>0</v>
-      </c>
-      <c r="R29" s="7" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:23" s="8" customFormat="1" ht="63">
@@ -2390,25 +2436,25 @@
         <v>22</v>
       </c>
       <c r="B30" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="O30" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="Q30" s="8" t="b">
         <v>0</v>
@@ -2419,92 +2465,89 @@
         <v>22</v>
       </c>
       <c r="B31" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O31" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Q31" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" s="8" customFormat="1" ht="110.25">
+      <c r="R31" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A32" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O32" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q32" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="R32" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" s="8" customFormat="1" ht="110.25">
+    </row>
+    <row r="33" spans="1:19" s="8" customFormat="1" ht="63">
       <c r="A33" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O33" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q33" s="8" t="b">
         <v>0</v>
-      </c>
-      <c r="R33" s="7" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="34" spans="1:19" s="8" customFormat="1" ht="110.25">
@@ -2512,16 +2555,16 @@
         <v>22</v>
       </c>
       <c r="B34" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N34" s="8" t="s">
         <v>221</v>
@@ -2536,274 +2579,268 @@
         <v>0</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" s="8" customFormat="1" ht="63">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" s="8" customFormat="1" ht="110.25">
       <c r="A35" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="O35" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P35" s="8" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="Q35" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="R35" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" s="8" customFormat="1" ht="110.25">
       <c r="A36" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N36" s="8" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="O36" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="Q36" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="R36" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" s="8" customFormat="1" ht="63">
       <c r="A37" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B37" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="O37" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="Q37" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="8" customFormat="1" ht="78.75">
+    <row r="38" spans="1:19" s="8" customFormat="1" ht="47.25">
       <c r="A38" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B38" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="N38" s="8" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="O38" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="Q38" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="39" spans="1:19" s="8" customFormat="1" ht="47.25">
       <c r="A39" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O39" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q39" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="40" spans="1:19" s="8" customFormat="1" ht="78.75">
       <c r="A40" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B40" s="6">
+        <v>16</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="O40" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q40" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="A41" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="6">
+        <v>17</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="O41" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q41" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="A42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="6">
         <v>18</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D42" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E42" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="N40" s="8" t="s">
+      <c r="N42" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="O40" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P40" s="8" t="s">
+      <c r="O42" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="Q40" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" s="8" customFormat="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="42" spans="1:19" ht="47.25">
-      <c r="A42" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="1">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S42" s="1"/>
-    </row>
-    <row r="43" spans="1:19" ht="47.25">
-      <c r="A43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="1">
-        <v>2013</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S43" s="1"/>
+      <c r="Q42" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" s="8" customFormat="1">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="E43" s="6"/>
     </row>
     <row r="44" spans="1:19" ht="47.25">
       <c r="A44" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B44" s="1">
-        <v>3</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D44" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>58</v>
+        <v>2014</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2812,7 +2849,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="11" t="s">
+      <c r="M44" s="1" t="s">
         <v>38</v>
       </c>
       <c r="N44" s="1"/>
@@ -2820,7 +2857,7 @@
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="S44" s="1"/>
     </row>
@@ -2829,16 +2866,16 @@
         <v>32</v>
       </c>
       <c r="B45" s="1">
-        <v>4</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D45" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>59</v>
+        <v>2013</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2847,15 +2884,15 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="11" t="s">
-        <v>38</v>
+      <c r="M45" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="S45" s="1"/>
     </row>
@@ -2864,16 +2901,16 @@
         <v>32</v>
       </c>
       <c r="B46" s="1">
-        <v>5</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>55</v>
+        <v>3</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="D46" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>40</v>
+        <v>2012</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2890,7 +2927,7 @@
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="S46" s="1"/>
     </row>
@@ -2899,16 +2936,16 @@
         <v>32</v>
       </c>
       <c r="B47" s="1">
-        <v>6</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>56</v>
+        <v>4</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="D47" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>60</v>
+        <v>2012</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2925,7 +2962,7 @@
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S47" s="1"/>
     </row>
@@ -2934,16 +2971,16 @@
         <v>32</v>
       </c>
       <c r="B48" s="1">
-        <v>7</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="D48" s="1">
         <v>2010</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>61</v>
+      <c r="E48" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2960,7 +2997,7 @@
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S48" s="1"/>
     </row>
@@ -2969,16 +3006,16 @@
         <v>32</v>
       </c>
       <c r="B49" s="1">
-        <v>8</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="D49" s="1">
         <v>2010</v>
       </c>
-      <c r="E49" s="10" t="s">
-        <v>62</v>
+      <c r="E49" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2995,7 +3032,7 @@
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S49" s="1"/>
     </row>
@@ -3004,16 +3041,16 @@
         <v>32</v>
       </c>
       <c r="B50" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D50" s="1">
         <v>2010</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -3030,7 +3067,7 @@
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
       <c r="R50" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S50" s="1"/>
     </row>
@@ -3039,16 +3076,16 @@
         <v>32</v>
       </c>
       <c r="B51" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D51" s="1">
         <v>2010</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -3065,86 +3102,98 @@
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
       <c r="R51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S51" s="1"/>
+    </row>
+    <row r="52" spans="1:22" ht="47.25">
+      <c r="A52" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" s="1">
+        <v>9</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S52" s="1"/>
+    </row>
+    <row r="53" spans="1:22" ht="47.25">
+      <c r="A53" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="1">
+        <v>10</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S51" s="1"/>
-    </row>
-    <row r="52" spans="1:22" ht="189">
-      <c r="A52" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="1">
-        <v>1</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P52" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T52" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" ht="63">
-      <c r="A53" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="1">
-        <v>2</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q53" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" ht="63">
+      <c r="S53" s="1"/>
+    </row>
+    <row r="54" spans="1:22" ht="189">
       <c r="A54" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>74</v>
@@ -3153,24 +3202,24 @@
         <v>0</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" ht="78.75">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="63">
       <c r="A55" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B55" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>73</v>
@@ -3182,105 +3231,114 @@
         <v>1</v>
       </c>
       <c r="T55" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="63">
+      <c r="A56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="1">
+        <v>3</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="78.75">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1">
+        <v>4</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q57" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="56" spans="1:22" s="13" customFormat="1" ht="78.75">
-      <c r="A56" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B56" s="1">
-        <v>1</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D56" s="13">
-        <v>2020</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S56" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="U56" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="V56" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" ht="63">
-      <c r="A57" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B57" s="1">
-        <v>2</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="S57" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U57" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" ht="63">
+    <row r="58" spans="1:22" s="13" customFormat="1" ht="78.75">
       <c r="A58" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B58" s="1">
-        <v>3</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2">
-        <v>2018</v>
+        <v>1</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D58" s="13">
+        <v>2020</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="S58" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U58" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" ht="78.75">
+        <v>84</v>
+      </c>
+      <c r="S58" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="U58" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="V58" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="63">
       <c r="A59" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B59" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D59" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:22" ht="63">
@@ -3288,145 +3346,194 @@
         <v>83</v>
       </c>
       <c r="B60" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="U60" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:22" ht="63">
+    <row r="61" spans="1:22" ht="78.75">
       <c r="A61" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B61" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="63">
+      <c r="A62" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B62" s="1">
+        <v>5</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2">
+        <v>2016</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U62" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="63">
+      <c r="A63" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="1">
+        <v>6</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2">
         <v>2015</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E63" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="S61" s="2" t="s">
+      <c r="S63" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="U61" s="12" t="s">
+      <c r="U63" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:22" ht="78.75">
-      <c r="A62" s="1" t="s">
+    <row r="64" spans="1:22" ht="78.75">
+      <c r="A64" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D62" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R62" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S62" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U62" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" ht="78.75">
-      <c r="A63" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D63" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="R63" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="S63" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U63" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" ht="94.5">
-      <c r="A64" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="B64" s="1">
         <v>1</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D64" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>111</v>
+        <v>2018</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18">
+        <v>102</v>
+      </c>
+      <c r="U64" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" ht="78.75">
       <c r="A65" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B65" s="1">
         <v>2</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C65" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D65" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U65" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" ht="94.5">
+      <c r="A66" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B66" s="1">
+        <v>1</v>
+      </c>
+      <c r="C66" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D66" s="2">
         <v>2019</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E66" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22">
+      <c r="A67" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E67" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="R65" s="2" t="s">
+      <c r="R67" s="2" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3436,7 +3543,7 @@
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J20" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
+    <hyperlink ref="J22" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
     <hyperlink ref="K2" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
     <hyperlink ref="K3" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
     <hyperlink ref="K4" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
@@ -3448,16 +3555,16 @@
     <hyperlink ref="K10" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
     <hyperlink ref="K12" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
     <hyperlink ref="K11" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
-    <hyperlink ref="R17" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
-    <hyperlink ref="S17" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
-    <hyperlink ref="K18" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
-    <hyperlink ref="R19" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W22" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R34" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R33" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R32" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R29" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R23" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="R19" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
+    <hyperlink ref="S19" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
+    <hyperlink ref="K20" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
+    <hyperlink ref="R21" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
+    <hyperlink ref="W24" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R36" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R35" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R34" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R31" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R25" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId23"/>

--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B14ADDC-CC70-42AC-9E6F-6CCBB29F9A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1CB808-E596-449C-912D-97A10025BE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27165" yWindow="3120" windowWidth="22440" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="306">
   <si>
     <t>authors</t>
   </si>
@@ -828,12 +828,6 @@
     <t>https://swat.tamu.edu/media/115048/swat-modflow-tutorial.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Assessment of snowmelt and groundwater-surface water dynamics in mountainous, foothill and plains regions in northern latitudes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zaremehrjardy, M., Victor, J., Park, S., Smerdon, B., Daniel, S. </t>
-  </si>
-  <si>
     <t>youtube</t>
   </si>
   <si>
@@ -867,19 +861,97 @@
     <t>Development of a Field Scale, SWAT+ Modeling Framework for the Contiguous US</t>
   </si>
   <si>
-    <t>Mike White, Jeff Arnold, Katrin Bieger, Peter Allen, Jungang Gao, Natalja Cerkasova, Mauro DiLuzio, Marilyn Gambone, Park, S., David D. Bosch, Haw Yen</t>
-  </si>
-  <si>
     <t>Journal of the American Water Resources Association</t>
   </si>
   <si>
     <t>Spatio-temporal variation of water resource and fluxes in the Okavango basin</t>
   </si>
   <si>
-    <t>Park, S., Jaehak Jeong, Tracy Baker, Piotr Wolski, Tadesse Abitew, Mike Murray-Hudson, Sekgowa Motsumi, Colin Apse and Carlos Andrade</t>
-  </si>
-  <si>
     <t>Water Resources Research</t>
+  </si>
+  <si>
+    <t>Michael White, Jeff Arnold, Katrin Bieger, Peter Allen, Jungang Gao, Natalja Cerkasova, Mauro DiLuzio, Marilyn Gambone, Park, S., David D. Bosch, Haw Yen</t>
+  </si>
+  <si>
+    <t>Assessment of snowmelt and groundwater-surface water dynamics in mountainous, foothill, and plain regions in northern latitudes</t>
+  </si>
+  <si>
+    <t>Zaremehrjardy, M., Victor, J., Park, S., Smerdon, B., Alessi, D.S. and Faramarzi, M.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jhydrol.2022.127449</t>
+  </si>
+  <si>
+    <t>10.1016/j.jhydrol.2022.127449</t>
+  </si>
+  <si>
+    <t>Park, S., Jaehak, J., Tracy Baker, Piotr Wolski, Tadesse Abitew, Mike Murray-Hudson, Sekgowa Motsumi, Colin Apse and Carlos Andrade</t>
+  </si>
+  <si>
+    <t>Introducing APEXMOD, A QGIS plugin for application and evaluation for the Enhanced APEX model</t>
+  </si>
+  <si>
+    <t>Park, S., Jeong, J.,  Motter, E., and Bailey, R.</t>
+  </si>
+  <si>
+    <t>Park, S., Jeong, J., Baker, B., Wolski, P., Abitew, T., Murray-Hudson, M., Motsumi, S., Apse, C., and Andrade, C.</t>
+  </si>
+  <si>
+    <t>December, 2021</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting 2021</t>
+  </si>
+  <si>
+    <t>https://agu.confex.com/agu/fm21/meetingapp.cgi/Paper/844635</t>
+  </si>
+  <si>
+    <t>New Orleans, LA, United States</t>
+  </si>
+  <si>
+    <t>A Machine Learning Approach for Assessing Wildfire Vulnerability in the Colorado River Basin</t>
+  </si>
+  <si>
+    <t>H Han, TA Abitew, S Park, C Green, J Jeong</t>
+  </si>
+  <si>
+    <t>https://agu.confex.com/agu/fm21/meetingapp.cgi/Paper/832202</t>
+  </si>
+  <si>
+    <t>https://agu.confex.com/agu/fm21/meetingapp.cgi/Paper/830768</t>
+  </si>
+  <si>
+    <t>Reproducible Parameter Estimation Framework for Integrated Hydrological Models as Evidenced in the Colorado River Basin</t>
+  </si>
+  <si>
+    <t>Park, S., Abitew, TA., Jeong, J., Han, H., and Green, C.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting 2022</t>
+  </si>
+  <si>
+    <t>https://agu.confex.com/agu/fm21/meetingapp.cgi/Paper/845898</t>
+  </si>
+  <si>
+    <t>technical_report</t>
+  </si>
+  <si>
+    <t>Park, S., Baker, T. and Jeong, J.</t>
+  </si>
+  <si>
+    <t>BREC Report No. 21-01.</t>
+  </si>
+  <si>
+    <t>Development Of The Cubango-Okavango River Basin SWAT-MODFLOW Model</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW Relink Editor On Hydrologic And Water Quality System (HAWQS)</t>
+  </si>
+  <si>
+    <t>BREC Report No. 22-01.</t>
+  </si>
+  <si>
+    <t>Park, S., Baker, T., Srinivasan, R. and Jeong, J.</t>
   </si>
 </sst>
 </file>
@@ -948,7 +1020,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -957,7 +1029,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -975,7 +1053,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1028,13 +1106,34 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1352,23 +1451,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="2" width="11" style="2"/>
+    <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11" style="2"/>
     <col min="3" max="3" width="44.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="11" style="2"/>
     <col min="5" max="5" width="55.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="7.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="11" style="2"/>
     <col min="11" max="11" width="35.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11" style="2"/>
+    <col min="12" max="12" width="26.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="26" style="2" customWidth="1"/>
     <col min="14" max="17" width="11" style="2"/>
     <col min="18" max="18" width="74" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="11" style="2"/>
+    <col min="19" max="19" width="33.5" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="31.5">
@@ -1439,7 +1540,7 @@
         <v>89</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="47.25">
@@ -1450,28 +1551,27 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>132</v>
+        <v>280</v>
       </c>
       <c r="D2" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>128</v>
+        <v>279</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G2" s="1">
-        <v>134</v>
-      </c>
-      <c r="H2" s="1">
-        <v>105093</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>130</v>
+        <v>273</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="1">
+        <v>127449</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>282</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>131</v>
+        <v>281</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1481,6 +1581,9 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
     </row>
     <row r="3" spans="1:23" ht="47.25">
       <c r="A3" s="1" t="s">
@@ -1490,29 +1593,28 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D3" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="1">
         <v>134</v>
       </c>
-      <c r="G3" s="1">
-        <v>32</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="4" t="s">
-        <v>138</v>
+      <c r="I3" s="21">
+        <v>105093</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1523,7 +1625,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:23" ht="63">
+    <row r="4" spans="1:23" ht="47.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1531,29 +1633,29 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D4" s="1">
         <v>2020</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>139</v>
+      <c r="E4" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G4" s="1">
-        <v>745</v>
-      </c>
-      <c r="H4" s="1">
-        <v>140933</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="5" t="s">
-        <v>141</v>
+        <v>32</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1564,78 +1666,77 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:23" ht="63">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="1">
         <v>2020</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="6">
-        <v>10</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6">
-        <v>503</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
+      <c r="E5" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="1">
+        <v>745</v>
+      </c>
+      <c r="I5" s="21">
+        <v>140933</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D6" s="6">
         <v>2020</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>129</v>
+        <v>143</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="G6" s="6">
-        <v>126</v>
-      </c>
-      <c r="H6" s="6">
-        <v>104660</v>
-      </c>
-      <c r="I6" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="6">
+        <v>503</v>
+      </c>
       <c r="J6" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -1650,33 +1751,32 @@
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D7" s="6">
         <v>2020</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="G7" s="6">
-        <v>706</v>
-      </c>
-      <c r="H7" s="6">
-        <v>135702</v>
-      </c>
-      <c r="I7" s="6"/>
+        <v>126</v>
+      </c>
+      <c r="I7" s="22">
+        <v>104660</v>
+      </c>
       <c r="J7" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -1691,33 +1791,32 @@
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D8" s="6">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G8" s="6">
-        <v>9</v>
-      </c>
-      <c r="H8" s="6">
-        <v>100260</v>
-      </c>
-      <c r="I8" s="6"/>
+        <v>706</v>
+      </c>
+      <c r="I8" s="22">
+        <v>135702</v>
+      </c>
       <c r="J8" s="6" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -1732,33 +1831,32 @@
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D9" s="6">
         <v>2019</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G9" s="6">
-        <v>11</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1681</v>
-      </c>
-      <c r="I9" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="I9" s="22">
+        <v>100260</v>
+      </c>
       <c r="J9" s="6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -1773,33 +1871,33 @@
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="D10" s="6">
         <v>2019</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="16" t="s">
-        <v>173</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G10" s="6">
+        <v>11</v>
+      </c>
+      <c r="H10" s="22">
+        <v>1681</v>
+      </c>
+      <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -1814,33 +1912,33 @@
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="D11" s="6">
         <v>2019</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G11" s="6">
-        <v>111</v>
+        <v>169</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="I11" s="15" t="s">
-        <v>182</v>
+      <c r="I11" s="16" t="s">
+        <v>173</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -1855,33 +1953,33 @@
       <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D12" s="6">
         <v>2019</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G12" s="6">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="15" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -1892,18 +1990,38 @@
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
     </row>
-    <row r="13" spans="1:23" s="8" customFormat="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+    <row r="13" spans="1:23" s="8" customFormat="1" ht="47.25">
+      <c r="A13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>12</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2019</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="6">
+        <v>64</v>
+      </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="7"/>
+      <c r="I13" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>185</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
@@ -1913,78 +2031,66 @@
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
     </row>
-    <row r="14" spans="1:23" s="8" customFormat="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-    </row>
-    <row r="15" spans="1:23" ht="47.25">
-      <c r="A15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="1:23" ht="31.5">
+    <row r="14" spans="1:23" s="20" customFormat="1">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+    </row>
+    <row r="15" spans="1:23" s="20" customFormat="1">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+    </row>
+    <row r="16" spans="1:23" ht="47.25">
       <c r="A16" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -2000,24 +2106,24 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:23" ht="63">
+    <row r="17" spans="1:19" ht="31.5">
       <c r="A17" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B17" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -2033,21 +2139,21 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:23" ht="31.5">
+    <row r="18" spans="1:19" ht="63">
       <c r="A18" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B18" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>275</v>
@@ -2066,1507 +2172,1902 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:23" s="18" customFormat="1" ht="126">
-      <c r="A19" s="17" t="s">
+    <row r="19" spans="1:19" ht="47.25">
+      <c r="A19" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="1">
+        <v>4</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+    </row>
+    <row r="20" spans="1:19" s="24" customFormat="1">
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="23"/>
+    </row>
+    <row r="21" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="A21" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B21" s="6">
         <v>1</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C21" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D21" s="6">
         <v>2019</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E21" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17" t="s">
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="20" t="s">
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="S19" s="20" t="s">
+      <c r="S21" s="7" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="63">
-      <c r="A20" s="1" t="s">
+    <row r="22" spans="1:19" ht="63">
+      <c r="A22" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D22" s="1">
         <v>2019</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-    </row>
-    <row r="21" spans="1:23" ht="63">
-      <c r="A21" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B21" s="1">
-        <v>3</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="S21" s="1"/>
-    </row>
-    <row r="22" spans="1:23" ht="78.75">
-      <c r="A22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
-      <c r="R22" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:23" ht="126">
+    <row r="23" spans="1:19" ht="63">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="B23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>255</v>
       </c>
       <c r="D23" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>57</v>
+        <v>2017</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>254</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
+      <c r="R23" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:23" s="18" customFormat="1" ht="78.75">
-      <c r="A24" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="17">
+    <row r="24" spans="1:19" s="24" customFormat="1">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="23"/>
+    </row>
+    <row r="25" spans="1:19" ht="29.25">
+      <c r="A25" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="1"/>
+    </row>
+    <row r="26" spans="1:19" ht="29.25">
+      <c r="A26" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B26" s="1">
         <v>1</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="N24" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="O24" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q24" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W24" s="20" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="6">
+      <c r="C26" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="1"/>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="1"/>
+    </row>
+    <row r="28" spans="1:19" s="24" customFormat="1">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="23"/>
+    </row>
+    <row r="29" spans="1:19" ht="47.25">
+      <c r="A29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S29" s="1"/>
+    </row>
+    <row r="30" spans="1:19" ht="47.25">
+      <c r="A30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="1">
         <v>2</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="O25" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q25" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6">
-        <v>3</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O26" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q26" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A27" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="6">
-        <v>4</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O27" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q27" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A28" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="6">
-        <v>5</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="N28" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O28" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q28" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A29" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="6">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O29" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q29" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A30" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="6">
-        <v>7</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O30" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q30" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A31" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="6">
-        <v>7</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="O31" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P31" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q31" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R31" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" s="8" customFormat="1" ht="63">
-      <c r="A32" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="6">
-        <v>8</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="N32" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="O32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q32" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+    </row>
+    <row r="31" spans="1:19" s="24" customFormat="1">
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+    </row>
+    <row r="33" spans="1:23" ht="47.25">
       <c r="A33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="6">
-        <v>9</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="O33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P33" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q33" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" s="8" customFormat="1" ht="110.25">
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="O33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="S33" s="1"/>
+    </row>
+    <row r="34" spans="1:23" ht="47.25">
       <c r="A34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="6">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="O34" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P34" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q34" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" s="8" customFormat="1" ht="110.25">
+      <c r="B34" s="1">
+        <v>2</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="O34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="S34" s="1"/>
+    </row>
+    <row r="35" spans="1:23" ht="47.25">
       <c r="A35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="6">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="O35" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P35" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q35" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" s="8" customFormat="1" ht="110.25">
+      <c r="B35" s="1">
+        <v>3</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="O35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="S35" s="1"/>
+    </row>
+    <row r="36" spans="1:23" ht="47.25">
       <c r="A36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="6">
-        <v>12</v>
+      <c r="B36" s="1">
+        <v>4</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>70</v>
+        <v>189</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="O36" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P36" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q36" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" s="8" customFormat="1" ht="63">
+        <v>186</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="O36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="S36" s="1"/>
+    </row>
+    <row r="37" spans="1:23" s="8" customFormat="1" ht="78.75">
       <c r="A37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="6">
-        <v>13</v>
+      <c r="B37" s="1">
+        <v>5</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>27</v>
+        <v>189</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="O37" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="Q37" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="W37" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A38" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="6">
-        <v>14</v>
+      <c r="B38" s="1">
+        <v>6</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="N38" s="8" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="O38" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="Q38" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="R38" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A39" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="6">
-        <v>15</v>
+      <c r="B39" s="1">
+        <v>7</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="O39" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="Q39" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="8" customFormat="1" ht="78.75">
+    <row r="40" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A40" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="6">
-        <v>16</v>
+      <c r="B40" s="1">
+        <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="N40" s="8" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="O40" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P40" s="8" t="s">
-        <v>248</v>
+        <v>202</v>
       </c>
       <c r="Q40" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="41" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A41" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="6">
-        <v>17</v>
+      <c r="B41" s="1">
+        <v>9</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>242</v>
+        <v>204</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>240</v>
+        <v>196</v>
       </c>
       <c r="O41" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="Q41" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="42" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A42" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="1">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="O42" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q42" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" s="8" customFormat="1" ht="63">
+      <c r="A43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="1">
+        <v>11</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="O43" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q43" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" s="8" customFormat="1" ht="63">
+      <c r="A44" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="1">
+        <v>12</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="N44" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="O44" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q44" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" s="8" customFormat="1" ht="63">
+      <c r="A45" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="1">
+        <v>13</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="O45" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q45" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" s="8" customFormat="1" ht="63">
+      <c r="A46" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="1">
+        <v>14</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="N46" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="O46" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q46" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" s="8" customFormat="1" ht="110.25">
+      <c r="A47" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="1">
+        <v>15</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O47" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q47" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" s="8" customFormat="1" ht="110.25">
+      <c r="A48" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="1">
+        <v>16</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="N48" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" s="8" customFormat="1" ht="110.25">
+      <c r="A49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="1">
+        <v>17</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="A50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="1">
         <v>18</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C50" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="N50" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q50" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="A51" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="1">
+        <v>19</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="O51" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q51" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="A52" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="1">
+        <v>20</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="O52" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q52" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" s="8" customFormat="1" ht="78.75">
+      <c r="A53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="1">
+        <v>21</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="N53" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="O53" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q53" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="A54" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="1">
+        <v>22</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="N54" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="O54" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q54" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="A55" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="1">
+        <v>23</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D55" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E55" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="N42" s="8" t="s">
+      <c r="N55" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="O42" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P42" s="8" t="s">
+      <c r="O55" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="Q42" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" s="8" customFormat="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" spans="1:19" ht="47.25">
-      <c r="A44" s="1" t="s">
+      <c r="Q55" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" s="24" customFormat="1">
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="E56" s="23"/>
+    </row>
+    <row r="57" spans="1:19" ht="47.25">
+      <c r="A57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B57" s="1">
         <v>1</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D57" s="1">
         <v>2014</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1" t="s">
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1" t="s">
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S44" s="1"/>
-    </row>
-    <row r="45" spans="1:19" ht="47.25">
-      <c r="A45" s="1" t="s">
+      <c r="S57" s="1"/>
+    </row>
+    <row r="58" spans="1:19" ht="47.25">
+      <c r="A58" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B58" s="1">
         <v>2</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D58" s="1">
         <v>2013</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1" t="s">
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1" t="s">
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="S45" s="1"/>
-    </row>
-    <row r="46" spans="1:19" ht="47.25">
-      <c r="A46" s="1" t="s">
+      <c r="S58" s="1"/>
+    </row>
+    <row r="59" spans="1:19" ht="47.25">
+      <c r="A59" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B59" s="1">
         <v>3</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C59" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D59" s="1">
         <v>2012</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E59" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="11" t="s">
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1" t="s">
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="S46" s="1"/>
-    </row>
-    <row r="47" spans="1:19" ht="47.25">
-      <c r="A47" s="1" t="s">
+      <c r="S59" s="1"/>
+    </row>
+    <row r="60" spans="1:19" ht="47.25">
+      <c r="A60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B60" s="1">
         <v>4</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C60" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D60" s="1">
         <v>2012</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E60" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="11" t="s">
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1" t="s">
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="S47" s="1"/>
-    </row>
-    <row r="48" spans="1:19" ht="47.25">
-      <c r="A48" s="1" t="s">
+      <c r="S60" s="1"/>
+    </row>
+    <row r="61" spans="1:19" ht="47.25">
+      <c r="A61" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B61" s="1">
         <v>5</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D61" s="1">
         <v>2010</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="11" t="s">
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1" t="s">
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S48" s="1"/>
-    </row>
-    <row r="49" spans="1:22" ht="47.25">
-      <c r="A49" s="1" t="s">
+      <c r="S61" s="1"/>
+    </row>
+    <row r="62" spans="1:19" ht="47.25">
+      <c r="A62" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B62" s="1">
         <v>6</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D62" s="1">
         <v>2010</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="11" t="s">
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1" t="s">
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S49" s="1"/>
-    </row>
-    <row r="50" spans="1:22" ht="47.25">
-      <c r="A50" s="1" t="s">
+      <c r="S62" s="1"/>
+    </row>
+    <row r="63" spans="1:19" ht="47.25">
+      <c r="A63" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B63" s="1">
         <v>7</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C63" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D63" s="1">
         <v>2010</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E63" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="11" t="s">
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1" t="s">
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S50" s="1"/>
-    </row>
-    <row r="51" spans="1:22" ht="47.25">
-      <c r="A51" s="1" t="s">
+      <c r="S63" s="1"/>
+    </row>
+    <row r="64" spans="1:19" ht="47.25">
+      <c r="A64" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B64" s="1">
         <v>8</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C64" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D64" s="1">
         <v>2010</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E64" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="11" t="s">
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1" t="s">
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="S51" s="1"/>
-    </row>
-    <row r="52" spans="1:22" ht="47.25">
-      <c r="A52" s="1" t="s">
+      <c r="S64" s="1"/>
+    </row>
+    <row r="65" spans="1:22" ht="47.25">
+      <c r="A65" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B65" s="1">
         <v>9</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C65" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D65" s="1">
         <v>2010</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E65" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="11" t="s">
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1" t="s">
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S52" s="1"/>
-    </row>
-    <row r="53" spans="1:22" ht="47.25">
-      <c r="A53" s="1" t="s">
+      <c r="S65" s="1"/>
+    </row>
+    <row r="66" spans="1:22" ht="47.25">
+      <c r="A66" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B66" s="1">
         <v>10</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D66" s="1">
         <v>2010</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E66" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="11" t="s">
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-      <c r="R53" s="1" t="s">
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S53" s="1"/>
-    </row>
-    <row r="54" spans="1:22" ht="189">
-      <c r="A54" s="1" t="s">
+      <c r="S66" s="1"/>
+    </row>
+    <row r="67" spans="1:22" ht="189">
+      <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B67" s="1">
         <v>1</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q54" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T54" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" ht="63">
-      <c r="A55" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B55" s="1">
-        <v>2</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q55" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T55" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" ht="63">
-      <c r="A56" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="1">
-        <v>3</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q56" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T56" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" ht="78.75">
-      <c r="A57" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="1">
-        <v>4</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T57" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" s="13" customFormat="1" ht="78.75">
-      <c r="A58" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B58" s="1">
-        <v>1</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58" s="13">
-        <v>2020</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S58" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="U58" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="V58" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" ht="63">
-      <c r="A59" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B59" s="1">
-        <v>2</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D59" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="S59" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U59" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" ht="63">
-      <c r="A60" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" s="1">
-        <v>3</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U60" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" ht="78.75">
-      <c r="A61" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B61" s="1">
-        <v>4</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="S61" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U61" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V61" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" ht="63">
-      <c r="A62" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B62" s="1">
-        <v>5</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2">
-        <v>2016</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="S62" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="U62" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" ht="63">
-      <c r="A63" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B63" s="1">
-        <v>6</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2">
-        <v>2015</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="S63" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="U63" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" ht="78.75">
-      <c r="A64" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D64" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R64" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S64" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="V64" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" ht="78.75">
-      <c r="A65" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B65" s="1">
-        <v>2</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D65" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="R65" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U65" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" ht="94.5">
-      <c r="A66" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B66" s="1">
-        <v>1</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="R66" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S66" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22">
-      <c r="A67" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B67" s="1">
-        <v>2</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" ht="63">
+      <c r="A68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q68" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="63">
+      <c r="A69" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B69" s="1">
+        <v>3</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="78.75">
+      <c r="A70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B70" s="1">
+        <v>4</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q70" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" s="13" customFormat="1" ht="78.75">
+      <c r="A71" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D71" s="13">
+        <v>2020</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="S71" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="U71" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="V71" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" ht="63">
+      <c r="A72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D72" s="2">
         <v>2019</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E72" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="U72" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" ht="63">
+      <c r="A73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" s="1">
+        <v>3</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="U73" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" ht="78.75">
+      <c r="A74" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="1">
+        <v>4</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" ht="63">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1">
+        <v>5</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2016</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U75" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" ht="63">
+      <c r="A76" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="1">
+        <v>6</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2">
+        <v>2015</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U76" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" ht="78.75">
+      <c r="A77" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U77" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="78.75">
+      <c r="A78" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D78" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R78" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U78" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="94.5">
+      <c r="A79" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="R79" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22">
+      <c r="A80" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E80" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="R67" s="2" t="s">
+      <c r="R80" s="2" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:K14">
-    <sortCondition ref="B4:B14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:K15">
+    <sortCondition ref="B5:B15"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J22" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
-    <hyperlink ref="K2" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
-    <hyperlink ref="K3" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
-    <hyperlink ref="K4" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
-    <hyperlink ref="K5" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
-    <hyperlink ref="K6" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
-    <hyperlink ref="K7" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
-    <hyperlink ref="K8" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
-    <hyperlink ref="K9" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
-    <hyperlink ref="K10" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
-    <hyperlink ref="K12" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
-    <hyperlink ref="K11" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
-    <hyperlink ref="R19" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
-    <hyperlink ref="S19" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
-    <hyperlink ref="K20" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
-    <hyperlink ref="R21" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W24" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R36" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R35" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R34" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R31" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R25" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="J29" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
+    <hyperlink ref="K5" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
+    <hyperlink ref="K6" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
+    <hyperlink ref="K8" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
+    <hyperlink ref="K9" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
+    <hyperlink ref="K10" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
+    <hyperlink ref="K11" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
+    <hyperlink ref="K13" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
+    <hyperlink ref="K12" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
+    <hyperlink ref="R21" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
+    <hyperlink ref="S21" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
+    <hyperlink ref="K22" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
+    <hyperlink ref="R23" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
+    <hyperlink ref="W37" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R49" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R48" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R47" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R44" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R38" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="K2" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
+    <hyperlink ref="J2" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
+    <hyperlink ref="R33" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
+    <hyperlink ref="R35" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
+    <hyperlink ref="R36" r:id="rId27" xr:uid="{07D0EF3C-F66D-4CB6-B546-064E64E53AAA}"/>
+    <hyperlink ref="R34" r:id="rId28" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId23"/>
+  <pageSetup orientation="portrait" r:id="rId29"/>
 </worksheet>
 </file>
--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1CB808-E596-449C-912D-97A10025BE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54917CDB-9F5D-4AA5-A4BC-ADCDD8129E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="306">
   <si>
     <t>authors</t>
   </si>
@@ -918,9 +918,6 @@
     <t>https://agu.confex.com/agu/fm21/meetingapp.cgi/Paper/832202</t>
   </si>
   <si>
-    <t>https://agu.confex.com/agu/fm21/meetingapp.cgi/Paper/830768</t>
-  </si>
-  <si>
     <t>Reproducible Parameter Estimation Framework for Integrated Hydrological Models as Evidenced in the Colorado River Basin</t>
   </si>
   <si>
@@ -952,6 +949,9 @@
   </si>
   <si>
     <t>Park, S., Baker, T., Srinivasan, R. and Jeong, J.</t>
+  </si>
+  <si>
+    <t>A new model for simulating surface-subsurface hydrological processes at the watershed scale</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -1466,7 +1466,8 @@
     <col min="11" max="11" width="35.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="26.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="26" style="2" customWidth="1"/>
-    <col min="14" max="17" width="11" style="2"/>
+    <col min="14" max="14" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="11" style="2"/>
     <col min="18" max="18" width="74" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="33.5" style="2" customWidth="1"/>
     <col min="20" max="16384" width="11" style="2"/>
@@ -2356,19 +2357,19 @@
     </row>
     <row r="25" spans="1:19" ht="29.25">
       <c r="A25" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D25" s="1">
         <v>2021</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2378,7 +2379,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -2389,19 +2390,19 @@
     </row>
     <row r="26" spans="1:19" ht="29.25">
       <c r="A26" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D26" s="1">
         <v>2022</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -2411,7 +2412,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -2631,13 +2632,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>287</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -2648,7 +2649,7 @@
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O34" s="1" t="b">
         <v>1</v>
@@ -2660,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="S34" s="1"/>
     </row>
@@ -2705,7 +2706,7 @@
       </c>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:23" ht="47.25">
+    <row r="36" spans="1:23" s="8" customFormat="1" ht="78.75">
       <c r="A36" s="6" t="s">
         <v>22</v>
       </c>
@@ -2721,32 +2722,23 @@
       <c r="E36" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="O36" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q36" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="S36" s="1"/>
-    </row>
-    <row r="37" spans="1:23" s="8" customFormat="1" ht="78.75">
+      <c r="N36" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="O36" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q36" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A37" s="6" t="s">
         <v>22</v>
       </c>
@@ -2754,28 +2746,28 @@
         <v>5</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="O37" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q37" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="W37" s="7" t="s">
-        <v>265</v>
+      <c r="R37" s="7" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="38" spans="1:23" s="8" customFormat="1" ht="63">
@@ -2786,28 +2778,25 @@
         <v>6</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N38" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="O38" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="Q38" s="8" t="b">
         <v>0</v>
-      </c>
-      <c r="R38" s="7" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="39" spans="1:23" s="8" customFormat="1" ht="63">
@@ -2818,13 +2807,13 @@
         <v>7</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N39" s="8" t="s">
         <v>196</v>
@@ -2847,13 +2836,13 @@
         <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N40" s="8" t="s">
         <v>196</v>
@@ -2876,13 +2865,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N41" s="8" t="s">
         <v>196</v>
@@ -2905,13 +2894,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N42" s="8" t="s">
         <v>196</v>
@@ -2934,25 +2923,28 @@
         <v>11</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="O43" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P43" s="8" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="Q43" s="8" t="b">
         <v>0</v>
+      </c>
+      <c r="R43" s="7" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:23" s="8" customFormat="1" ht="63">
@@ -2963,28 +2955,25 @@
         <v>12</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N44" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O44" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P44" s="8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q44" s="8" t="b">
         <v>0</v>
-      </c>
-      <c r="R44" s="7" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="45" spans="1:23" s="8" customFormat="1" ht="63">
@@ -2995,13 +2984,13 @@
         <v>13</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>66</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N45" s="8" t="s">
         <v>215</v>
@@ -3016,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:23" s="8" customFormat="1" ht="63">
+    <row r="46" spans="1:23" s="8" customFormat="1" ht="110.25">
       <c r="A46" s="6" t="s">
         <v>22</v>
       </c>
@@ -3024,28 +3013,31 @@
         <v>14</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="O46" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P46" s="8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Q46" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" s="8" customFormat="1" ht="110.25">
+      <c r="R46" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" s="8" customFormat="1" ht="78.75">
       <c r="A47" s="6" t="s">
         <v>22</v>
       </c>
@@ -3053,13 +3045,13 @@
         <v>15</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="N47" s="8" t="s">
         <v>221</v>
@@ -3074,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="R47" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:23" s="8" customFormat="1" ht="110.25">
@@ -3085,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>70</v>
@@ -3106,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="R48" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" s="8" customFormat="1" ht="110.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" s="8" customFormat="1" ht="63">
       <c r="A49" s="6" t="s">
         <v>22</v>
       </c>
@@ -3117,31 +3109,28 @@
         <v>17</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="O49" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P49" s="8" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="Q49" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="R49" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" s="8" customFormat="1" ht="63">
+    </row>
+    <row r="50" spans="1:19" s="8" customFormat="1" ht="47.25">
       <c r="A50" s="6" t="s">
         <v>22</v>
       </c>
@@ -3149,22 +3138,22 @@
         <v>18</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N50" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="O50" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P50" s="8" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="Q50" s="8" t="b">
         <v>0</v>
@@ -3178,28 +3167,28 @@
         <v>19</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="O51" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P51" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q51" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="8" customFormat="1" ht="47.25">
+    <row r="52" spans="1:19" s="8" customFormat="1" ht="78.75">
       <c r="A52" s="6" t="s">
         <v>22</v>
       </c>
@@ -3207,28 +3196,28 @@
         <v>20</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="N52" s="8" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="O52" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P52" s="8" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="Q52" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="8" customFormat="1" ht="78.75">
+    <row r="53" spans="1:19" s="8" customFormat="1" ht="63">
       <c r="A53" s="6" t="s">
         <v>22</v>
       </c>
@@ -3236,22 +3225,22 @@
         <v>21</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="O53" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P53" s="8" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="Q53" s="8" t="b">
         <v>0</v>
@@ -3265,13 +3254,13 @@
         <v>22</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>243</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N54" s="8" t="s">
         <v>240</v>
@@ -3286,56 +3275,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="8" customFormat="1" ht="63">
-      <c r="A55" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B55" s="1">
-        <v>23</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="O55" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P55" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q55" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" s="24" customFormat="1">
-      <c r="A56" s="23"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="E56" s="23"/>
+    <row r="55" spans="1:19" s="24" customFormat="1">
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="E55" s="23"/>
+    </row>
+    <row r="56" spans="1:19" ht="47.25">
+      <c r="A56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S56" s="1"/>
     </row>
     <row r="57" spans="1:19" ht="47.25">
       <c r="A57" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="D57" s="1">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -3345,14 +3340,14 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S57" s="1"/>
     </row>
@@ -3361,16 +3356,16 @@
         <v>32</v>
       </c>
       <c r="B58" s="1">
-        <v>2</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="D58" s="1">
-        <v>2013</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>37</v>
+        <v>2012</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -3379,15 +3374,15 @@
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
-      <c r="M58" s="1" t="s">
-        <v>36</v>
+      <c r="M58" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="S58" s="1"/>
     </row>
@@ -3396,16 +3391,16 @@
         <v>32</v>
       </c>
       <c r="B59" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D59" s="1">
         <v>2012</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -3422,7 +3417,7 @@
       <c r="P59" s="1"/>
       <c r="Q59" s="1"/>
       <c r="R59" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S59" s="1"/>
     </row>
@@ -3431,16 +3426,16 @@
         <v>32</v>
       </c>
       <c r="B60" s="1">
-        <v>4</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>52</v>
+        <v>5</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="D60" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>59</v>
+        <v>2010</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -3457,7 +3452,7 @@
       <c r="P60" s="1"/>
       <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="S60" s="1"/>
     </row>
@@ -3466,16 +3461,16 @@
         <v>32</v>
       </c>
       <c r="B61" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D61" s="1">
         <v>2010</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -3492,7 +3487,7 @@
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="S61" s="1"/>
     </row>
@@ -3501,16 +3496,16 @@
         <v>32</v>
       </c>
       <c r="B62" s="1">
-        <v>6</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>56</v>
+        <v>7</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="D62" s="1">
         <v>2010</v>
       </c>
-      <c r="E62" s="11" t="s">
-        <v>60</v>
+      <c r="E62" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -3527,7 +3522,7 @@
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
       <c r="R62" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S62" s="1"/>
     </row>
@@ -3536,16 +3531,16 @@
         <v>32</v>
       </c>
       <c r="B63" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D63" s="1">
         <v>2010</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -3562,7 +3557,7 @@
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S63" s="1"/>
     </row>
@@ -3571,16 +3566,16 @@
         <v>32</v>
       </c>
       <c r="B64" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D64" s="1">
         <v>2010</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -3597,7 +3592,7 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S64" s="1"/>
     </row>
@@ -3606,16 +3601,16 @@
         <v>32</v>
       </c>
       <c r="B65" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D65" s="1">
         <v>2010</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -3632,72 +3627,66 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S65" s="1"/>
     </row>
-    <row r="66" spans="1:22" ht="47.25">
+    <row r="66" spans="1:22" ht="189">
       <c r="A66" s="1" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D66" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="R66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S66" s="1"/>
-    </row>
-    <row r="67" spans="1:22" ht="189">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="63">
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="Q67" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:22" ht="63">
@@ -3705,143 +3694,137 @@
         <v>65</v>
       </c>
       <c r="B68" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="Q68" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" ht="63">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="78.75">
       <c r="A69" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="Q69" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" ht="78.75">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" s="13" customFormat="1" ht="78.75">
       <c r="A70" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B70" s="1">
-        <v>4</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D70" s="13">
+        <v>2020</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="N70" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P70" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q70" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T70" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" s="13" customFormat="1" ht="78.75">
+        <v>84</v>
+      </c>
+      <c r="S70" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="U70" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="V70" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" ht="31.5">
       <c r="A71" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B71" s="1">
-        <v>1</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D71" s="13">
-        <v>2020</v>
+        <v>2</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2019</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S71" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="U71" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="V71" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" ht="63">
+        <v>119</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" ht="31.5">
       <c r="A72" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B72" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="D72" s="2">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U72" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" ht="63">
+        <v>88</v>
+      </c>
+      <c r="U72" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" ht="78.75">
       <c r="A73" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B73" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>8</v>
@@ -3850,85 +3833,91 @@
         <v>2018</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" ht="78.75">
+        <v>92</v>
+      </c>
+      <c r="U73" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22">
       <c r="A74" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B74" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="2">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U74" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V74" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" ht="63">
+        <v>96</v>
+      </c>
+      <c r="U74" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" ht="31.5">
       <c r="A75" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B75" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="U75" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="63">
+    <row r="76" spans="1:22" ht="78.75">
       <c r="A76" s="1" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B76" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D76" s="2">
-        <v>2015</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>97</v>
+        <v>2018</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>86</v>
+        <v>103</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:22" ht="78.75">
@@ -3936,65 +3925,59 @@
         <v>99</v>
       </c>
       <c r="B77" s="1">
-        <v>1</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>100</v>
+        <v>2</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="D77" s="2">
         <v>2018</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>101</v>
+      <c r="E77" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="V77" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" ht="78.75">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="31.5">
       <c r="A78" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B78" s="1">
-        <v>2</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>8</v>
       </c>
       <c r="D78" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U78" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" ht="94.5">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22">
       <c r="A79" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B79" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>8</v>
@@ -4002,33 +3985,10 @@
       <c r="D79" s="2">
         <v>2019</v>
       </c>
-      <c r="E79" s="12" t="s">
-        <v>111</v>
+      <c r="E79" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22">
-      <c r="A80" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B80" s="1">
-        <v>2</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E80" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="R80" s="2" t="s">
         <v>115</v>
       </c>
     </row>
@@ -4054,20 +4014,19 @@
     <hyperlink ref="S21" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
     <hyperlink ref="K22" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
     <hyperlink ref="R23" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W37" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R49" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R48" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R47" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R44" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R38" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="W36" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R48" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R47" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R46" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R43" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R37" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
     <hyperlink ref="K2" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
     <hyperlink ref="J2" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
     <hyperlink ref="R33" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
     <hyperlink ref="R35" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
-    <hyperlink ref="R36" r:id="rId27" xr:uid="{07D0EF3C-F66D-4CB6-B546-064E64E53AAA}"/>
-    <hyperlink ref="R34" r:id="rId28" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="R34" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId29"/>
+  <pageSetup orientation="portrait" r:id="rId28"/>
 </worksheet>
 </file>
--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54917CDB-9F5D-4AA5-A4BC-ADCDD8129E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E20379-DC20-4D22-9641-B61186D72D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="3165" yWindow="2295" windowWidth="25050" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="308">
   <si>
     <t>authors</t>
   </si>
@@ -952,6 +952,12 @@
   </si>
   <si>
     <t>A new model for simulating surface-subsurface hydrological processes at the watershed scale</t>
+  </si>
+  <si>
+    <t>Quantifying the impact of climate change and irrigation management on groundwater in an arid region with intensive groundwater abstraction</t>
+  </si>
+  <si>
+    <t>Saadatpour, A., Bailey, R., Izady, A., Amin, Ziaei, A. and Park, S.</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -2074,57 +2080,57 @@
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
     </row>
-    <row r="16" spans="1:23" ht="47.25">
+    <row r="16" spans="1:23" s="8" customFormat="1" ht="31.5">
       <c r="A16" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="6">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>283</v>
+      <c r="C16" s="6" t="s">
+        <v>307</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="1:19" ht="31.5">
+      <c r="E16" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+    </row>
+    <row r="17" spans="1:19" ht="47.25">
       <c r="A17" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="6">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -2140,24 +2146,24 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" ht="63">
+    <row r="18" spans="1:19" ht="31.5">
       <c r="A18" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="6">
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -2173,24 +2179,24 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" ht="47.25">
+    <row r="19" spans="1:19" ht="63">
       <c r="A19" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="6">
         <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -2206,92 +2212,68 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" s="24" customFormat="1">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-    </row>
-    <row r="21" spans="1:19" s="8" customFormat="1" ht="47.25">
-      <c r="A21" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B21" s="6">
-        <v>1</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D21" s="6">
-        <v>2019</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="63">
-      <c r="A22" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="F22" s="1"/>
+    <row r="20" spans="1:19" ht="47.25">
+      <c r="A20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="6">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+    </row>
+    <row r="22" spans="1:19">
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="3" t="s">
-        <v>262</v>
-      </c>
+      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="1" t="s">
-        <v>259</v>
-      </c>
+      <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -2299,110 +2281,114 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" ht="63">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:19" s="24" customFormat="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+    </row>
+    <row r="24" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="A24" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B23" s="1">
-        <v>3</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="S23" s="1"/>
-    </row>
-    <row r="24" spans="1:19" s="24" customFormat="1">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="23"/>
-    </row>
-    <row r="25" spans="1:19" ht="29.25">
+      <c r="B24" s="6">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D24" s="6">
+        <v>2019</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="S24" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="63">
       <c r="A25" s="1" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
       <c r="D25" s="1">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>301</v>
+        <v>253</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="K25" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-      <c r="R25" s="3"/>
+      <c r="R25" s="1"/>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19" ht="29.25">
+    <row r="26" spans="1:19" ht="63">
       <c r="A26" s="1" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="D26" s="1">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>302</v>
+        <v>254</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -2412,133 +2398,123 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-      <c r="R26" s="3"/>
+      <c r="R26" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="1"/>
-    </row>
-    <row r="28" spans="1:19" s="24" customFormat="1">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="23"/>
-    </row>
-    <row r="29" spans="1:19" ht="47.25">
+    <row r="27" spans="1:19" s="24" customFormat="1">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="23"/>
+    </row>
+    <row r="28" spans="1:19" ht="29.25">
+      <c r="A28" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="1"/>
+    </row>
+    <row r="29" spans="1:19" ht="29.25">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>298</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>304</v>
       </c>
       <c r="D29" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>2022</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>302</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
-        <v>17</v>
+        <v>303</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-      <c r="R29" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="R29" s="3"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19" ht="47.25">
-      <c r="A30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>57</v>
-      </c>
+    <row r="30" spans="1:19">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="9"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
+      <c r="R30" s="3"/>
       <c r="S30" s="1"/>
     </row>
     <row r="31" spans="1:19" s="24" customFormat="1">
@@ -2546,7 +2522,7 @@
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="E31" s="26"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
@@ -2559,128 +2535,114 @@
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
       <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
+      <c r="R31" s="27"/>
       <c r="S31" s="23"/>
     </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+    <row r="32" spans="1:19" ht="47.25">
+      <c r="A32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
+      <c r="J32" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
+      <c r="R32" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="S32" s="1"/>
     </row>
     <row r="33" spans="1:23" ht="47.25">
-      <c r="A33" s="6" t="s">
-        <v>22</v>
+      <c r="A33" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>287</v>
+        <v>29</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2011</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>276</v>
+        <v>57</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="O33" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q33" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>289</v>
-      </c>
+      <c r="L33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:23" ht="47.25">
-      <c r="A34" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="1">
-        <v>2</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="O34" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q34" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="S34" s="1"/>
-    </row>
-    <row r="35" spans="1:23" ht="47.25">
-      <c r="A35" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="1">
-        <v>3</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>291</v>
-      </c>
+    <row r="34" spans="1:23" s="24" customFormat="1">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
+      <c r="M34" s="23"/>
+      <c r="N34" s="23"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="23"/>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2689,143 +2651,166 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="N35" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="O35" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q35" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>293</v>
-      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:23" s="8" customFormat="1" ht="78.75">
+    <row r="36" spans="1:23" ht="47.25">
       <c r="A36" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="1">
-        <v>4</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="O36" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P36" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q36" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W36" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" s="8" customFormat="1" ht="63">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="O36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="S36" s="1"/>
+    </row>
+    <row r="37" spans="1:23" ht="47.25">
       <c r="A37" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B37" s="1">
-        <v>5</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N37" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="O37" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q37" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" s="8" customFormat="1" ht="63">
+        <v>2</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="O37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="S37" s="1"/>
+    </row>
+    <row r="38" spans="1:23" ht="47.25">
       <c r="A38" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B38" s="1">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N38" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O38" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q38" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" s="8" customFormat="1" ht="63">
+        <v>3</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="O38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q38" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="S38" s="1"/>
+    </row>
+    <row r="39" spans="1:23" s="8" customFormat="1" ht="78.75">
       <c r="A39" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O39" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="Q39" s="8" t="b">
         <v>0</v>
+      </c>
+      <c r="W39" s="7" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="40" spans="1:23" s="8" customFormat="1" ht="63">
@@ -2833,45 +2818,48 @@
         <v>22</v>
       </c>
       <c r="B40" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="N40" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O40" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P40" s="8" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Q40" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" s="8" customFormat="1" ht="63">
+      <c r="R40" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" s="8" customFormat="1" ht="31.5">
       <c r="A41" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="N41" s="8" t="s">
         <v>196</v>
@@ -2886,21 +2874,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:23" s="8" customFormat="1" ht="63">
+    <row r="42" spans="1:23" s="8" customFormat="1" ht="31.5">
       <c r="A42" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B42" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>198</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N42" s="8" t="s">
         <v>196</v>
@@ -2915,492 +2903,474 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:23" s="8" customFormat="1" ht="63">
+    <row r="43" spans="1:23" s="8" customFormat="1" ht="31.5">
       <c r="A43" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="O43" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P43" s="8" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="Q43" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="R43" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" s="8" customFormat="1" ht="63">
+    </row>
+    <row r="44" spans="1:23" s="8" customFormat="1" ht="31.5">
       <c r="A44" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="N44" s="8" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="O44" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P44" s="8" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="Q44" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:23" s="8" customFormat="1" ht="63">
+    <row r="45" spans="1:23" s="8" customFormat="1" ht="31.5">
       <c r="A45" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="O45" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P45" s="8" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="Q45" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:23" s="8" customFormat="1" ht="110.25">
+    <row r="46" spans="1:23" s="8" customFormat="1" ht="63">
       <c r="A46" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="O46" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P46" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="Q46" s="8" t="b">
         <v>0</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" s="8" customFormat="1" ht="78.75">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" s="8" customFormat="1" ht="31.5">
       <c r="A47" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>305</v>
+        <v>214</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O47" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P47" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q47" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="R47" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" s="8" customFormat="1" ht="110.25">
+    </row>
+    <row r="48" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A48" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B48" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="N48" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O48" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P48" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q48" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="R48" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" s="8" customFormat="1" ht="63">
+    </row>
+    <row r="49" spans="1:19" s="8" customFormat="1" ht="78.75">
       <c r="A49" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B49" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="O49" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P49" s="8" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="Q49" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="R49" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" s="8" customFormat="1" ht="78.75">
       <c r="A50" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B50" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="N50" s="8" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="O50" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P50" s="8" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="Q50" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="R50" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" s="8" customFormat="1" ht="78.75">
       <c r="A51" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>237</v>
+        <v>70</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="O51" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P51" s="8" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="Q51" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" s="8" customFormat="1" ht="78.75">
+      <c r="R51" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" s="8" customFormat="1" ht="31.5">
       <c r="A52" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="N52" s="8" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="O52" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P52" s="8" t="s">
-        <v>248</v>
+        <v>202</v>
       </c>
       <c r="Q52" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="53" spans="1:19" s="8" customFormat="1" ht="47.25">
       <c r="A53" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O53" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P53" s="8" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="Q53" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="54" spans="1:19" s="8" customFormat="1" ht="47.25">
       <c r="A54" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="1">
+        <v>19</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="N54" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="O54" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q54" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" s="8" customFormat="1" ht="63">
+      <c r="A55" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="B55" s="1">
+        <v>20</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="O55" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q55" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="A56" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="1">
+        <v>21</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="N56" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="O56" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q56" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" s="8" customFormat="1" ht="31.5">
+      <c r="A57" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="1">
+        <v>22</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D57" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E57" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="N54" s="8" t="s">
+      <c r="N57" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="O54" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P54" s="8" t="s">
+      <c r="O57" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="Q54" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" s="24" customFormat="1">
-      <c r="A55" s="23"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="E55" s="23"/>
-    </row>
-    <row r="56" spans="1:19" ht="47.25">
-      <c r="A56" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B56" s="1">
-        <v>1</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D56" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S56" s="1"/>
-    </row>
-    <row r="57" spans="1:19" ht="47.25">
-      <c r="A57" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B57" s="1">
-        <v>2</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="1">
-        <v>2013</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S57" s="1"/>
-    </row>
-    <row r="58" spans="1:19" ht="47.25">
-      <c r="A58" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B58" s="1">
-        <v>3</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S58" s="1"/>
+      <c r="Q57" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" s="24" customFormat="1">
+      <c r="A58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="E58" s="23"/>
     </row>
     <row r="59" spans="1:19" ht="47.25">
       <c r="A59" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B59" s="1">
-        <v>4</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D59" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>59</v>
+        <v>2014</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -3409,7 +3379,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="11" t="s">
+      <c r="M59" s="1" t="s">
         <v>38</v>
       </c>
       <c r="N59" s="1"/>
@@ -3417,7 +3387,7 @@
       <c r="P59" s="1"/>
       <c r="Q59" s="1"/>
       <c r="R59" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="S59" s="1"/>
     </row>
@@ -3426,16 +3396,16 @@
         <v>32</v>
       </c>
       <c r="B60" s="1">
-        <v>5</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D60" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>40</v>
+        <v>2013</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -3444,15 +3414,15 @@
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
-      <c r="M60" s="11" t="s">
-        <v>38</v>
+      <c r="M60" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
       <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S60" s="1"/>
     </row>
@@ -3461,16 +3431,16 @@
         <v>32</v>
       </c>
       <c r="B61" s="1">
-        <v>6</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>56</v>
+        <v>3</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="D61" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>60</v>
+        <v>2012</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -3487,7 +3457,7 @@
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="S61" s="1"/>
     </row>
@@ -3496,16 +3466,16 @@
         <v>32</v>
       </c>
       <c r="B62" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D62" s="1">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -3522,7 +3492,7 @@
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
       <c r="R62" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="S62" s="1"/>
     </row>
@@ -3531,16 +3501,16 @@
         <v>32</v>
       </c>
       <c r="B63" s="1">
-        <v>8</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>44</v>
+        <v>5</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="D63" s="1">
         <v>2010</v>
       </c>
-      <c r="E63" s="10" t="s">
-        <v>62</v>
+      <c r="E63" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -3557,7 +3527,7 @@
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="S63" s="1"/>
     </row>
@@ -3566,16 +3536,16 @@
         <v>32</v>
       </c>
       <c r="B64" s="1">
-        <v>9</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>46</v>
+        <v>6</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="D64" s="1">
         <v>2010</v>
       </c>
-      <c r="E64" s="10" t="s">
-        <v>63</v>
+      <c r="E64" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -3592,7 +3562,7 @@
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="S64" s="1"/>
     </row>
@@ -3601,16 +3571,16 @@
         <v>32</v>
       </c>
       <c r="B65" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D65" s="1">
         <v>2010</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -3627,245 +3597,278 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S65" s="1"/>
+    </row>
+    <row r="66" spans="1:22" ht="47.25">
+      <c r="A66" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B66" s="1">
+        <v>8</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S66" s="1"/>
+    </row>
+    <row r="67" spans="1:22" ht="47.25">
+      <c r="A67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" s="1">
+        <v>9</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S67" s="1"/>
+    </row>
+    <row r="68" spans="1:22" ht="47.25">
+      <c r="A68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B68" s="1">
+        <v>10</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S65" s="1"/>
-    </row>
-    <row r="66" spans="1:22" ht="189">
-      <c r="A66" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1">
-        <v>1</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q66" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T66" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" ht="63">
-      <c r="A67" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="1">
-        <v>2</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="N67" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P67" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q67" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T67" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" ht="63">
-      <c r="A68" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="1">
-        <v>3</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q68" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" ht="78.75">
+      <c r="S68" s="1"/>
+    </row>
+    <row r="69" spans="1:22" ht="110.25">
       <c r="A69" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B69" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N69" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="63">
+      <c r="A70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="N70" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="P69" s="2" t="s">
+      <c r="P70" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q69" s="2" t="b">
+      <c r="Q70" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T69" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" s="13" customFormat="1" ht="78.75">
-      <c r="A70" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B70" s="1">
-        <v>1</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D70" s="13">
-        <v>2020</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S70" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="U70" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="V70" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" ht="31.5">
+      <c r="T70" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" ht="63">
       <c r="A71" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B71" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D71" s="2">
-        <v>2019</v>
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="S71" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U71" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" ht="31.5">
+        <v>76</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" ht="78.75">
       <c r="A72" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B72" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D72" s="2">
-        <v>2018</v>
+      <c r="D72" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="S72" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U72" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" ht="78.75">
+        <v>80</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q72" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" s="13" customFormat="1" ht="78.75">
       <c r="A73" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B73" s="1">
-        <v>4</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2">
-        <v>2018</v>
+        <v>1</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D73" s="13">
+        <v>2020</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="S73" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U73" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V73" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22">
+        <v>84</v>
+      </c>
+      <c r="S73" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="U73" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="V73" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" ht="31.5">
       <c r="A74" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B74" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D74" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="U74" s="12" t="s">
-        <v>86</v>
+        <v>120</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="31.5">
@@ -3873,19 +3876,19 @@
         <v>83</v>
       </c>
       <c r="B75" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="2">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="U75" s="12" t="s">
         <v>86</v>
@@ -3893,102 +3896,174 @@
     </row>
     <row r="76" spans="1:22" ht="78.75">
       <c r="A76" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B76" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D76" s="2">
         <v>2018</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R76" s="2" t="s">
-        <v>116</v>
+      <c r="E76" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U76" s="12" t="s">
-        <v>103</v>
+        <v>92</v>
+      </c>
+      <c r="U76" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="V76" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" ht="78.75">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22">
       <c r="A77" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B77" s="1">
-        <v>2</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>105</v>
+        <v>5</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>8</v>
       </c>
       <c r="D77" s="2">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="R77" s="2" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="V77" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:22" ht="31.5">
       <c r="A78" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="B78" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="2">
+        <v>2015</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U78" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="78.75">
+      <c r="A79" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R79" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U79" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="V79" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="78.75">
+      <c r="A80" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D80" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U80" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="31.5">
+      <c r="A81" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" s="1">
+        <v>1</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2">
         <v>2019</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E81" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="R78" s="2" t="s">
+      <c r="R81" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S78" s="2" t="s">
+      <c r="S81" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
-      <c r="A79" s="1" t="s">
+    <row r="82" spans="1:19">
+      <c r="A82" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B82" s="1">
         <v>2</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C82" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D82" s="2">
         <v>2019</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E82" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="R79" s="2" t="s">
+      <c r="R82" s="2" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3998,7 +4073,7 @@
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J29" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
+    <hyperlink ref="J32" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
     <hyperlink ref="K3" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
     <hyperlink ref="K4" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
     <hyperlink ref="K5" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
@@ -4010,21 +4085,21 @@
     <hyperlink ref="K11" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
     <hyperlink ref="K13" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
     <hyperlink ref="K12" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
-    <hyperlink ref="R21" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
-    <hyperlink ref="S21" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
-    <hyperlink ref="K22" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
-    <hyperlink ref="R23" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W36" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R48" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R47" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R46" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R43" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R37" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="R24" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
+    <hyperlink ref="S24" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
+    <hyperlink ref="K25" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
+    <hyperlink ref="R26" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
+    <hyperlink ref="W39" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R51" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R50" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R49" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R46" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R40" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
     <hyperlink ref="K2" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
     <hyperlink ref="J2" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
-    <hyperlink ref="R33" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
-    <hyperlink ref="R35" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
-    <hyperlink ref="R34" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="R36" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
+    <hyperlink ref="R38" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
+    <hyperlink ref="R37" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId28"/>

--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E20379-DC20-4D22-9641-B61186D72D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE5F44A-4AB0-439C-9F40-683B714677CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3165" yWindow="2295" windowWidth="25050" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="38700" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="326">
   <si>
     <t>authors</t>
   </si>
@@ -852,15 +852,9 @@
     <t>Bailey, R.T., Jeong, J., Park, S. and Green, C.H.</t>
   </si>
   <si>
-    <t>Simulating Salinity Transport in High-Desert Landscapes using APEX-MODFLOW-Salt</t>
-  </si>
-  <si>
     <t>Journal of Hydrology</t>
   </si>
   <si>
-    <t>Development of a Field Scale, SWAT+ Modeling Framework for the Contiguous US</t>
-  </si>
-  <si>
     <t>Journal of the American Water Resources Association</t>
   </si>
   <si>
@@ -870,9 +864,6 @@
     <t>Water Resources Research</t>
   </si>
   <si>
-    <t>Michael White, Jeff Arnold, Katrin Bieger, Peter Allen, Jungang Gao, Natalja Cerkasova, Mauro DiLuzio, Marilyn Gambone, Park, S., David D. Bosch, Haw Yen</t>
-  </si>
-  <si>
     <t>Assessment of snowmelt and groundwater-surface water dynamics in mountainous, foothill, and plain regions in northern latitudes</t>
   </si>
   <si>
@@ -924,9 +915,6 @@
     <t>Park, S., Abitew, TA., Jeong, J., Han, H., and Green, C.</t>
   </si>
   <si>
-    <t>AGU Fall Meeting 2022</t>
-  </si>
-  <si>
     <t>https://agu.confex.com/agu/fm21/meetingapp.cgi/Paper/845898</t>
   </si>
   <si>
@@ -958,13 +946,79 @@
   </si>
   <si>
     <t>Saadatpour, A., Bailey, R., Izady, A., Amin, Ziaei, A. and Park, S.</t>
+  </si>
+  <si>
+    <t>Simulating salinity transport in High-Desert landscapes using APEX-MODFLOW-Salt</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jhydrol.2022.127873</t>
+  </si>
+  <si>
+    <t>10.1016/j.jhydrol.2022.127873</t>
+  </si>
+  <si>
+    <t>Climate Change Impacts on Water Balance and Groundwater/Surface Water Interactions in the Colorado River Basin</t>
+  </si>
+  <si>
+    <t>2022 World Environmental &amp; Water Resources Congress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atlanta, GA, United States </t>
+  </si>
+  <si>
+    <t>June, 2022</t>
+  </si>
+  <si>
+    <t>Park, S., Han, H., Abitew, TA., Jeong, J., and Green, C.</t>
+  </si>
+  <si>
+    <t>Assessment of Spatial and Temporal Variability of Water Resources and Fluxes in the Okavango Basin</t>
+  </si>
+  <si>
+    <t>July, 2022</t>
+  </si>
+  <si>
+    <t>Jeong, J. and Park, S.</t>
+  </si>
+  <si>
+    <t>2022 International SWAT Conference</t>
+  </si>
+  <si>
+    <t>Prague, Czechoslovakia</t>
+  </si>
+  <si>
+    <t>White, M.J., Arnold, J.G., Bieger, K., Allen, P.M., Gao, J., Cerkasova, N., Gambone, M., Park, S., Bosch, D.D., Yen, H. and Osorio, J.M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Development of a Field Scale SWAT+ Modeling Framework for the Contiguous US</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/1752-1688.13056</t>
+  </si>
+  <si>
+    <t>10.1111/1752-1688.13056</t>
+  </si>
+  <si>
+    <t>Latest Advances and Applications of SWAT-MODFLOW</t>
+  </si>
+  <si>
+    <t>Korea Institute of Civil Engineering and Building Technology No. 22-01.</t>
+  </si>
+  <si>
+    <t>Park, S.</t>
+  </si>
+  <si>
+    <t>QSWATMOD: Advances and Applications</t>
+  </si>
+  <si>
+    <t>Korea Institute of Civil Engineering and Building Technology No. 22-02.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1025,8 +1079,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="Times Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1045,6 +1111,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1059,7 +1131,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1140,6 +1212,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1457,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W82"/>
+  <dimension ref="A1:W88"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -1473,7 +1557,9 @@
     <col min="12" max="12" width="26.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="26" style="2" customWidth="1"/>
     <col min="14" max="14" width="15.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="11" style="2"/>
+    <col min="15" max="15" width="11" style="2"/>
+    <col min="16" max="16" width="23.5" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11" style="2"/>
     <col min="18" max="18" width="74" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="33.5" style="2" customWidth="1"/>
     <col min="20" max="16384" width="11" style="2"/>
@@ -1550,7 +1636,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="47.25">
+    <row r="2" spans="1:23" ht="63">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1558,27 +1644,27 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="D2" s="1">
         <v>2022</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="1">
-        <v>127449</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>282</v>
+      <c r="G2" s="1">
+        <v>146</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1600,28 +1686,27 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="D3" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>128</v>
+        <v>304</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>129</v>
+        <v>272</v>
       </c>
       <c r="G3" s="1">
-        <v>134</v>
-      </c>
-      <c r="I3" s="21">
-        <v>105093</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>130</v>
+        <v>306</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1631,6 +1716,9 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
     </row>
     <row r="4" spans="1:23" ht="47.25">
       <c r="A4" s="1" t="s">
@@ -1640,29 +1728,29 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="D4" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="G4" s="1">
-        <v>32</v>
+        <v>606</v>
       </c>
       <c r="H4" s="21"/>
-      <c r="I4" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>135</v>
+      <c r="I4" s="1">
+        <v>127449</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>137</v>
+        <v>278</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1672,8 +1760,11 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-    </row>
-    <row r="5" spans="1:23" ht="63">
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+    </row>
+    <row r="5" spans="1:23" ht="47.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1681,28 +1772,28 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D5" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>139</v>
+        <v>2021</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G5" s="1">
-        <v>745</v>
+        <v>134</v>
       </c>
       <c r="I5" s="21">
-        <v>140933</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>141</v>
+        <v>105093</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1713,86 +1804,86 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:23" ht="47.25">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="1">
         <v>2020</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="G6" s="6">
-        <v>10</v>
-      </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="6">
-        <v>503</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-    </row>
-    <row r="7" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A7" s="6" t="s">
+      <c r="E6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="1">
+        <v>32</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="I6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7" spans="1:23" ht="63">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="1">
         <v>2020</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>149</v>
+      <c r="E7" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" s="6">
-        <v>126</v>
-      </c>
-      <c r="I7" s="22">
-        <v>104660</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
+        <v>140</v>
+      </c>
+      <c r="G7" s="1">
+        <v>745</v>
+      </c>
+      <c r="I7" s="21">
+        <v>140933</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
     </row>
     <row r="8" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A8" s="6" t="s">
@@ -1802,28 +1893,29 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D8" s="6">
         <v>2020</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G8" s="6">
-        <v>706</v>
-      </c>
-      <c r="I8" s="22">
-        <v>135702</v>
+        <v>10</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" s="6">
+        <v>503</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -1842,28 +1934,28 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D9" s="6">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>159</v>
+        <v>149</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="G9" s="6">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="I9" s="22">
-        <v>100260</v>
+        <v>104660</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -1882,29 +1974,28 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D10" s="6">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G10" s="6">
-        <v>11</v>
-      </c>
-      <c r="H10" s="22">
-        <v>1681</v>
-      </c>
-      <c r="I10" s="6"/>
+        <v>706</v>
+      </c>
+      <c r="I10" s="22">
+        <v>135702</v>
+      </c>
       <c r="J10" s="6" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -1923,29 +2014,28 @@
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D11" s="6">
         <v>2019</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="16" t="s">
-        <v>173</v>
+        <v>159</v>
+      </c>
+      <c r="G11" s="6">
+        <v>9</v>
+      </c>
+      <c r="I11" s="22">
+        <v>100260</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -1964,29 +2054,29 @@
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D12" s="6">
         <v>2019</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="G12" s="6">
-        <v>111</v>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="15" t="s">
-        <v>182</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H12" s="22">
+        <v>1681</v>
+      </c>
+      <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -2005,29 +2095,29 @@
         <v>12</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="D13" s="6">
         <v>2019</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G13" s="6">
-        <v>64</v>
+        <v>169</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="15" t="s">
-        <v>177</v>
+      <c r="I13" s="16" t="s">
+        <v>173</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -2038,156 +2128,172 @@
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
     </row>
-    <row r="14" spans="1:23" s="20" customFormat="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-    </row>
-    <row r="15" spans="1:23" s="20" customFormat="1">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-    </row>
-    <row r="16" spans="1:23" s="8" customFormat="1" ht="31.5">
-      <c r="A16" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B16" s="6">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="F16" s="6" t="s">
+    <row r="14" spans="1:23" s="8" customFormat="1" ht="47.25">
+      <c r="A14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1">
+        <v>13</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2019</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G14" s="6">
+        <v>111</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+    </row>
+    <row r="15" spans="1:23" s="8" customFormat="1" ht="47.25">
+      <c r="A15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>14</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2019</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-    </row>
-    <row r="17" spans="1:19" ht="47.25">
-      <c r="A17" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="6">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-    </row>
-    <row r="18" spans="1:19" ht="31.5">
+      <c r="G15" s="6">
+        <v>64</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+    </row>
+    <row r="16" spans="1:23" s="20" customFormat="1">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+    </row>
+    <row r="17" spans="1:19" s="20" customFormat="1">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+    </row>
+    <row r="18" spans="1:19" s="8" customFormat="1" ht="31.5">
       <c r="A18" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B18" s="6">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>271</v>
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>303</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-    </row>
-    <row r="19" spans="1:19" ht="63">
+      <c r="E18" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+    </row>
+    <row r="19" spans="1:19" ht="47.25">
       <c r="A19" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B19" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>124</v>
@@ -2217,16 +2323,16 @@
         <v>123</v>
       </c>
       <c r="B20" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>181</v>
@@ -2245,206 +2351,192 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-    </row>
-    <row r="22" spans="1:19">
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-    </row>
-    <row r="23" spans="1:19" s="24" customFormat="1">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-    </row>
-    <row r="24" spans="1:19" s="8" customFormat="1" ht="47.25">
-      <c r="A24" s="6" t="s">
+    <row r="21" spans="1:19" s="29" customFormat="1">
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+    </row>
+    <row r="22" spans="1:19" s="31" customFormat="1">
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+    </row>
+    <row r="23" spans="1:19" s="29" customFormat="1">
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+    </row>
+    <row r="25" spans="1:19" s="24" customFormat="1">
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+    </row>
+    <row r="26" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="A26" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B26" s="6">
         <v>1</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D26" s="6">
         <v>2019</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E26" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6" t="s">
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7" t="s">
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="S24" s="7" t="s">
+      <c r="S26" s="7" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="63">
-      <c r="A25" s="1" t="s">
+    <row r="27" spans="1:19" ht="63">
+      <c r="A27" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B27" s="1">
         <v>2</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D27" s="1">
         <v>2019</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="3" t="s">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1" t="s">
+      <c r="L27" s="1"/>
+      <c r="M27" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-    </row>
-    <row r="26" spans="1:19" ht="63">
-      <c r="A26" s="1" t="s">
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+    </row>
+    <row r="28" spans="1:19" ht="63">
+      <c r="A28" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B28" s="1">
         <v>3</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D28" s="1">
         <v>2017</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E28" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="S26" s="1"/>
-    </row>
-    <row r="27" spans="1:19" s="24" customFormat="1">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="23"/>
-    </row>
-    <row r="28" spans="1:19" ht="29.25">
-      <c r="A28" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B28" s="1">
-        <v>2</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -2454,54 +2546,54 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-      <c r="R28" s="3"/>
+      <c r="R28" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" ht="29.25">
-      <c r="A29" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B29" s="1">
+    <row r="29" spans="1:19" s="24" customFormat="1">
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="23"/>
+    </row>
+    <row r="30" spans="1:19" ht="47.25">
+      <c r="A30" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B30" s="1">
         <v>1</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D29" s="1">
+      <c r="C30" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D30" s="1">
         <v>2022</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="1"/>
-    </row>
-    <row r="30" spans="1:19">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="9"/>
+      <c r="E30" s="9" t="s">
+        <v>324</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2509,7 +2601,9 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
@@ -2517,509 +2611,528 @@
       <c r="R30" s="3"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" s="24" customFormat="1">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="23"/>
-    </row>
-    <row r="32" spans="1:19" ht="47.25">
+    <row r="31" spans="1:19" ht="47.25">
+      <c r="A31" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="1"/>
+    </row>
+    <row r="32" spans="1:19" ht="29.25">
       <c r="A32" s="1" t="s">
-        <v>13</v>
+        <v>294</v>
       </c>
       <c r="B32" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="D32" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>2022</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>298</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>17</v>
+        <v>299</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-      <c r="R32" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="R32" s="3"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:23" ht="47.25">
+    <row r="33" spans="1:23" ht="29.25">
       <c r="A33" s="1" t="s">
-        <v>13</v>
+        <v>294</v>
       </c>
       <c r="B33" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="D33" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>57</v>
+        <v>2021</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>297</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
+      <c r="R33" s="3"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:23" s="24" customFormat="1">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
-      <c r="S34" s="23"/>
-    </row>
-    <row r="35" spans="1:23">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
+    <row r="34" spans="1:23">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="1"/>
+    </row>
+    <row r="35" spans="1:23" s="24" customFormat="1">
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="23"/>
     </row>
     <row r="36" spans="1:23" ht="47.25">
-      <c r="A36" s="6" t="s">
-        <v>22</v>
+      <c r="A36" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>287</v>
+        <v>28</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2020</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>276</v>
+        <v>14</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="O36" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q36" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>289</v>
+      <c r="J36" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="S36" s="1"/>
     </row>
     <row r="37" spans="1:23" ht="47.25">
-      <c r="A37" s="6" t="s">
-        <v>22</v>
+      <c r="A37" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B37" s="1">
         <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>287</v>
+        <v>29</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2011</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>294</v>
+        <v>57</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="O37" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q37" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" s="3" t="s">
-        <v>297</v>
-      </c>
+      <c r="L37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:23" ht="47.25">
-      <c r="A38" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="1">
-        <v>3</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+    <row r="38" spans="1:23" s="24" customFormat="1">
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
       <c r="M38" s="1"/>
-      <c r="N38" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="O38" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q38" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="S38" s="1"/>
-    </row>
-    <row r="39" spans="1:23" s="8" customFormat="1" ht="78.75">
-      <c r="A39" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B39" s="1">
-        <v>4</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="O39" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P39" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q39" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W39" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" s="8" customFormat="1" ht="63">
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="23"/>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+    </row>
+    <row r="40" spans="1:23" ht="31.5">
       <c r="A40" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B40" s="1">
-        <v>5</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N40" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="O40" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P40" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q40" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R40" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" s="8" customFormat="1" ht="31.5">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="O40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+    </row>
+    <row r="41" spans="1:23" ht="63">
       <c r="A41" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="1">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N41" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O41" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P41" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q41" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" s="8" customFormat="1" ht="31.5">
+        <v>2</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="O41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+    </row>
+    <row r="42" spans="1:23" ht="47.25">
       <c r="A42" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B42" s="1">
-        <v>7</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="N42" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O42" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P42" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q42" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" s="8" customFormat="1" ht="31.5">
+        <v>3</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O42" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q42" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="S42" s="1"/>
+    </row>
+    <row r="43" spans="1:23" ht="31.5">
       <c r="A43" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="1">
-        <v>8</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O43" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P43" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q43" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" s="8" customFormat="1" ht="31.5">
+        <v>4</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="S43" s="1"/>
+    </row>
+    <row r="44" spans="1:23" ht="31.5">
       <c r="A44" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="1">
-        <v>9</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="N44" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O44" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P44" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q44" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" s="8" customFormat="1" ht="31.5">
+        <v>5</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q44" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="S44" s="1"/>
+    </row>
+    <row r="45" spans="1:23" s="8" customFormat="1" ht="78.75">
       <c r="A45" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O45" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P45" s="8" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="Q45" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" s="8" customFormat="1" ht="63">
+      <c r="W45" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" s="8" customFormat="1" ht="47.25">
       <c r="A46" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="O46" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P46" s="8" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="Q46" s="8" t="b">
         <v>0</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:23" s="8" customFormat="1" ht="31.5">
@@ -3027,560 +3140,527 @@
         <v>22</v>
       </c>
       <c r="B47" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="O47" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P47" s="8" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="Q47" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:23" s="8" customFormat="1" ht="47.25">
+    <row r="48" spans="1:23" s="8" customFormat="1" ht="31.5">
       <c r="A48" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B48" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="N48" s="8" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="O48" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P48" s="8" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="Q48" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:19" s="8" customFormat="1" ht="78.75">
+    <row r="49" spans="1:18" s="8" customFormat="1" ht="31.5">
       <c r="A49" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B49" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="O49" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P49" s="8" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="Q49" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="R49" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" s="8" customFormat="1" ht="78.75">
+    </row>
+    <row r="50" spans="1:18" s="8" customFormat="1" ht="31.5">
       <c r="A50" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B50" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="N50" s="8" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="O50" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P50" s="8" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="Q50" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="R50" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" s="8" customFormat="1" ht="78.75">
+    </row>
+    <row r="51" spans="1:18" s="8" customFormat="1" ht="31.5">
       <c r="A51" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="O51" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P51" s="8" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="Q51" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="R51" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" s="8" customFormat="1" ht="31.5">
+    </row>
+    <row r="52" spans="1:18" s="8" customFormat="1" ht="31.5">
       <c r="A52" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="N52" s="8" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="O52" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P52" s="8" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="Q52" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="R52" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" s="8" customFormat="1" ht="31.5">
       <c r="A53" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>232</v>
+        <v>66</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="O53" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P53" s="8" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="Q53" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="8" customFormat="1" ht="47.25">
+    <row r="54" spans="1:18" s="8" customFormat="1" ht="47.25">
       <c r="A54" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>237</v>
+        <v>66</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="N54" s="8" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="O54" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="Q54" s="8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="8" customFormat="1" ht="63">
+    <row r="55" spans="1:18" s="8" customFormat="1" ht="78.75">
       <c r="A55" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B55" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="O55" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="Q55" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" s="8" customFormat="1" ht="47.25">
+      <c r="R55" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" s="8" customFormat="1" ht="78.75">
       <c r="A56" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B56" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>242</v>
+        <v>204</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>243</v>
+        <v>70</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="N56" s="8" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="O56" s="8" t="b">
         <v>0</v>
       </c>
       <c r="P56" s="8" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="Q56" s="8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:19" s="8" customFormat="1" ht="31.5">
+      <c r="R56" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" s="8" customFormat="1" ht="78.75">
       <c r="A57" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B57" s="1">
+        <v>18</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="N57" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O57" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q57" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R57" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" s="8" customFormat="1" ht="31.5">
+      <c r="A58" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="B58" s="1">
+        <v>19</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="N58" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O58" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q58" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" s="8" customFormat="1" ht="47.25">
+      <c r="A59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="1">
+        <v>20</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="O59" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q59" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" s="8" customFormat="1" ht="31.5">
+      <c r="A60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="1">
+        <v>21</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="O60" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q60" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" s="8" customFormat="1" ht="63">
+      <c r="A61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="1">
+        <v>22</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="O61" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q61" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" s="8" customFormat="1" ht="47.25">
+      <c r="A62" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="1">
+        <v>23</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="N62" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="O62" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q62" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" s="8" customFormat="1" ht="31.5">
+      <c r="A63" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="1">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D63" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E63" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="N57" s="8" t="s">
+      <c r="N63" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="O57" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P57" s="8" t="s">
+      <c r="O63" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="Q57" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" s="24" customFormat="1">
-      <c r="A58" s="23"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="E58" s="23"/>
-    </row>
-    <row r="59" spans="1:19" ht="47.25">
-      <c r="A59" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B59" s="1">
-        <v>1</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D59" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S59" s="1"/>
-    </row>
-    <row r="60" spans="1:19" ht="47.25">
-      <c r="A60" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B60" s="1">
-        <v>2</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="1">
-        <v>2013</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S60" s="1"/>
-    </row>
-    <row r="61" spans="1:19" ht="47.25">
-      <c r="A61" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B61" s="1">
-        <v>3</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D61" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S61" s="1"/>
-    </row>
-    <row r="62" spans="1:19" ht="47.25">
-      <c r="A62" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B62" s="1">
-        <v>4</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D62" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S62" s="1"/>
-    </row>
-    <row r="63" spans="1:19" ht="47.25">
-      <c r="A63" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B63" s="1">
-        <v>5</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D63" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-      <c r="R63" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S63" s="1"/>
-    </row>
-    <row r="64" spans="1:19" ht="47.25">
-      <c r="A64" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B64" s="1">
-        <v>6</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D64" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S64" s="1"/>
+      <c r="Q63" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" s="24" customFormat="1">
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
+      <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:22" ht="47.25">
       <c r="A65" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B65" s="1">
-        <v>7</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D65" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>61</v>
+        <v>2014</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -3589,7 +3669,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
-      <c r="M65" s="11" t="s">
+      <c r="M65" s="1" t="s">
         <v>38</v>
       </c>
       <c r="N65" s="1"/>
@@ -3597,7 +3677,7 @@
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="S65" s="1"/>
     </row>
@@ -3606,16 +3686,16 @@
         <v>32</v>
       </c>
       <c r="B66" s="1">
+        <v>2</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>44</v>
-      </c>
       <c r="D66" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>62</v>
+        <v>2013</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -3624,15 +3704,15 @@
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
-      <c r="M66" s="11" t="s">
-        <v>38</v>
+      <c r="M66" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="S66" s="1"/>
     </row>
@@ -3641,16 +3721,16 @@
         <v>32</v>
       </c>
       <c r="B67" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D67" s="1">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -3667,7 +3747,7 @@
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
       <c r="R67" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="S67" s="1"/>
     </row>
@@ -3676,16 +3756,16 @@
         <v>32</v>
       </c>
       <c r="B68" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D68" s="1">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -3702,406 +3782,618 @@
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S68" s="1"/>
+    </row>
+    <row r="69" spans="1:22" ht="47.25">
+      <c r="A69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B69" s="1">
+        <v>5</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S69" s="1"/>
+    </row>
+    <row r="70" spans="1:22" ht="47.25">
+      <c r="A70" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B70" s="1">
+        <v>6</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D70" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S70" s="1"/>
+    </row>
+    <row r="71" spans="1:22" ht="47.25">
+      <c r="A71" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B71" s="1">
+        <v>7</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D71" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S71" s="1"/>
+    </row>
+    <row r="72" spans="1:22" ht="47.25">
+      <c r="A72" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B72" s="1">
+        <v>8</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S72" s="1"/>
+    </row>
+    <row r="73" spans="1:22" ht="47.25">
+      <c r="A73" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B73" s="1">
+        <v>9</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D73" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S73" s="1"/>
+    </row>
+    <row r="74" spans="1:22" ht="47.25">
+      <c r="A74" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B74" s="1">
+        <v>10</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S68" s="1"/>
-    </row>
-    <row r="69" spans="1:22" ht="110.25">
-      <c r="A69" s="1" t="s">
+      <c r="S74" s="1"/>
+    </row>
+    <row r="75" spans="1:22" ht="110.25">
+      <c r="A75" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B75" s="1">
         <v>1</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="N69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P69" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q69" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T69" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" ht="63">
-      <c r="A70" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B70" s="1">
-        <v>2</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="N70" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P70" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q70" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T70" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" ht="63">
-      <c r="A71" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="1">
-        <v>3</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="N71" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P71" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q71" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T71" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" ht="78.75">
-      <c r="A72" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="1">
-        <v>4</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="N72" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P72" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q72" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T72" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" s="13" customFormat="1" ht="78.75">
-      <c r="A73" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="1">
-        <v>1</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D73" s="13">
-        <v>2020</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S73" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="U73" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="V73" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" ht="31.5">
-      <c r="A74" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B74" s="1">
-        <v>2</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D74" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="S74" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U74" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" ht="31.5">
-      <c r="A75" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75" s="1">
-        <v>3</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D75" s="2">
-        <v>2018</v>
+      <c r="D75" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="S75" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U75" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" ht="78.75">
+        <v>67</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" ht="63">
       <c r="A76" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B76" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="2">
-        <v>2018</v>
+      <c r="D76" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="S76" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U76" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V76" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22">
+        <v>71</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q76" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" ht="63">
       <c r="A77" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B77" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D77" s="2">
-        <v>2016</v>
+      <c r="D77" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="U77" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" ht="31.5">
+        <v>76</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="78.75">
       <c r="A78" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B78" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D78" s="2">
-        <v>2015</v>
+      <c r="D78" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="S78" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="U78" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" ht="78.75">
+        <v>80</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q78" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" s="13" customFormat="1" ht="78.75">
       <c r="A79" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B79" s="1">
         <v>1</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D79" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R79" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U79" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="V79" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" ht="78.75">
+      <c r="C79" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D79" s="13">
+        <v>2020</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="S79" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="U79" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="V79" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="31.5">
       <c r="A80" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B80" s="1">
         <v>2</v>
       </c>
-      <c r="C80" s="12" t="s">
-        <v>105</v>
+      <c r="C80" s="10" t="s">
+        <v>126</v>
       </c>
       <c r="D80" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U80" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="31.5">
+        <v>120</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="31.5">
       <c r="A81" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="B81" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="2">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="R81" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19">
+        <v>88</v>
+      </c>
+      <c r="U81" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" ht="78.75">
       <c r="A82" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="B82" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="S82" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U82" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22">
+      <c r="A83" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="1">
+        <v>5</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2">
+        <v>2016</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S83" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U83" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" ht="31.5">
+      <c r="A84" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1">
+        <v>6</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2">
+        <v>2015</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U84" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="78.75">
+      <c r="A85" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B85" s="1">
+        <v>1</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R85" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="S85" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U85" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" ht="78.75">
+      <c r="A86" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86" s="1">
+        <v>2</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D86" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U86" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="31.5">
+      <c r="A87" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B87" s="1">
+        <v>1</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="2">
         <v>2019</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E87" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S87" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22">
+      <c r="A88" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" s="1">
+        <v>2</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E88" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="R82" s="2" t="s">
+      <c r="R88" s="2" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:K15">
-    <sortCondition ref="B5:B15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:K17">
+    <sortCondition ref="B7:B17"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J32" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
-    <hyperlink ref="K3" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
-    <hyperlink ref="K4" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
-    <hyperlink ref="K5" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
-    <hyperlink ref="K6" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
-    <hyperlink ref="K7" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
-    <hyperlink ref="K8" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
-    <hyperlink ref="K9" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
-    <hyperlink ref="K10" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
-    <hyperlink ref="K11" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
-    <hyperlink ref="K13" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
-    <hyperlink ref="K12" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
-    <hyperlink ref="R24" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
-    <hyperlink ref="S24" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
-    <hyperlink ref="K25" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
-    <hyperlink ref="R26" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W39" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R51" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R50" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R49" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R46" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R40" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
-    <hyperlink ref="K2" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
-    <hyperlink ref="J2" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
-    <hyperlink ref="R36" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
-    <hyperlink ref="R38" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
-    <hyperlink ref="R37" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="J36" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
+    <hyperlink ref="K5" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
+    <hyperlink ref="K6" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
+    <hyperlink ref="K7" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
+    <hyperlink ref="K8" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
+    <hyperlink ref="K9" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
+    <hyperlink ref="K10" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
+    <hyperlink ref="K11" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
+    <hyperlink ref="K12" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
+    <hyperlink ref="K13" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
+    <hyperlink ref="K15" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
+    <hyperlink ref="K14" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
+    <hyperlink ref="R26" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
+    <hyperlink ref="S26" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
+    <hyperlink ref="K27" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
+    <hyperlink ref="R28" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
+    <hyperlink ref="W45" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R57" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R56" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R55" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R52" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R46" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="K4" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
+    <hyperlink ref="J4" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
+    <hyperlink ref="R42" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
+    <hyperlink ref="R44" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
+    <hyperlink ref="R43" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="K3" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
+    <hyperlink ref="K2" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId28"/>
+  <pageSetup orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>
--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE5F44A-4AB0-439C-9F40-683B714677CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F117C4BC-9567-4612-8265-B9C2B6F6FAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="38700" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -903,9 +903,6 @@
     <t>A Machine Learning Approach for Assessing Wildfire Vulnerability in the Colorado River Basin</t>
   </si>
   <si>
-    <t>H Han, TA Abitew, S Park, C Green, J Jeong</t>
-  </si>
-  <si>
     <t>https://agu.confex.com/agu/fm21/meetingapp.cgi/Paper/832202</t>
   </si>
   <si>
@@ -1012,6 +1009,9 @@
   </si>
   <si>
     <t>Korea Institute of Civil Engineering and Building Technology No. 22-02.</t>
+  </si>
+  <si>
+    <t>Han, H., Abitew, TA.,  Park, S., Green, C., and Jeong, J.</t>
   </si>
 </sst>
 </file>
@@ -1644,13 +1644,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D2" s="1">
         <v>2022</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>273</v>
@@ -1661,10 +1661,10 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1692,7 +1692,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>272</v>
@@ -1703,10 +1703,10 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -2260,13 +2260,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>176</v>
@@ -2580,19 +2580,19 @@
     </row>
     <row r="30" spans="1:19" ht="47.25">
       <c r="A30" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D30" s="1">
         <v>2022</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -2602,7 +2602,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -2613,19 +2613,19 @@
     </row>
     <row r="31" spans="1:19" ht="47.25">
       <c r="A31" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B31" s="1">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D31" s="1">
         <v>2022</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -2635,7 +2635,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -2646,19 +2646,19 @@
     </row>
     <row r="32" spans="1:19" ht="29.25">
       <c r="A32" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D32" s="1">
         <v>2022</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -2668,7 +2668,7 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
@@ -2679,19 +2679,19 @@
     </row>
     <row r="33" spans="1:23" ht="29.25">
       <c r="A33" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B33" s="1">
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D33" s="1">
         <v>2021</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -2701,7 +2701,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -2878,13 +2878,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -2895,13 +2895,13 @@
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="O40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="O40" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="Q40" s="1" t="b">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2934,13 +2934,13 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="O41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="O41" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="Q41" s="1" t="b">
         <v>0</v>
@@ -2997,13 +2997,13 @@
         <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>284</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="S43" s="1"/>
     </row>
@@ -3038,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>284</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S44" s="1"/>
     </row>
@@ -3416,7 +3416,7 @@
         <v>70</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N56" s="8" t="s">
         <v>221</v>

--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F117C4BC-9567-4612-8265-B9C2B6F6FAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABCC2C5-9F3E-404E-81D4-C40A2BD4E3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="51480" yWindow="3300" windowWidth="29040" windowHeight="17790" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="336">
   <si>
     <t>authors</t>
   </si>
@@ -1012,6 +1012,36 @@
   </si>
   <si>
     <t>Han, H., Abitew, TA.,  Park, S., Green, C., and Jeong, J.</t>
+  </si>
+  <si>
+    <t>Environmental Earth Sciences</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.envsoft.2023.105723</t>
+  </si>
+  <si>
+    <t>10.1016/j.envsoft.2023.105723</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s12665-022-10662-9</t>
+  </si>
+  <si>
+    <t>10.1007/s12665-022-10662-9</t>
+  </si>
+  <si>
+    <t>March, 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2nd PEST Conference </t>
+  </si>
+  <si>
+    <t>La Jolla, CA, Unitied States</t>
+  </si>
+  <si>
+    <t>Park, S., Abitew, T., and Jeong, J.</t>
+  </si>
+  <si>
+    <t>Reproducible Parameter Estimation Framework for Integrated Hydrological Models</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1148,13 +1178,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1169,16 +1193,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1196,16 +1214,10 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1541,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W88"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -1636,7 +1648,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="63">
+    <row r="2" spans="1:23" ht="47.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1644,27 +1656,29 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="D2" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="G2" s="1">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1">
+        <v>105723</v>
+      </c>
       <c r="J2" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1686,27 +1700,29 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="D3" s="1">
         <v>2022</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="G3" s="1">
-        <v>610</v>
+        <v>81</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1">
+        <v>531</v>
+      </c>
       <c r="J3" s="1" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1720,7 +1736,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:23" ht="47.25">
+    <row r="4" spans="1:23" ht="63">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1728,29 +1744,27 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="D4" s="1">
         <v>2022</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G4" s="1">
-        <v>606</v>
-      </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="1">
-        <v>127449</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>279</v>
+        <v>146</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>278</v>
+        <v>318</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1772,28 +1786,27 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="D5" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>128</v>
+        <v>303</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>129</v>
+        <v>272</v>
       </c>
       <c r="G5" s="1">
-        <v>134</v>
-      </c>
-      <c r="I5" s="21">
-        <v>105093</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>130</v>
+        <v>305</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1803,6 +1816,9 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
     </row>
     <row r="6" spans="1:23" ht="47.25">
       <c r="A6" s="1" t="s">
@@ -1812,29 +1828,29 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="D6" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="G6" s="1">
-        <v>32</v>
-      </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>135</v>
+        <v>606</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="1">
+        <v>127449</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>137</v>
+        <v>278</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1844,8 +1860,11 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="1:23" ht="63">
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+    </row>
+    <row r="7" spans="1:23" ht="47.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1853,28 +1872,28 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D7" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>139</v>
+        <v>2021</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G7" s="1">
-        <v>745</v>
-      </c>
-      <c r="I7" s="21">
-        <v>140933</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>141</v>
+        <v>134</v>
+      </c>
+      <c r="I7" s="17">
+        <v>105093</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1885,457 +1904,472 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:23" ht="47.25">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="1">
         <v>2020</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="G8" s="6">
-        <v>10</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="6">
-        <v>503</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-    </row>
-    <row r="9" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A9" s="6" t="s">
+      <c r="E8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="1">
+        <v>32</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9" spans="1:23" ht="63">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="1">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="1">
         <v>2020</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>149</v>
+      <c r="E9" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="6">
-        <v>126</v>
-      </c>
-      <c r="I9" s="22">
-        <v>104660</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-    </row>
-    <row r="10" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A10" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="1">
+        <v>745</v>
+      </c>
+      <c r="I9" s="17">
+        <v>140933</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="10" spans="1:23" ht="47.25">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="1">
         <v>2020</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G10" s="6">
-        <v>706</v>
-      </c>
-      <c r="I10" s="22">
-        <v>135702</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-    </row>
-    <row r="11" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A11" s="6" t="s">
+      <c r="E10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="1">
+        <v>503</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+    </row>
+    <row r="11" spans="1:23" ht="47.25">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="6">
-        <v>2019</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G11" s="6">
-        <v>9</v>
-      </c>
-      <c r="I11" s="22">
-        <v>100260</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-    </row>
-    <row r="12" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A12" s="6" t="s">
+      <c r="C11" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="1">
+        <v>126</v>
+      </c>
+      <c r="I11" s="17">
+        <v>104660</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+    </row>
+    <row r="12" spans="1:23" ht="47.25">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="6">
-        <v>2019</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="G12" s="6">
-        <v>11</v>
-      </c>
-      <c r="H12" s="22">
-        <v>1681</v>
-      </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-    </row>
-    <row r="13" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A13" s="6" t="s">
+      <c r="C12" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G12" s="1">
+        <v>706</v>
+      </c>
+      <c r="I12" s="17">
+        <v>135702</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+    </row>
+    <row r="13" spans="1:23" ht="47.25">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="1">
         <v>2019</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-    </row>
-    <row r="14" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A14" s="6" t="s">
+      <c r="E13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" s="1">
+        <v>9</v>
+      </c>
+      <c r="I13" s="17">
+        <v>100260</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+    </row>
+    <row r="14" spans="1:23" ht="47.25">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" s="1">
         <v>2019</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G14" s="6">
-        <v>111</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-    </row>
-    <row r="15" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A15" s="6" t="s">
+      <c r="E14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="1">
+        <v>11</v>
+      </c>
+      <c r="H14" s="17">
+        <v>1681</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+    </row>
+    <row r="15" spans="1:23" ht="47.25">
+      <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+    </row>
+    <row r="16" spans="1:23" ht="47.25">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G16" s="1">
+        <v>111</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+    </row>
+    <row r="17" spans="1:19" ht="47.25">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="1">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D17" s="1">
         <v>2019</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E17" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G17" s="1">
         <v>64</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="15" t="s">
+      <c r="H17" s="1"/>
+      <c r="I17" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J17" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K17" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-    </row>
-    <row r="16" spans="1:23" s="20" customFormat="1">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-    </row>
-    <row r="17" spans="1:19" s="20" customFormat="1">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-    </row>
-    <row r="18" spans="1:19" s="8" customFormat="1" ht="31.5">
-      <c r="A18" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="6">
-        <v>1</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-    </row>
-    <row r="19" spans="1:19" ht="47.25">
-      <c r="A19" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="6">
-        <v>2</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+    </row>
+    <row r="18" spans="1:19" s="16" customFormat="1">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+    </row>
+    <row r="19" spans="1:19" s="16" customFormat="1">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
     </row>
     <row r="20" spans="1:19" ht="47.25">
       <c r="A20" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="6">
-        <v>3</v>
+      <c r="B20" s="1">
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -2351,68 +2385,68 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" s="29" customFormat="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="28"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-    </row>
-    <row r="22" spans="1:19" s="31" customFormat="1">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-    </row>
-    <row r="23" spans="1:19" s="29" customFormat="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
+    <row r="21" spans="1:19" s="23" customFormat="1">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="22"/>
+    </row>
+    <row r="22" spans="1:19" s="25" customFormat="1">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+    </row>
+    <row r="23" spans="1:19" s="23" customFormat="1">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="22"/>
     </row>
     <row r="24" spans="1:19">
       <c r="G24" s="1"/>
@@ -2429,61 +2463,61 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19" s="24" customFormat="1">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-    </row>
-    <row r="26" spans="1:19" s="8" customFormat="1" ht="47.25">
-      <c r="A26" s="6" t="s">
+    <row r="25" spans="1:19" s="19" customFormat="1">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+    </row>
+    <row r="26" spans="1:19" ht="47.25">
+      <c r="A26" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="1">
         <v>1</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="1">
         <v>2019</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E26" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6" t="s">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="7" t="s">
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="S26" s="7" t="s">
+      <c r="S26" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -2500,7 +2534,7 @@
       <c r="D27" s="1">
         <v>2019</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>253</v>
       </c>
       <c r="F27" s="1"/>
@@ -2535,7 +2569,7 @@
       <c r="D28" s="1">
         <v>2017</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>254</v>
       </c>
       <c r="F28" s="1"/>
@@ -2557,26 +2591,26 @@
       </c>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19" s="24" customFormat="1">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="23"/>
+    <row r="29" spans="1:19" s="19" customFormat="1">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="18"/>
     </row>
     <row r="30" spans="1:19" ht="47.25">
       <c r="A30" s="1" t="s">
@@ -2591,7 +2625,7 @@
       <c r="D30" s="1">
         <v>2022</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="7" t="s">
         <v>323</v>
       </c>
       <c r="F30" s="1"/>
@@ -2624,7 +2658,7 @@
       <c r="D31" s="1">
         <v>2022</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="7" t="s">
         <v>320</v>
       </c>
       <c r="F31" s="1"/>
@@ -2657,7 +2691,7 @@
       <c r="D32" s="1">
         <v>2022</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="7" t="s">
         <v>297</v>
       </c>
       <c r="F32" s="1"/>
@@ -2690,7 +2724,7 @@
       <c r="D33" s="1">
         <v>2021</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="7" t="s">
         <v>296</v>
       </c>
       <c r="F33" s="1"/>
@@ -2715,7 +2749,7 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="9"/>
+      <c r="E34" s="7"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -2731,26 +2765,26 @@
       <c r="R34" s="3"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:23" s="24" customFormat="1">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="23"/>
+    <row r="35" spans="1:23" s="19" customFormat="1">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="18"/>
     </row>
     <row r="36" spans="1:23" ht="47.25">
       <c r="A36" s="1" t="s">
@@ -2830,25 +2864,25 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:23" s="24" customFormat="1">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
+    <row r="38" spans="1:23" s="19" customFormat="1">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
       <c r="M38" s="1"/>
-      <c r="O38" s="23"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="23"/>
-      <c r="R38" s="23"/>
-      <c r="S38" s="23"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
     </row>
     <row r="39" spans="1:23">
       <c r="A39" s="1"/>
@@ -2871,20 +2905,20 @@
       <c r="S39" s="1"/>
     </row>
     <row r="40" spans="1:23" ht="31.5">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -2893,15 +2927,14 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
       <c r="N40" s="1" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="O40" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="Q40" s="1" t="b">
         <v>0</v>
@@ -2909,21 +2942,21 @@
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:23" ht="63">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:23" ht="31.5">
+      <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="1">
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2934,13 +2967,13 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="O41" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q41" s="1" t="b">
         <v>0</v>
@@ -2948,21 +2981,21 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="47.25">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:23" ht="63">
+      <c r="A42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B42" s="1">
         <v>3</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -2973,37 +3006,35 @@
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="O42" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="Q42" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="31.5">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:23" ht="47.25">
+      <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="1">
         <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>284</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -3026,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="S43" s="1"/>
     </row>
     <row r="44" spans="1:23" ht="31.5">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="1">
         <v>5</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>284</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -3067,635 +3098,641 @@
         <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:23" s="8" customFormat="1" ht="78.75">
-      <c r="A45" s="6" t="s">
+    <row r="45" spans="1:23" ht="31.5">
+      <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="1">
         <v>6</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="N45" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="O45" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P45" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q45" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W45" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" s="8" customFormat="1" ht="47.25">
-      <c r="A46" s="6" t="s">
+      <c r="C45" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O45" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q45" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="S45" s="1"/>
+    </row>
+    <row r="46" spans="1:23" ht="78.75">
+      <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="1">
         <v>7</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N46" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="O46" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P46" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q46" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R46" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" s="8" customFormat="1" ht="31.5">
-      <c r="A47" s="6" t="s">
+      <c r="C46" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="O46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="47.25">
+      <c r="A47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="1">
         <v>8</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N47" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O47" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P47" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q47" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" s="8" customFormat="1" ht="31.5">
-      <c r="A48" s="6" t="s">
+      <c r="C47" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="O47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" ht="31.5">
+      <c r="A48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B48" s="1">
         <v>9</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D48" s="8" t="s">
+      <c r="C48" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="N48" s="8" t="s">
+      <c r="E48" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="N48" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="O48" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P48" s="8" t="s">
+      <c r="O48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="Q48" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" s="8" customFormat="1" ht="31.5">
-      <c r="A49" s="6" t="s">
+      <c r="Q48" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="31.5">
+      <c r="A49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B49" s="1">
         <v>10</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D49" s="8" t="s">
+      <c r="C49" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="N49" s="8" t="s">
+      <c r="E49" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N49" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="O49" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P49" s="8" t="s">
+      <c r="O49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="Q49" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" s="8" customFormat="1" ht="31.5">
-      <c r="A50" s="6" t="s">
+      <c r="Q49" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="31.5">
+      <c r="A50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B50" s="1">
         <v>11</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D50" s="8" t="s">
+      <c r="C50" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="N50" s="8" t="s">
+      <c r="E50" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="N50" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="O50" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P50" s="8" t="s">
+      <c r="O50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="Q50" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" s="8" customFormat="1" ht="31.5">
-      <c r="A51" s="6" t="s">
+      <c r="Q50" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="31.5">
+      <c r="A51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="1">
         <v>12</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D51" s="8" t="s">
+      <c r="C51" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="N51" s="8" t="s">
+      <c r="E51" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="N51" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="O51" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P51" s="8" t="s">
+      <c r="O51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="Q51" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" s="8" customFormat="1" ht="31.5">
-      <c r="A52" s="6" t="s">
+      <c r="Q51" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="31.5">
+      <c r="A52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="1">
         <v>13</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="N52" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="O52" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P52" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q52" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R52" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" s="8" customFormat="1" ht="31.5">
-      <c r="A53" s="6" t="s">
+      <c r="C52" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="O52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q52" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="31.5">
+      <c r="A53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="1">
         <v>14</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="N53" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="O53" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P53" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q53" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" s="8" customFormat="1" ht="47.25">
-      <c r="A54" s="6" t="s">
+      <c r="C53" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="O53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="31.5">
+      <c r="A54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="1">
         <v>15</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D54" s="8" t="s">
+      <c r="C54" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="N54" s="8" t="s">
+      <c r="E54" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N54" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="O54" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P54" s="8" t="s">
+      <c r="O54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="Q54" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" s="8" customFormat="1" ht="78.75">
-      <c r="A55" s="6" t="s">
+      <c r="Q54" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="47.25">
+      <c r="A55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B55" s="1">
         <v>16</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="O55" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P55" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q55" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R55" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" s="8" customFormat="1" ht="78.75">
-      <c r="A56" s="6" t="s">
+      <c r="C55" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="O55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q55" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="78.75">
+      <c r="A56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B56" s="1">
         <v>17</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D56" s="8" t="s">
+      <c r="C56" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="N56" s="8" t="s">
+      <c r="E56" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="N56" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="O56" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P56" s="8" t="s">
+      <c r="O56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="Q56" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R56" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" s="8" customFormat="1" ht="78.75">
-      <c r="A57" s="6" t="s">
+      <c r="Q56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="78.75">
+      <c r="A57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B57" s="1">
         <v>18</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D57" s="8" t="s">
+      <c r="C57" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="N57" s="8" t="s">
+      <c r="E57" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N57" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="O57" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P57" s="8" t="s">
+      <c r="O57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="Q57" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R57" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" s="8" customFormat="1" ht="31.5">
-      <c r="A58" s="6" t="s">
+      <c r="Q57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="78.75">
+      <c r="A58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B58" s="1">
         <v>19</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="N58" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="O58" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P58" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q58" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" s="8" customFormat="1" ht="47.25">
-      <c r="A59" s="6" t="s">
+      <c r="C58" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="31.5">
+      <c r="A59" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B59" s="1">
         <v>20</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="N59" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="O59" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P59" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q59" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" s="8" customFormat="1" ht="31.5">
-      <c r="A60" s="6" t="s">
+      <c r="C59" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="O59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q59" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="47.25">
+      <c r="A60" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B60" s="1">
         <v>21</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="N60" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="O60" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P60" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q60" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" s="8" customFormat="1" ht="63">
-      <c r="A61" s="6" t="s">
+      <c r="C60" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q60" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="31.5">
+      <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B61" s="1">
         <v>22</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="N61" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="O61" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P61" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q61" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" s="8" customFormat="1" ht="47.25">
-      <c r="A62" s="6" t="s">
+      <c r="C61" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="O61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q61" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="63">
+      <c r="A62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B62" s="1">
         <v>23</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="N62" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="O62" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P62" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q62" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" s="8" customFormat="1" ht="31.5">
-      <c r="A63" s="6" t="s">
+      <c r="C62" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q62" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="47.25">
+      <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B63" s="1">
         <v>24</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="O63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q63" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="31.5">
+      <c r="A64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="1">
+        <v>25</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D64" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E64" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="N63" s="8" t="s">
+      <c r="N64" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="O63" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P63" s="8" t="s">
+      <c r="O64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="Q63" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" s="24" customFormat="1">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="E64" s="23"/>
-    </row>
-    <row r="65" spans="1:22" ht="47.25">
-      <c r="A65" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D65" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S65" s="1"/>
+      <c r="Q64" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" s="19" customFormat="1">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="E65" s="18"/>
     </row>
     <row r="66" spans="1:22" ht="47.25">
       <c r="A66" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B66" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D66" s="1">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -3705,14 +3742,14 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S66" s="1"/>
     </row>
@@ -3721,16 +3758,16 @@
         <v>32</v>
       </c>
       <c r="B67" s="1">
-        <v>3</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D67" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>58</v>
+        <v>2013</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -3739,15 +3776,15 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
-      <c r="M67" s="11" t="s">
-        <v>38</v>
+      <c r="M67" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
       <c r="R67" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="S67" s="1"/>
     </row>
@@ -3756,16 +3793,16 @@
         <v>32</v>
       </c>
       <c r="B68" s="1">
-        <v>4</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>52</v>
+        <v>3</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D68" s="1">
         <v>2012</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>59</v>
+      <c r="E68" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -3774,7 +3811,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
-      <c r="M68" s="11" t="s">
+      <c r="M68" s="9" t="s">
         <v>38</v>
       </c>
       <c r="N68" s="1"/>
@@ -3782,7 +3819,7 @@
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S68" s="1"/>
     </row>
@@ -3791,16 +3828,16 @@
         <v>32</v>
       </c>
       <c r="B69" s="1">
-        <v>5</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="D69" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>40</v>
+        <v>2012</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -3809,7 +3846,7 @@
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
-      <c r="M69" s="11" t="s">
+      <c r="M69" s="9" t="s">
         <v>38</v>
       </c>
       <c r="N69" s="1"/>
@@ -3817,7 +3854,7 @@
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="S69" s="1"/>
     </row>
@@ -3826,16 +3863,16 @@
         <v>32</v>
       </c>
       <c r="B70" s="1">
-        <v>6</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="D70" s="1">
         <v>2010</v>
       </c>
-      <c r="E70" s="11" t="s">
-        <v>60</v>
+      <c r="E70" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -3844,7 +3881,7 @@
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="11" t="s">
+      <c r="M70" s="9" t="s">
         <v>38</v>
       </c>
       <c r="N70" s="1"/>
@@ -3852,7 +3889,7 @@
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="S70" s="1"/>
     </row>
@@ -3861,16 +3898,16 @@
         <v>32</v>
       </c>
       <c r="B71" s="1">
-        <v>7</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="D71" s="1">
         <v>2010</v>
       </c>
-      <c r="E71" s="10" t="s">
-        <v>61</v>
+      <c r="E71" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -3879,7 +3916,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
-      <c r="M71" s="11" t="s">
+      <c r="M71" s="9" t="s">
         <v>38</v>
       </c>
       <c r="N71" s="1"/>
@@ -3887,7 +3924,7 @@
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S71" s="1"/>
     </row>
@@ -3896,16 +3933,16 @@
         <v>32</v>
       </c>
       <c r="B72" s="1">
-        <v>8</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>44</v>
+        <v>7</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D72" s="1">
         <v>2010</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>62</v>
+      <c r="E72" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -3914,7 +3951,7 @@
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
-      <c r="M72" s="11" t="s">
+      <c r="M72" s="9" t="s">
         <v>38</v>
       </c>
       <c r="N72" s="1"/>
@@ -3922,7 +3959,7 @@
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S72" s="1"/>
     </row>
@@ -3931,16 +3968,16 @@
         <v>32</v>
       </c>
       <c r="B73" s="1">
-        <v>9</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>46</v>
+        <v>8</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="D73" s="1">
         <v>2010</v>
       </c>
-      <c r="E73" s="10" t="s">
-        <v>63</v>
+      <c r="E73" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -3949,7 +3986,7 @@
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
-      <c r="M73" s="11" t="s">
+      <c r="M73" s="9" t="s">
         <v>38</v>
       </c>
       <c r="N73" s="1"/>
@@ -3957,7 +3994,7 @@
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S73" s="1"/>
     </row>
@@ -3966,16 +4003,16 @@
         <v>32</v>
       </c>
       <c r="B74" s="1">
-        <v>10</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>48</v>
+        <v>9</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="D74" s="1">
         <v>2010</v>
       </c>
-      <c r="E74" s="10" t="s">
-        <v>64</v>
+      <c r="E74" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -3984,7 +4021,7 @@
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
-      <c r="M74" s="11" t="s">
+      <c r="M74" s="9" t="s">
         <v>38</v>
       </c>
       <c r="N74" s="1"/>
@@ -3992,66 +4029,72 @@
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S74" s="1"/>
+    </row>
+    <row r="75" spans="1:22" ht="47.25">
+      <c r="A75" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B75" s="1">
+        <v>10</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S74" s="1"/>
-    </row>
-    <row r="75" spans="1:22" ht="110.25">
-      <c r="A75" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="1">
-        <v>1</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="N75" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P75" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q75" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T75" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" ht="63">
+      <c r="S75" s="1"/>
+    </row>
+    <row r="76" spans="1:22" ht="110.25">
       <c r="A76" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B76" s="1">
-        <v>2</v>
-      </c>
-      <c r="C76" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>71</v>
+        <v>66</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="Q76" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:22" ht="63">
@@ -4059,106 +4102,112 @@
         <v>65</v>
       </c>
       <c r="B77" s="1">
-        <v>3</v>
-      </c>
-      <c r="C77" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>71</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="Q77" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" ht="78.75">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="63">
       <c r="A78" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B78" s="1">
+        <v>3</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="78.75">
+      <c r="A79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1">
         <v>4</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C79" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E79" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="N78" s="2" t="s">
+      <c r="N79" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="P78" s="2" t="s">
+      <c r="P79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q78" s="2" t="b">
+      <c r="Q79" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T78" s="2" t="s">
+      <c r="T79" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:22" s="13" customFormat="1" ht="78.75">
-      <c r="A79" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B79" s="1">
-        <v>1</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D79" s="13">
-        <v>2020</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S79" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="U79" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="V79" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" ht="31.5">
+    <row r="80" spans="1:22" ht="78.75">
       <c r="A80" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B80" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D80" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E80" s="12" t="s">
-        <v>119</v>
+        <v>2020</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>121</v>
+        <v>87</v>
+      </c>
+      <c r="U80" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:22" ht="31.5">
@@ -4166,123 +4215,117 @@
         <v>83</v>
       </c>
       <c r="B81" s="1">
-        <v>3</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="D81" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>94</v>
+        <v>2019</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U81" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" ht="78.75">
+        <v>120</v>
+      </c>
+      <c r="U81" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" ht="31.5">
       <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B82" s="1">
-        <v>4</v>
-      </c>
-      <c r="C82" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="2">
         <v>2018</v>
       </c>
-      <c r="E82" s="12" t="s">
-        <v>93</v>
+      <c r="E82" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U82" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V82" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22">
+        <v>88</v>
+      </c>
+      <c r="U82" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" ht="78.75">
       <c r="A83" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>5</v>
-      </c>
-      <c r="C83" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="2">
-        <v>2016</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>95</v>
+        <v>2018</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="U83" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" ht="31.5">
+        <v>92</v>
+      </c>
+      <c r="U83" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22">
       <c r="A84" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B84" s="1">
+        <v>5</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2">
+        <v>2016</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U84" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="31.5">
+      <c r="A85" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85" s="1">
         <v>6</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C85" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D85" s="2">
         <v>2015</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E85" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="S84" s="2" t="s">
+      <c r="S85" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="U84" s="12" t="s">
+      <c r="U85" s="10" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" ht="78.75">
-      <c r="A85" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B85" s="1">
-        <v>1</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D85" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R85" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S85" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U85" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="V85" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:22" ht="78.75">
@@ -4290,110 +4333,141 @@
         <v>99</v>
       </c>
       <c r="B86" s="1">
-        <v>2</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="D86" s="2">
         <v>2018</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U86" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="78.75">
+      <c r="A87" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B87" s="1">
+        <v>2</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D87" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E87" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="R86" s="2" t="s">
+      <c r="R87" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="S86" s="2" t="s">
+      <c r="S87" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="U86" s="12" t="s">
+      <c r="U87" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="V86" s="2" t="s">
+      <c r="V87" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="87" spans="1:22" ht="31.5">
-      <c r="A87" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B87" s="1">
-        <v>1</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="R87" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S87" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:22" ht="31.5">
       <c r="A88" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B88" s="1">
-        <v>2</v>
-      </c>
-      <c r="C88" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="2">
         <v>2019</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="E88" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S88" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22">
+      <c r="A89" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B89" s="1">
+        <v>2</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E89" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="R88" s="2" t="s">
+      <c r="R89" s="2" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:K17">
-    <sortCondition ref="B7:B17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:K19">
+    <sortCondition ref="B9:B19"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J36" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
-    <hyperlink ref="K5" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
-    <hyperlink ref="K6" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
-    <hyperlink ref="K7" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
-    <hyperlink ref="K8" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
-    <hyperlink ref="K9" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
-    <hyperlink ref="K10" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
-    <hyperlink ref="K11" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
-    <hyperlink ref="K12" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
-    <hyperlink ref="K13" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
-    <hyperlink ref="K15" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
-    <hyperlink ref="K14" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
+    <hyperlink ref="K7" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
+    <hyperlink ref="K8" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
+    <hyperlink ref="K9" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
+    <hyperlink ref="K10" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
+    <hyperlink ref="K11" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
+    <hyperlink ref="K12" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
+    <hyperlink ref="K13" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
+    <hyperlink ref="K14" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
+    <hyperlink ref="K15" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
+    <hyperlink ref="K17" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
+    <hyperlink ref="K16" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
     <hyperlink ref="R26" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
     <hyperlink ref="S26" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
     <hyperlink ref="K27" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
     <hyperlink ref="R28" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W45" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R57" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R56" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R55" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R52" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R46" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
-    <hyperlink ref="K4" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
-    <hyperlink ref="J4" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
-    <hyperlink ref="R42" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
-    <hyperlink ref="R44" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
-    <hyperlink ref="R43" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
-    <hyperlink ref="K3" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
-    <hyperlink ref="K2" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
+    <hyperlink ref="W46" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R58" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R57" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R56" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R53" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R47" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="K6" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
+    <hyperlink ref="J6" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
+    <hyperlink ref="R43" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
+    <hyperlink ref="R45" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
+    <hyperlink ref="R44" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="K5" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
+    <hyperlink ref="K4" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
+    <hyperlink ref="K2" r:id="rId30" xr:uid="{2A765B15-3B0B-4BAF-95AD-4FC851D8343D}"/>
+    <hyperlink ref="K3" r:id="rId31" xr:uid="{7D61F22C-7D64-491C-BA97-44A28B404208}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId30"/>
+  <pageSetup orientation="portrait" r:id="rId32"/>
 </worksheet>
 </file>
--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABCC2C5-9F3E-404E-81D4-C40A2BD4E3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B123D1-3940-4413-B6BD-E412C0053BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="3300" windowWidth="29040" windowHeight="17790" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="343">
   <si>
     <t>authors</t>
   </si>
@@ -1042,6 +1042,27 @@
   </si>
   <si>
     <t>Reproducible Parameter Estimation Framework for Integrated Hydrological Models</t>
+  </si>
+  <si>
+    <t>Fort Collins, CO, Unitied States</t>
+  </si>
+  <si>
+    <t>June, 2023</t>
+  </si>
+  <si>
+    <t>Uncertainty Quantification of Salinity Transport Simulation for Integrated Hydrological Models</t>
+  </si>
+  <si>
+    <t>2023 UCOWR Annual Water Resources Conference</t>
+  </si>
+  <si>
+    <t>Exploring the Controlling Factors on the Process of Salt Transport within the Upper Colorado River Basin Using APEX-MODFLOW-Salt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park, S., Jeong, J., Motter, E., Xiang, Z., and Bailey, R. </t>
+  </si>
+  <si>
+    <t>Xiang, Z., Bailey, R., Park, S., and Jeong, J.</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W89"/>
+  <dimension ref="A1:W91"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -2904,7 +2925,7 @@
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
     </row>
-    <row r="40" spans="1:23" ht="31.5">
+    <row r="40" spans="1:23" ht="63">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
@@ -2912,13 +2933,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -2928,13 +2949,13 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="N40" s="1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="O40" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q40" s="1" t="b">
         <v>0</v>
@@ -2942,7 +2963,7 @@
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:23" ht="31.5">
+    <row r="41" spans="1:23" ht="63">
       <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,13 +2971,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2965,15 +2986,14 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
       <c r="N41" s="1" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="O41" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="Q41" s="1" t="b">
         <v>0</v>
@@ -2981,7 +3001,7 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="63">
+    <row r="42" spans="1:23" ht="31.5">
       <c r="A42" s="1" t="s">
         <v>22</v>
       </c>
@@ -2989,13 +3009,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -3004,15 +3024,14 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
       <c r="N42" s="1" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="O42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="Q42" s="1" t="b">
         <v>0</v>
@@ -3020,7 +3039,7 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="47.25">
+    <row r="43" spans="1:23" ht="31.5">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -3028,13 +3047,13 @@
         <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -3045,23 +3064,21 @@
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="O43" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="Q43" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="R43" s="1"/>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:23" ht="31.5">
+    <row r="44" spans="1:23" ht="63">
       <c r="A44" s="1" t="s">
         <v>22</v>
       </c>
@@ -3069,13 +3086,13 @@
         <v>5</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -3086,23 +3103,21 @@
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="O44" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="Q44" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>292</v>
-      </c>
+      <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:23" ht="31.5">
+    <row r="45" spans="1:23" ht="47.25">
       <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
@@ -3110,13 +3125,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>284</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -3139,11 +3154,11 @@
         <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:23" ht="78.75">
+    <row r="46" spans="1:23" ht="31.5">
       <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
@@ -3151,31 +3166,40 @@
         <v>7</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>189</v>
+        <v>291</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="O46" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q46" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W46" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" ht="47.25">
+        <v>290</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q46" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="S46" s="1"/>
+    </row>
+    <row r="47" spans="1:23" ht="31.5">
       <c r="A47" s="1" t="s">
         <v>22</v>
       </c>
@@ -3183,31 +3207,40 @@
         <v>8</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>197</v>
+        <v>325</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="O47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q47" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R47" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" ht="31.5">
+        <v>288</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q47" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="S47" s="1"/>
+    </row>
+    <row r="48" spans="1:23" ht="78.75">
       <c r="A48" s="1" t="s">
         <v>22</v>
       </c>
@@ -3215,28 +3248,31 @@
         <v>9</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="Q48" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" ht="31.5">
+      <c r="W48" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="47.25">
       <c r="A49" s="1" t="s">
         <v>22</v>
       </c>
@@ -3244,25 +3280,28 @@
         <v>10</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Q49" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="31.5">
@@ -3273,13 +3312,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>196</v>
@@ -3302,13 +3341,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>196</v>
@@ -3331,13 +3370,13 @@
         <v>13</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>196</v>
@@ -3360,28 +3399,25 @@
         <v>14</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="O53" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="Q53" s="2" t="b">
         <v>0</v>
-      </c>
-      <c r="R53" s="6" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="31.5">
@@ -3392,28 +3428,28 @@
         <v>15</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="O54" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="47.25">
+    <row r="55" spans="1:18" ht="31.5">
       <c r="A55" s="1" t="s">
         <v>22</v>
       </c>
@@ -3421,28 +3457,31 @@
         <v>16</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O55" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Q55" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" ht="78.75">
+      <c r="R55" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="31.5">
       <c r="A56" s="1" t="s">
         <v>22</v>
       </c>
@@ -3450,31 +3489,28 @@
         <v>17</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q56" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="R56" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" ht="78.75">
+    </row>
+    <row r="57" spans="1:18" ht="47.25">
       <c r="A57" s="1" t="s">
         <v>22</v>
       </c>
@@ -3482,28 +3518,25 @@
         <v>18</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>300</v>
+        <v>218</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q57" s="2" t="b">
         <v>0</v>
-      </c>
-      <c r="R57" s="6" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="78.75">
@@ -3514,13 +3547,13 @@
         <v>19</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>221</v>
@@ -3535,10 +3568,10 @@
         <v>0</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" ht="31.5">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="78.75">
       <c r="A59" s="1" t="s">
         <v>22</v>
       </c>
@@ -3546,28 +3579,31 @@
         <v>20</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="O59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="Q59" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" ht="47.25">
+      <c r="R59" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="78.75">
       <c r="A60" s="1" t="s">
         <v>22</v>
       </c>
@@ -3575,25 +3611,28 @@
         <v>21</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="O60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="31.5">
@@ -3604,28 +3643,28 @@
         <v>22</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="O61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="Q61" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="63">
+    <row r="62" spans="1:18" ht="47.25">
       <c r="A62" s="1" t="s">
         <v>22</v>
       </c>
@@ -3633,28 +3672,28 @@
         <v>23</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="O62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="Q62" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="47.25">
+    <row r="63" spans="1:18" ht="31.5">
       <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
@@ -3662,28 +3701,28 @@
         <v>24</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q63" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="31.5">
+    <row r="64" spans="1:18" ht="63">
       <c r="A64" s="1" t="s">
         <v>22</v>
       </c>
@@ -3691,118 +3730,106 @@
         <v>25</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q64" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="47.25">
+      <c r="A65" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="1">
+        <v>26</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="O65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q65" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="31.5">
+      <c r="A66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="1">
+        <v>27</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D66" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="N64" s="2" t="s">
+      <c r="N66" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="O64" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P64" s="2" t="s">
+      <c r="O66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="Q64" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" s="19" customFormat="1">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="E65" s="18"/>
-    </row>
-    <row r="66" spans="1:22" ht="47.25">
-      <c r="A66" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B66" s="1">
-        <v>1</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D66" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="R66" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S66" s="1"/>
-    </row>
-    <row r="67" spans="1:22" ht="47.25">
-      <c r="A67" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B67" s="1">
-        <v>2</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="1">
-        <v>2013</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S67" s="1"/>
-    </row>
-    <row r="68" spans="1:22" ht="47.25">
+      <c r="Q66" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" s="19" customFormat="1">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="E67" s="18"/>
+    </row>
+    <row r="68" spans="1:20" ht="47.25">
       <c r="A68" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B68" s="1">
-        <v>3</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D68" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>58</v>
+        <v>2014</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -3811,7 +3838,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
-      <c r="M68" s="9" t="s">
+      <c r="M68" s="1" t="s">
         <v>38</v>
       </c>
       <c r="N68" s="1"/>
@@ -3819,25 +3846,25 @@
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="S68" s="1"/>
     </row>
-    <row r="69" spans="1:22" ht="47.25">
+    <row r="69" spans="1:20" ht="47.25">
       <c r="A69" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B69" s="1">
-        <v>4</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D69" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>59</v>
+        <v>2013</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -3846,33 +3873,33 @@
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
-      <c r="M69" s="9" t="s">
-        <v>38</v>
+      <c r="M69" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="S69" s="1"/>
     </row>
-    <row r="70" spans="1:22" ht="47.25">
+    <row r="70" spans="1:20" ht="47.25">
       <c r="A70" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B70" s="1">
-        <v>5</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>55</v>
+        <v>3</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D70" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>40</v>
+        <v>2012</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -3889,25 +3916,25 @@
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="S70" s="1"/>
     </row>
-    <row r="71" spans="1:22" ht="47.25">
+    <row r="71" spans="1:20" ht="47.25">
       <c r="A71" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B71" s="1">
-        <v>6</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>56</v>
+        <v>4</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="D71" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>60</v>
+        <v>2012</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -3924,25 +3951,25 @@
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S71" s="1"/>
     </row>
-    <row r="72" spans="1:22" ht="47.25">
+    <row r="72" spans="1:20" ht="47.25">
       <c r="A72" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B72" s="1">
-        <v>7</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="D72" s="1">
         <v>2010</v>
       </c>
-      <c r="E72" s="8" t="s">
-        <v>61</v>
+      <c r="E72" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -3959,25 +3986,25 @@
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S72" s="1"/>
     </row>
-    <row r="73" spans="1:22" ht="47.25">
+    <row r="73" spans="1:20" ht="47.25">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B73" s="1">
-        <v>8</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="D73" s="1">
         <v>2010</v>
       </c>
-      <c r="E73" s="8" t="s">
-        <v>62</v>
+      <c r="E73" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -3994,25 +4021,25 @@
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" spans="1:22" ht="47.25">
+    <row r="74" spans="1:20" ht="47.25">
       <c r="A74" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B74" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D74" s="1">
         <v>2010</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -4029,25 +4056,25 @@
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" spans="1:22" ht="47.25">
+    <row r="75" spans="1:20" ht="47.25">
       <c r="A75" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B75" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D75" s="1">
         <v>2010</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -4064,86 +4091,98 @@
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S75" s="1"/>
+    </row>
+    <row r="76" spans="1:20" ht="47.25">
+      <c r="A76" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B76" s="1">
+        <v>9</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S76" s="1"/>
+    </row>
+    <row r="77" spans="1:20" ht="47.25">
+      <c r="A77" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B77" s="1">
+        <v>10</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S75" s="1"/>
-    </row>
-    <row r="76" spans="1:22" ht="110.25">
-      <c r="A76" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B76" s="1">
-        <v>1</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N76" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P76" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q76" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T76" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" ht="63">
-      <c r="A77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="1">
-        <v>2</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N77" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P77" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q77" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T77" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" ht="63">
+      <c r="S77" s="1"/>
+    </row>
+    <row r="78" spans="1:20" ht="110.25">
       <c r="A78" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B78" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>74</v>
@@ -4152,24 +4191,24 @@
         <v>0</v>
       </c>
       <c r="T78" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" ht="78.75">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="63">
       <c r="A79" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B79" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>73</v>
@@ -4181,251 +4220,309 @@
         <v>1</v>
       </c>
       <c r="T79" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="63">
+      <c r="A80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1">
+        <v>3</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="78.75">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1">
+        <v>4</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q81" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:22" ht="78.75">
-      <c r="A80" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80" s="1">
-        <v>1</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D80" s="2">
-        <v>2020</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U80" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" ht="31.5">
-      <c r="A81" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B81" s="1">
-        <v>2</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D81" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="S81" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U81" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" ht="31.5">
+    <row r="82" spans="1:22" ht="78.75">
       <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B82" s="1">
-        <v>3</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="D82" s="2">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U82" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" ht="78.75">
+        <v>87</v>
+      </c>
+      <c r="U82" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" ht="31.5">
       <c r="A83" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D83" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="U83" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" ht="31.5">
       <c r="A84" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B84" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="U84" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="85" spans="1:22" ht="31.5">
+    <row r="85" spans="1:22" ht="78.75">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B85" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="S85" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U85" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22">
+      <c r="A86" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B86" s="1">
+        <v>5</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="2">
+        <v>2016</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U86" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="31.5">
+      <c r="A87" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B87" s="1">
+        <v>6</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="2">
         <v>2015</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E87" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="S85" s="2" t="s">
+      <c r="S87" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="U85" s="10" t="s">
+      <c r="U87" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="86" spans="1:22" ht="78.75">
-      <c r="A86" s="1" t="s">
+    <row r="88" spans="1:22" ht="78.75">
+      <c r="A88" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B86" s="1">
-        <v>1</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D86" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R86" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S86" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U86" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="V86" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22" ht="78.75">
-      <c r="A87" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B87" s="1">
-        <v>2</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D87" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="R87" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="S87" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U87" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="V87" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22" ht="31.5">
-      <c r="A88" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="B88" s="1">
         <v>1</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D88" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>111</v>
+        <v>2018</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22">
+        <v>102</v>
+      </c>
+      <c r="U88" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" ht="78.75">
       <c r="A89" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B89" s="1">
         <v>2</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="R89" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S89" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U89" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="V89" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" ht="31.5">
+      <c r="A90" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90" s="1">
+        <v>1</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D90" s="2">
         <v>2019</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E90" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="R90" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S90" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22">
+      <c r="A91" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="1">
+        <v>2</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E91" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="R89" s="2" t="s">
+      <c r="R91" s="2" t="s">
         <v>115</v>
       </c>
     </row>
@@ -4451,17 +4548,17 @@
     <hyperlink ref="S26" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
     <hyperlink ref="K27" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
     <hyperlink ref="R28" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W46" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R58" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R57" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R56" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R53" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R47" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="W48" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R60" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R59" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R58" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R55" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R49" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
     <hyperlink ref="K6" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
     <hyperlink ref="J6" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
-    <hyperlink ref="R43" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
-    <hyperlink ref="R45" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
-    <hyperlink ref="R44" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="R45" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
+    <hyperlink ref="R47" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
+    <hyperlink ref="R46" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
     <hyperlink ref="K5" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
     <hyperlink ref="K4" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
     <hyperlink ref="K2" r:id="rId30" xr:uid="{2A765B15-3B0B-4BAF-95AD-4FC851D8343D}"/>

--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B123D1-3940-4413-B6BD-E412C0053BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60AE455-8009-4ADB-AD80-5E59871BA8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="347">
   <si>
     <t>authors</t>
   </si>
@@ -1063,6 +1063,18 @@
   </si>
   <si>
     <t>Xiang, Z., Bailey, R., Park, S., and Jeong, J.</t>
+  </si>
+  <si>
+    <t>Han, H., Abitew, T.A., Park, S., Green, C.H. and Jeong, J.</t>
+  </si>
+  <si>
+    <t>Spatio-Temporal Evaluation of Satellite-based Precipitation Products in the Colorado River Basin. Journal of Hydrometeorology</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1175/JHM-D-23-0003.1</t>
+  </si>
+  <si>
+    <t>10.1175/JHM-D-23-0003.1</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W91"/>
+  <dimension ref="A1:W92"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -1677,29 +1689,29 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="D2" s="1">
         <v>2023</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>181</v>
       </c>
       <c r="G2" s="1">
-        <v>165</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1">
-        <v>105723</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H2" s="1">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1721,29 +1733,29 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="D3" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>326</v>
+        <v>181</v>
       </c>
       <c r="G3" s="1">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1">
-        <v>531</v>
+        <v>105723</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1757,7 +1769,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:23" ht="63">
+    <row r="4" spans="1:23" ht="47.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1765,27 +1777,29 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="D4" s="1">
         <v>2022</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>273</v>
+        <v>326</v>
       </c>
       <c r="G4" s="1">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>531</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1799,7 +1813,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:23" ht="47.25">
+    <row r="5" spans="1:23" ht="63">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1807,27 +1821,27 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="D5" s="1">
         <v>2022</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G5" s="1">
-        <v>610</v>
+        <v>146</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1849,29 +1863,27 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D6" s="1">
         <v>2022</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>272</v>
       </c>
       <c r="G6" s="1">
-        <v>606</v>
-      </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="1">
-        <v>127449</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>279</v>
+        <v>610</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1893,28 +1905,29 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>132</v>
+        <v>277</v>
       </c>
       <c r="D7" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>128</v>
+        <v>276</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>129</v>
+        <v>272</v>
       </c>
       <c r="G7" s="1">
-        <v>134</v>
-      </c>
-      <c r="I7" s="17">
-        <v>105093</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>130</v>
+        <v>606</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="1">
+        <v>127449</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>131</v>
+        <v>278</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1924,6 +1937,9 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
     </row>
     <row r="8" spans="1:23" ht="47.25">
       <c r="A8" s="1" t="s">
@@ -1933,29 +1949,28 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D8" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="1">
         <v>134</v>
       </c>
-      <c r="G8" s="1">
-        <v>32</v>
-      </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="4" t="s">
-        <v>138</v>
+      <c r="I8" s="17">
+        <v>105093</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1966,7 +1981,7 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:23" ht="63">
+    <row r="9" spans="1:23" ht="47.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1974,28 +1989,29 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D9" s="1">
         <v>2020</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>139</v>
+      <c r="E9" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G9" s="1">
-        <v>745</v>
-      </c>
-      <c r="I9" s="17">
-        <v>140933</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>141</v>
+        <v>32</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2006,7 +2022,7 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:23" ht="47.25">
+    <row r="10" spans="1:23" ht="63">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -2014,29 +2030,28 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" s="1">
         <v>2020</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>143</v>
+      <c r="E10" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="1">
-        <v>503</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>148</v>
+        <v>745</v>
+      </c>
+      <c r="I10" s="17">
+        <v>140933</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2055,28 +2070,29 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D11" s="1">
         <v>2020</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="G11" s="1">
-        <v>126</v>
-      </c>
-      <c r="I11" s="17">
-        <v>104660</v>
+        <v>10</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="1">
+        <v>503</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2095,28 +2111,28 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1">
         <v>2020</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="G12" s="1">
-        <v>706</v>
+        <v>126</v>
       </c>
       <c r="I12" s="17">
-        <v>135702</v>
+        <v>104660</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -2135,28 +2151,28 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D13" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G13" s="1">
-        <v>9</v>
+        <v>706</v>
       </c>
       <c r="I13" s="17">
-        <v>100260</v>
+        <v>135702</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2175,29 +2191,28 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D14" s="1">
         <v>2019</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G14" s="1">
-        <v>11</v>
-      </c>
-      <c r="H14" s="17">
-        <v>1681</v>
-      </c>
-      <c r="I14" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="I14" s="17">
+        <v>100260</v>
+      </c>
       <c r="J14" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2216,29 +2231,29 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="D15" s="1">
         <v>2019</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="4" t="s">
-        <v>173</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="17">
+        <v>1681</v>
+      </c>
+      <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2257,29 +2272,29 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="D16" s="1">
         <v>2019</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G16" s="1">
-        <v>111</v>
+        <v>169</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="12" t="s">
-        <v>182</v>
+      <c r="I16" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2298,29 +2313,29 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D17" s="1">
         <v>2019</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G17" s="1">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="12" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2331,26 +2346,46 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" s="16" customFormat="1">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
+    <row r="18" spans="1:19" ht="47.25">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G18" s="1">
+        <v>64</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
     </row>
     <row r="19" spans="1:19" s="16" customFormat="1">
       <c r="A19" s="13"/>
@@ -2373,232 +2408,220 @@
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
     </row>
-    <row r="20" spans="1:19" ht="47.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:19" s="16" customFormat="1">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+    </row>
+    <row r="21" spans="1:19" ht="47.25">
+      <c r="A21" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-    </row>
-    <row r="21" spans="1:19" s="23" customFormat="1">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="22"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="22"/>
-    </row>
-    <row r="22" spans="1:19" s="25" customFormat="1">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-    </row>
-    <row r="23" spans="1:19" s="23" customFormat="1">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-    </row>
-    <row r="24" spans="1:19">
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-    </row>
-    <row r="25" spans="1:19" s="19" customFormat="1">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="18"/>
-    </row>
-    <row r="26" spans="1:19" ht="47.25">
-      <c r="A26" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="S26" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="63">
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+    </row>
+    <row r="22" spans="1:19" s="23" customFormat="1">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
+    </row>
+    <row r="23" spans="1:19" s="25" customFormat="1">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
+    </row>
+    <row r="24" spans="1:19" s="23" customFormat="1">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="22"/>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+    </row>
+    <row r="26" spans="1:19" s="19" customFormat="1">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+    </row>
+    <row r="27" spans="1:19" ht="47.25">
       <c r="A27" s="1" t="s">
         <v>251</v>
       </c>
       <c r="B27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D27" s="1">
         <v>2019</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="3" t="s">
-        <v>262</v>
-      </c>
+      <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
+      <c r="R27" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="S27" s="6" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="28" spans="1:19" ht="63">
       <c r="A28" s="1" t="s">
         <v>251</v>
       </c>
       <c r="B28" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D28" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="K28" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
         <v>259</v>
@@ -2607,71 +2630,71 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-      <c r="R28" s="3" t="s">
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+    </row>
+    <row r="29" spans="1:19" ht="63">
+      <c r="A29" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B29" s="1">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="S28" s="1"/>
-    </row>
-    <row r="29" spans="1:19" s="19" customFormat="1">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="18"/>
-    </row>
-    <row r="30" spans="1:19" ht="47.25">
-      <c r="A30" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2022</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="1"/>
+      <c r="S29" s="1"/>
+    </row>
+    <row r="30" spans="1:19" s="19" customFormat="1">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="21"/>
+      <c r="S30" s="18"/>
     </row>
     <row r="31" spans="1:19" ht="47.25">
       <c r="A31" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B31" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>322</v>
@@ -2680,7 +2703,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -2690,7 +2713,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -2699,21 +2722,21 @@
       <c r="R31" s="3"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19" ht="29.25">
+    <row r="32" spans="1:19" ht="47.25">
       <c r="A32" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B32" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="D32" s="1">
         <v>2022</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -2723,7 +2746,7 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
@@ -2732,21 +2755,21 @@
       <c r="R32" s="3"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:23" ht="29.25">
+    <row r="33" spans="1:19" ht="29.25">
       <c r="A33" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B33" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D33" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -2756,7 +2779,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -2765,12 +2788,22 @@
       <c r="R33" s="3"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:23">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="7"/>
+    <row r="34" spans="1:19" ht="29.25">
+      <c r="A34" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>296</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -2778,7 +2811,9 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+      <c r="M34" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -2786,161 +2821,152 @@
       <c r="R34" s="3"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:23" s="19" customFormat="1">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
-      <c r="Q35" s="18"/>
-      <c r="R35" s="21"/>
-      <c r="S35" s="18"/>
-    </row>
-    <row r="36" spans="1:23" ht="47.25">
-      <c r="A36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="1">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="S36" s="1"/>
-    </row>
-    <row r="37" spans="1:23" ht="47.25">
+    <row r="35" spans="1:19">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="1"/>
+    </row>
+    <row r="36" spans="1:19" s="19" customFormat="1">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="21"/>
+      <c r="S36" s="18"/>
+    </row>
+    <row r="37" spans="1:19" ht="47.25">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B37" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" s="1">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="L37" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
+      <c r="R37" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:23" s="19" customFormat="1">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="1"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-    </row>
-    <row r="40" spans="1:23" ht="63">
-      <c r="A40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" s="1">
-        <v>1</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>338</v>
-      </c>
+    <row r="38" spans="1:19" ht="47.25">
+      <c r="A38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="1">
+        <v>2</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+    </row>
+    <row r="39" spans="1:19" s="19" customFormat="1">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="1"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2948,36 +2974,28 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
-      <c r="N40" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="O40" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q40" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:23" ht="63">
+    <row r="41" spans="1:19" ht="63">
       <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>337</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -3001,21 +3019,21 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="31.5">
+    <row r="42" spans="1:19" ht="63">
       <c r="A42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B42" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -3025,13 +3043,13 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="N42" s="1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="O42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q42" s="1" t="b">
         <v>0</v>
@@ -3039,21 +3057,21 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="31.5">
+    <row r="43" spans="1:19" ht="31.5">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -3062,15 +3080,14 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
       <c r="N43" s="1" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="O43" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="Q43" s="1" t="b">
         <v>0</v>
@@ -3078,21 +3095,21 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:23" ht="63">
+    <row r="44" spans="1:19" ht="31.5">
       <c r="A44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -3103,13 +3120,13 @@
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="O44" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q44" s="1" t="b">
         <v>0</v>
@@ -3117,21 +3134,21 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:23" ht="47.25">
+    <row r="45" spans="1:19" ht="63">
       <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -3142,37 +3159,35 @@
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="O45" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="Q45" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="R45" s="1"/>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:23" ht="31.5">
+    <row r="46" spans="1:19" ht="47.25">
       <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>284</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -3195,25 +3210,25 @@
         <v>0</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" spans="1:23" ht="31.5">
+    <row r="47" spans="1:19" ht="31.5">
       <c r="A47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>284</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -3236,118 +3251,130 @@
         <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:23" ht="78.75">
+    <row r="48" spans="1:19" ht="31.5">
       <c r="A48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B48" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>189</v>
+        <v>325</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="O48" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q48" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W48" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="47.25">
+        <v>288</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q48" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="S48" s="1"/>
+    </row>
+    <row r="49" spans="1:23" ht="78.75">
       <c r="A49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B49" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="Q49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="R49" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="31.5">
+      <c r="W49" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" ht="47.25">
       <c r="A50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B50" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Q50" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" ht="31.5">
+      <c r="R50" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" ht="31.5">
       <c r="A51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>196</v>
@@ -3362,21 +3389,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="31.5">
+    <row r="52" spans="1:23" ht="31.5">
       <c r="A52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>196</v>
@@ -3391,21 +3418,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="31.5">
+    <row r="53" spans="1:23" ht="31.5">
       <c r="A53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>196</v>
@@ -3420,21 +3447,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="31.5">
+    <row r="54" spans="1:23" ht="31.5">
       <c r="A54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>196</v>
@@ -3449,82 +3476,82 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="31.5">
+    <row r="55" spans="1:23" ht="31.5">
       <c r="A55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B55" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="O55" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="Q55" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="R55" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" ht="31.5">
+    </row>
+    <row r="56" spans="1:23" ht="31.5">
       <c r="A56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B56" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Q56" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" ht="47.25">
+      <c r="R56" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" ht="31.5">
       <c r="A57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B57" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>215</v>
@@ -3539,53 +3566,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="78.75">
+    <row r="58" spans="1:23" ht="47.25">
       <c r="A58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B58" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="R58" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" ht="78.75">
+    </row>
+    <row r="59" spans="1:23" ht="78.75">
       <c r="A59" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B59" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>221</v>
@@ -3600,24 +3624,24 @@
         <v>0</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" ht="78.75">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" ht="78.75">
       <c r="A60" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B60" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>221</v>
@@ -3632,169 +3656,172 @@
         <v>0</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="31.5">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" ht="78.75">
       <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B61" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="O61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" ht="47.25">
+      <c r="R61" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="31.5">
       <c r="A62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B62" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>232</v>
+        <v>27</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="Q62" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="31.5">
+    <row r="63" spans="1:23" ht="47.25">
       <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B63" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="O63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="63">
+    <row r="64" spans="1:23" ht="31.5">
       <c r="A64" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="O64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="Q64" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="47.25">
+    <row r="65" spans="1:20" ht="63">
       <c r="A65" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="O65" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="Q65" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="31.5">
+    <row r="66" spans="1:20" ht="47.25">
       <c r="A66" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>243</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>240</v>
@@ -3809,62 +3836,56 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:20" s="19" customFormat="1">
-      <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="E67" s="18"/>
-    </row>
-    <row r="68" spans="1:20" ht="47.25">
-      <c r="A68" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D68" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S68" s="1"/>
+    <row r="67" spans="1:20" ht="31.5">
+      <c r="A67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="1">
+        <v>27</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="O67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q67" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" s="19" customFormat="1">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="E68" s="18"/>
     </row>
     <row r="69" spans="1:20" ht="47.25">
       <c r="A69" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B69" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D69" s="1">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -3874,14 +3895,14 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S69" s="1"/>
     </row>
@@ -3890,16 +3911,16 @@
         <v>32</v>
       </c>
       <c r="B70" s="1">
-        <v>3</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D70" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>58</v>
+        <v>2013</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -3908,15 +3929,15 @@
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="9" t="s">
-        <v>38</v>
+      <c r="M70" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="S70" s="1"/>
     </row>
@@ -3925,16 +3946,16 @@
         <v>32</v>
       </c>
       <c r="B71" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D71" s="1">
         <v>2012</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -3951,7 +3972,7 @@
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S71" s="1"/>
     </row>
@@ -3960,16 +3981,16 @@
         <v>32</v>
       </c>
       <c r="B72" s="1">
-        <v>5</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="D72" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>40</v>
+        <v>2012</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -3986,7 +4007,7 @@
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="S72" s="1"/>
     </row>
@@ -3995,16 +4016,16 @@
         <v>32</v>
       </c>
       <c r="B73" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D73" s="1">
         <v>2010</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -4021,7 +4042,7 @@
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="S73" s="1"/>
     </row>
@@ -4030,16 +4051,16 @@
         <v>32</v>
       </c>
       <c r="B74" s="1">
-        <v>7</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="D74" s="1">
         <v>2010</v>
       </c>
-      <c r="E74" s="8" t="s">
-        <v>61</v>
+      <c r="E74" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -4056,7 +4077,7 @@
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S74" s="1"/>
     </row>
@@ -4065,16 +4086,16 @@
         <v>32</v>
       </c>
       <c r="B75" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D75" s="1">
         <v>2010</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -4091,7 +4112,7 @@
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S75" s="1"/>
     </row>
@@ -4100,16 +4121,16 @@
         <v>32</v>
       </c>
       <c r="B76" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D76" s="1">
         <v>2010</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -4126,7 +4147,7 @@
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S76" s="1"/>
     </row>
@@ -4135,16 +4156,16 @@
         <v>32</v>
       </c>
       <c r="B77" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D77" s="1">
         <v>2010</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -4161,66 +4182,72 @@
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
       <c r="R77" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S77" s="1"/>
+    </row>
+    <row r="78" spans="1:20" ht="47.25">
+      <c r="A78" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B78" s="1">
+        <v>10</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D78" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1"/>
+      <c r="R78" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S77" s="1"/>
-    </row>
-    <row r="78" spans="1:20" ht="110.25">
-      <c r="A78" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B78" s="1">
-        <v>1</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N78" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P78" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q78" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T78" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" ht="63">
+      <c r="S78" s="1"/>
+    </row>
+    <row r="79" spans="1:20" ht="110.25">
       <c r="A79" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B79" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="Q79" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="63">
@@ -4228,106 +4255,112 @@
         <v>65</v>
       </c>
       <c r="B80" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="Q80" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" ht="78.75">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="63">
       <c r="A81" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B81" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="Q81" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:22" ht="78.75">
       <c r="A82" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B82" s="1">
+        <v>4</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q82" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D82" s="2">
-        <v>2020</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="S82" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U82" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="V82" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" ht="31.5">
+      <c r="T82" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" ht="78.75">
       <c r="A83" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>2</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>126</v>
+        <v>1</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="D83" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U83" s="2" t="s">
-        <v>121</v>
+        <v>87</v>
+      </c>
+      <c r="U83" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:22" ht="31.5">
@@ -4335,30 +4368,30 @@
         <v>83</v>
       </c>
       <c r="B84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D84" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U84" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" ht="78.75">
+        <v>120</v>
+      </c>
+      <c r="U84" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="31.5">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B85" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>8</v>
@@ -4367,91 +4400,85 @@
         <v>2018</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U85" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V85" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22">
+        <v>88</v>
+      </c>
+      <c r="U85" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" ht="78.75">
       <c r="A86" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B86" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="U86" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22" ht="31.5">
+        <v>92</v>
+      </c>
+      <c r="U86" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22">
       <c r="A87" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B87" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="U87" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:22" ht="78.75">
+    <row r="88" spans="1:22" ht="31.5">
       <c r="A88" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B88" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D88" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R88" s="2" t="s">
-        <v>116</v>
+        <v>2015</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="V88" s="2" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:22" ht="78.75">
@@ -4459,59 +4486,65 @@
         <v>99</v>
       </c>
       <c r="B89" s="1">
-        <v>2</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="D89" s="2">
         <v>2018</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R89" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="S89" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U89" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="V89" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" ht="78.75">
+      <c r="A90" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B90" s="1">
+        <v>2</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D90" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E90" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="R89" s="2" t="s">
+      <c r="R90" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="S89" s="2" t="s">
+      <c r="S90" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="U89" s="10" t="s">
+      <c r="U90" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="V89" s="2" t="s">
+      <c r="V90" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="90" spans="1:22" ht="31.5">
-      <c r="A90" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B90" s="1">
-        <v>1</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="R90" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S90" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:22" ht="31.5">
       <c r="A91" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B91" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>8</v>
@@ -4519,52 +4552,76 @@
       <c r="D91" s="2">
         <v>2019</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="R91" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22">
+      <c r="A92" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B92" s="1">
+        <v>2</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E92" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="R91" s="2" t="s">
+      <c r="R92" s="2" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:K19">
-    <sortCondition ref="B9:B19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:K20">
+    <sortCondition ref="B10:B20"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J36" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
-    <hyperlink ref="K7" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
-    <hyperlink ref="K8" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
-    <hyperlink ref="K9" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
-    <hyperlink ref="K10" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
-    <hyperlink ref="K11" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
-    <hyperlink ref="K12" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
-    <hyperlink ref="K13" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
-    <hyperlink ref="K14" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
-    <hyperlink ref="K15" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
-    <hyperlink ref="K17" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
-    <hyperlink ref="K16" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
-    <hyperlink ref="R26" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
-    <hyperlink ref="S26" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
-    <hyperlink ref="K27" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
-    <hyperlink ref="R28" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W48" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R60" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R59" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R58" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R55" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R49" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
-    <hyperlink ref="K6" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
-    <hyperlink ref="J6" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
-    <hyperlink ref="R45" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
-    <hyperlink ref="R47" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
-    <hyperlink ref="R46" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
-    <hyperlink ref="K5" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
-    <hyperlink ref="K4" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
-    <hyperlink ref="K2" r:id="rId30" xr:uid="{2A765B15-3B0B-4BAF-95AD-4FC851D8343D}"/>
-    <hyperlink ref="K3" r:id="rId31" xr:uid="{7D61F22C-7D64-491C-BA97-44A28B404208}"/>
+    <hyperlink ref="J37" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
+    <hyperlink ref="K8" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
+    <hyperlink ref="K9" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
+    <hyperlink ref="K10" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
+    <hyperlink ref="K11" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
+    <hyperlink ref="K12" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
+    <hyperlink ref="K13" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
+    <hyperlink ref="K14" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
+    <hyperlink ref="K15" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
+    <hyperlink ref="K16" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
+    <hyperlink ref="K18" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
+    <hyperlink ref="K17" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
+    <hyperlink ref="R27" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
+    <hyperlink ref="S27" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
+    <hyperlink ref="K28" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
+    <hyperlink ref="R29" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
+    <hyperlink ref="W49" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R61" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R60" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R59" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R56" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R50" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="K7" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
+    <hyperlink ref="J7" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
+    <hyperlink ref="R46" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
+    <hyperlink ref="R48" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
+    <hyperlink ref="R47" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="K6" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
+    <hyperlink ref="K5" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
+    <hyperlink ref="K3" r:id="rId30" xr:uid="{2A765B15-3B0B-4BAF-95AD-4FC851D8343D}"/>
+    <hyperlink ref="K4" r:id="rId31" xr:uid="{7D61F22C-7D64-491C-BA97-44A28B404208}"/>
+    <hyperlink ref="K2" r:id="rId32" xr:uid="{824F3703-A805-4B51-BA57-B640C8BF73D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId32"/>
+  <pageSetup orientation="portrait" r:id="rId33"/>
 </worksheet>
 </file>
--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60AE455-8009-4ADB-AD80-5E59871BA8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA644AFA-6173-4BDC-BA81-E1DF65AEAFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15555" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="348">
   <si>
     <t>authors</t>
   </si>
@@ -1068,13 +1068,16 @@
     <t>Han, H., Abitew, T.A., Park, S., Green, C.H. and Jeong, J.</t>
   </si>
   <si>
-    <t>Spatio-Temporal Evaluation of Satellite-based Precipitation Products in the Colorado River Basin. Journal of Hydrometeorology</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1175/JHM-D-23-0003.1</t>
   </si>
   <si>
     <t>10.1175/JHM-D-23-0003.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatio-Temporal Evaluation of Satellite-based Precipitation Products in the Colorado River Basin. </t>
+  </si>
+  <si>
+    <t>Journal of Hydrometeorology</t>
   </si>
 </sst>
 </file>
@@ -1695,10 +1698,10 @@
         <v>2023</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>181</v>
+        <v>347</v>
       </c>
       <c r="G2" s="1">
         <v>27</v>
@@ -1708,10 +1711,10 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>

--- a/spark-cv/data/pubs.xlsx
+++ b/spark-cv/data/pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA644AFA-6173-4BDC-BA81-E1DF65AEAFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376FF413-9EBE-4526-8CE7-0FA9F142266C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="59610" yWindow="5355" windowWidth="38745" windowHeight="17775" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="362">
   <si>
     <t>authors</t>
   </si>
@@ -1078,13 +1078,55 @@
   </si>
   <si>
     <t>Journal of Hydrometeorology</t>
+  </si>
+  <si>
+    <t>Journal of Contaminant Hydrology</t>
+  </si>
+  <si>
+    <t>Balakrishnan, J.V., Bailey, R.T., Jeong, J., Park, S. and Abitew, T.</t>
+  </si>
+  <si>
+    <t>Quantifying climate change impacts on future water resources and salinity transport in a high semi-arid watershed.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jconhyd.2023.104289</t>
+  </si>
+  <si>
+    <t>10.1016/j.jconhyd.2023.104289</t>
+  </si>
+  <si>
+    <t>DayCent-CUTE: A global sensitivity, auto-calibration, and uncertainty analysis tool for DayCent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.envsoft.2023.105832</t>
+  </si>
+  <si>
+    <t>10.1016/j.envsoft.2023.105832</t>
+  </si>
+  <si>
+    <t>Wang, X., Jeong, J., Park, S., Zhang, X., Gao, J. and Silvero, N.E.</t>
+  </si>
+  <si>
+    <t>Park, S., Abitew, T. and Jeong, J.</t>
+  </si>
+  <si>
+    <t>Enhancement of APEX for simulating soil erosion and salt transport in the Colorado River Basin</t>
+  </si>
+  <si>
+    <t>BREC Report No. 23-01.</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>tool</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1157,6 +1199,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1197,7 +1249,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1272,6 +1324,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1589,31 +1647,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:W92"/>
+  <dimension ref="A1:Y94"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="11" style="2"/>
-    <col min="3" max="3" width="44.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30.375" style="2" customWidth="1"/>
     <col min="4" max="4" width="11" style="2"/>
-    <col min="5" max="5" width="55.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="7.875" style="2" customWidth="1"/>
     <col min="8" max="8" width="9.875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="11" style="2"/>
     <col min="11" max="11" width="35.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="26.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="26" style="2" customWidth="1"/>
-    <col min="14" max="14" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.75" style="2" customWidth="1"/>
     <col min="15" max="15" width="11" style="2"/>
-    <col min="16" max="16" width="23.5" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.375" style="2" customWidth="1"/>
     <col min="17" max="17" width="11" style="2"/>
-    <col min="18" max="18" width="74" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="33.5" style="2" customWidth="1"/>
+    <col min="18" max="18" width="15.875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="11.375" style="2" customWidth="1"/>
     <col min="20" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="31.5">
+    <row r="1" spans="1:25" ht="31.5">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1683,8 +1741,14 @@
       <c r="W1" s="2" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" ht="47.25">
+      <c r="X1" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="47.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1692,29 +1756,29 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D2" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G2" s="1">
-        <v>27</v>
-      </c>
-      <c r="H2" s="1">
-        <v>7</v>
-      </c>
-      <c r="I2" s="1"/>
+        <v>261</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1">
+        <v>104289</v>
+      </c>
       <c r="J2" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1728,7 +1792,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="47.25">
+    <row r="3" spans="1:25" ht="47.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1736,29 +1800,29 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>282</v>
+        <v>356</v>
       </c>
       <c r="D3" s="1">
         <v>2023</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>281</v>
+        <v>353</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="G3" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1">
-        <v>105723</v>
+        <v>105832</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1772,7 +1836,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:23" ht="47.25">
+    <row r="4" spans="1:25" ht="47.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1780,29 +1844,29 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
       <c r="D4" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>301</v>
+        <v>346</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="G4" s="1">
-        <v>81</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1">
-        <v>531</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H4" s="1">
+        <v>7</v>
+      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1816,7 +1880,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:23" ht="63">
+    <row r="5" spans="1:25" ht="47.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1824,27 +1888,29 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="D5" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="G5" s="1">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1">
+        <v>105723</v>
+      </c>
       <c r="J5" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1858,7 +1924,7 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:23" ht="47.25">
+    <row r="6" spans="1:25" ht="63">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1866,27 +1932,29 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="D6" s="1">
         <v>2022</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="G6" s="1">
-        <v>610</v>
+        <v>81</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>531</v>
+      </c>
       <c r="J6" s="1" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1900,7 +1968,7 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:23" ht="47.25">
+    <row r="7" spans="1:25" ht="63">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1908,29 +1976,27 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="D7" s="1">
         <v>2022</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G7" s="1">
-        <v>606</v>
-      </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="1">
-        <v>127449</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>279</v>
+        <v>146</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>278</v>
+        <v>318</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1944,7 +2010,7 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:23" ht="47.25">
+    <row r="8" spans="1:25" ht="47.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1952,28 +2018,27 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="D8" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>128</v>
+        <v>303</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>129</v>
+        <v>272</v>
       </c>
       <c r="G8" s="1">
-        <v>134</v>
-      </c>
-      <c r="I8" s="17">
-        <v>105093</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>130</v>
+        <v>305</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1983,8 +2048,11 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:23" ht="47.25">
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+    </row>
+    <row r="9" spans="1:25" ht="47.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1992,29 +2060,29 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="D9" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="G9" s="1">
-        <v>32</v>
+        <v>606</v>
       </c>
       <c r="H9" s="17"/>
-      <c r="I9" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>135</v>
+      <c r="I9" s="1">
+        <v>127449</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>137</v>
+        <v>278</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2024,8 +2092,11 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-    </row>
-    <row r="10" spans="1:23" ht="63">
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+    </row>
+    <row r="10" spans="1:25" ht="47.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -2033,28 +2104,28 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D10" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>139</v>
+        <v>2021</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G10" s="1">
-        <v>745</v>
+        <v>134</v>
       </c>
       <c r="I10" s="17">
-        <v>140933</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>141</v>
+        <v>105093</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2065,7 +2136,7 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:23" ht="47.25">
+    <row r="11" spans="1:25" ht="78.75">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -2073,29 +2144,29 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D11" s="1">
         <v>2020</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="G11" s="1">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H11" s="17"/>
-      <c r="I11" s="1">
-        <v>503</v>
+      <c r="I11" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>148</v>
+        <v>135</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2106,7 +2177,7 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:23" ht="47.25">
+    <row r="12" spans="1:25" ht="94.5">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -2114,28 +2185,28 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D12" s="1">
         <v>2020</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>149</v>
+      <c r="E12" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="G12" s="1">
-        <v>126</v>
+        <v>745</v>
       </c>
       <c r="I12" s="17">
-        <v>104660</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>152</v>
+        <v>140933</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -2146,7 +2217,7 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:23" ht="47.25">
+    <row r="13" spans="1:25" ht="63">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -2154,28 +2225,29 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D13" s="1">
         <v>2020</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G13" s="1">
-        <v>706</v>
-      </c>
-      <c r="I13" s="17">
-        <v>135702</v>
+        <v>10</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="1">
+        <v>503</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2186,7 +2258,7 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:23" ht="47.25">
+    <row r="14" spans="1:25" ht="63">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -2194,28 +2266,28 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D14" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="G14" s="1">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="I14" s="17">
-        <v>100260</v>
+        <v>104660</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2226,7 +2298,7 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:23" ht="47.25">
+    <row r="15" spans="1:25" ht="63">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -2234,29 +2306,28 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D15" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="17">
-        <v>1681</v>
-      </c>
-      <c r="I15" s="1"/>
+        <v>706</v>
+      </c>
+      <c r="I15" s="17">
+        <v>135702</v>
+      </c>
       <c r="J15" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2267,7 +2338,7 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:23" ht="47.25">
+    <row r="16" spans="1:25" ht="47.25">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -2275,29 +2346,28 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D16" s="1">
         <v>2019</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="4" t="s">
-        <v>173</v>
+        <v>159</v>
+      </c>
+      <c r="G16" s="1">
+        <v>9</v>
+      </c>
+      <c r="I16" s="17">
+        <v>100260</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2308,7 +2378,7 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" ht="47.25">
+    <row r="17" spans="1:19" ht="63">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -2316,29 +2386,29 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D17" s="1">
         <v>2019</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="G17" s="1">
-        <v>111</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="12" t="s">
-        <v>182</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1681</v>
+      </c>
+      <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2349,7 +2419,7 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" ht="47.25">
+    <row r="18" spans="1:19" ht="78.75">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -2357,29 +2427,29 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="D18" s="1">
         <v>2019</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G18" s="1">
-        <v>64</v>
+        <v>169</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="12" t="s">
-        <v>177</v>
+      <c r="I18" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2390,122 +2460,162 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" s="16" customFormat="1">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-    </row>
-    <row r="20" spans="1:19" s="16" customFormat="1">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-    </row>
-    <row r="21" spans="1:19" ht="47.25">
-      <c r="A21" s="1" t="s">
+    <row r="19" spans="1:19" ht="47.25">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="1">
+        <v>18</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G19" s="1">
+        <v>111</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+    </row>
+    <row r="20" spans="1:19" ht="63">
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="1">
+        <v>19</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G20" s="1">
+        <v>64</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+    </row>
+    <row r="21" spans="1:19" s="16" customFormat="1">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+    </row>
+    <row r="22" spans="1:19" s="16" customFormat="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+    </row>
+    <row r="23" spans="1:19" ht="63">
+      <c r="A23" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B23" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-    </row>
-    <row r="22" spans="1:19" s="23" customFormat="1">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
-    </row>
-    <row r="23" spans="1:19" s="25" customFormat="1">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
     </row>
     <row r="24" spans="1:19" s="23" customFormat="1">
       <c r="A24" s="22"/>
@@ -2528,136 +2638,124 @@
       <c r="R24" s="22"/>
       <c r="S24" s="22"/>
     </row>
-    <row r="25" spans="1:19">
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-    </row>
-    <row r="26" spans="1:19" s="19" customFormat="1">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-    </row>
-    <row r="27" spans="1:19" ht="47.25">
-      <c r="A27" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="S27" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="63">
+    <row r="25" spans="1:19" s="25" customFormat="1">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+    </row>
+    <row r="26" spans="1:19" s="27" customFormat="1">
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+    </row>
+    <row r="27" spans="1:19" s="19" customFormat="1">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+    </row>
+    <row r="28" spans="1:19" ht="110.25">
       <c r="A28" s="1" t="s">
         <v>251</v>
       </c>
       <c r="B28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D28" s="1">
         <v>2019</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="3" t="s">
-        <v>262</v>
-      </c>
+      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
+      <c r="R28" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="S28" s="6" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="29" spans="1:19" ht="63">
       <c r="A29" s="1" t="s">
         <v>251</v>
       </c>
       <c r="B29" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D29" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="K29" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
         <v>259</v>
@@ -2666,80 +2764,80 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-      <c r="R29" s="3" t="s">
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+    </row>
+    <row r="30" spans="1:19" ht="63">
+      <c r="A30" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B30" s="1">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="S29" s="1"/>
-    </row>
-    <row r="30" spans="1:19" s="19" customFormat="1">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="18"/>
-    </row>
-    <row r="31" spans="1:19" ht="47.25">
-      <c r="A31" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D31" s="1">
-        <v>2022</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="1"/>
-    </row>
-    <row r="32" spans="1:19" ht="47.25">
+      <c r="S30" s="1"/>
+    </row>
+    <row r="31" spans="1:19" s="19" customFormat="1">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="18"/>
+    </row>
+    <row r="32" spans="1:19" ht="43.5">
       <c r="A32" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="D32" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -2749,30 +2847,30 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-      <c r="R32" s="3"/>
+      <c r="R32" s="6"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:19" ht="29.25">
+    <row r="33" spans="1:19" ht="47.25">
       <c r="A33" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B33" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="D33" s="1">
         <v>2022</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -2782,7 +2880,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -2791,21 +2889,21 @@
       <c r="R33" s="3"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:19" ht="29.25">
+    <row r="34" spans="1:19" ht="47.25">
       <c r="A34" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B34" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="D34" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -2815,7 +2913,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
@@ -2824,12 +2922,22 @@
       <c r="R34" s="3"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:19">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="7"/>
+    <row r="35" spans="1:19" ht="43.5">
+      <c r="A35" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>297</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2837,7 +2945,9 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
+      <c r="M35" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
@@ -2845,138 +2955,152 @@
       <c r="R35" s="3"/>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:19" s="19" customFormat="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="21"/>
-      <c r="S36" s="18"/>
-    </row>
-    <row r="37" spans="1:19" ht="47.25">
-      <c r="A37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="36" spans="1:19" ht="43.5">
+      <c r="A36" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B36" s="1">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="1"/>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="7"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-      <c r="R37" s="1" t="s">
+      <c r="R37" s="3"/>
+      <c r="S37" s="1"/>
+    </row>
+    <row r="38" spans="1:19" s="19" customFormat="1">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="21"/>
+      <c r="S38" s="18"/>
+    </row>
+    <row r="39" spans="1:19" ht="63">
+      <c r="A39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="S37" s="1"/>
-    </row>
-    <row r="38" spans="1:19" ht="47.25">
-      <c r="A38" s="1" t="s">
+      <c r="S39" s="1"/>
+    </row>
+    <row r="40" spans="1:19" ht="94.5">
+      <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B40" s="1">
         <v>2</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D40" s="1">
         <v>2011</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-    </row>
-    <row r="39" spans="1:19" s="19" customFormat="1">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="1"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-    </row>
-    <row r="40" spans="1:19">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+      <c r="I40" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="L40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -2984,60 +3108,32 @@
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:19" ht="63">
-      <c r="A41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="N41" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="O41" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q41" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-    </row>
-    <row r="42" spans="1:19" ht="63">
-      <c r="A42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>340</v>
-      </c>
+    <row r="41" spans="1:19" s="19" customFormat="1">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="1"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -3045,36 +3141,28 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
-      <c r="N42" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="O42" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q42" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19" ht="31.5">
+    <row r="43" spans="1:19" ht="94.5">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -3084,13 +3172,13 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="N43" s="1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="O43" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q43" s="1" t="b">
         <v>0</v>
@@ -3098,21 +3186,21 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:19" ht="31.5">
+    <row r="44" spans="1:19" ht="94.5">
       <c r="A44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -3121,15 +3209,14 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="O44" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="Q44" s="1" t="b">
         <v>0</v>
@@ -3137,21 +3224,21 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:19" ht="63">
+    <row r="45" spans="1:19" ht="47.25">
       <c r="A45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -3160,15 +3247,14 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="O45" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="Q45" s="1" t="b">
         <v>0</v>
@@ -3176,21 +3262,21 @@
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:19" ht="47.25">
+    <row r="46" spans="1:19" ht="63">
       <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -3201,37 +3287,35 @@
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="O46" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="Q46" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="R46" s="1"/>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" spans="1:19" ht="31.5">
+    <row r="47" spans="1:19" ht="110.25">
       <c r="A47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -3242,37 +3326,35 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="O47" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="Q47" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>292</v>
-      </c>
+      <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:19" ht="31.5">
+    <row r="48" spans="1:19" ht="63">
       <c r="A48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B48" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>284</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -3295,147 +3377,171 @@
         <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="1:23" ht="78.75">
+    <row r="49" spans="1:23" ht="63">
       <c r="A49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B49" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>189</v>
+        <v>291</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="O49" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q49" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W49" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" ht="47.25">
+        <v>290</v>
+      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q49" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="S49" s="1"/>
+    </row>
+    <row r="50" spans="1:23" ht="63">
       <c r="A50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B50" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>197</v>
+        <v>325</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="O50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R50" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" ht="31.5">
+        <v>288</v>
+      </c>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q50" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="S50" s="1"/>
+    </row>
+    <row r="51" spans="1:23" ht="94.5">
       <c r="A51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" ht="31.5">
+      <c r="W51" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="63">
       <c r="A52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" ht="31.5">
+      <c r="R52" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" ht="78.75">
       <c r="A53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>196</v>
@@ -3450,21 +3556,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="31.5">
+    <row r="54" spans="1:23" ht="78.75">
       <c r="A54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>196</v>
@@ -3479,21 +3585,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="31.5">
+    <row r="55" spans="1:23" ht="78.75">
       <c r="A55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B55" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>196</v>
@@ -3508,94 +3614,94 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="31.5">
+    <row r="56" spans="1:23" ht="78.75">
       <c r="A56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B56" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="O56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="R56" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23" ht="31.5">
+    </row>
+    <row r="57" spans="1:23" ht="78.75">
       <c r="A57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B57" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="O57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="Q57" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="47.25">
+    <row r="58" spans="1:23" ht="63">
       <c r="A58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B58" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:23" ht="78.75">
@@ -3603,31 +3709,28 @@
         <v>22</v>
       </c>
       <c r="B59" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q59" s="2" t="b">
         <v>0</v>
-      </c>
-      <c r="R59" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:23" ht="78.75">
@@ -3635,48 +3738,45 @@
         <v>22</v>
       </c>
       <c r="B60" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>300</v>
+        <v>218</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="O60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="R60" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23" ht="78.75">
+    </row>
+    <row r="61" spans="1:23" ht="157.5">
       <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B61" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>221</v>
@@ -3691,274 +3791,268 @@
         <v>0</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23" ht="31.5">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="157.5">
       <c r="A62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B62" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="O62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" ht="47.25">
+      <c r="R62" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" ht="157.5">
       <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B63" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="O63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="Q63" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" ht="31.5">
+      <c r="R63" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" ht="63">
       <c r="A64" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="O64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="Q64" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="63">
+    <row r="65" spans="1:19" ht="78.75">
       <c r="A65" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="O65" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="47.25">
+    <row r="66" spans="1:19" ht="47.25">
       <c r="A66" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O66" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="31.5">
+    <row r="67" spans="1:19" ht="110.25">
       <c r="A67" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="1">
+        <v>25</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q67" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="78.75">
+      <c r="A68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="1">
+        <v>26</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="O68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q68" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="78.75">
+      <c r="A69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="1">
         <v>27</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="N67" s="2" t="s">
+      <c r="N69" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="O67" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P67" s="2" t="s">
+      <c r="O69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="Q67" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" s="19" customFormat="1">
-      <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="E68" s="18"/>
-    </row>
-    <row r="69" spans="1:20" ht="47.25">
-      <c r="A69" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D69" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S69" s="1"/>
-    </row>
-    <row r="70" spans="1:20" ht="47.25">
-      <c r="A70" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B70" s="1">
-        <v>2</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="1">
-        <v>2013</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S70" s="1"/>
-    </row>
-    <row r="71" spans="1:20" ht="47.25">
+      <c r="Q69" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" s="19" customFormat="1">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="E70" s="18"/>
+    </row>
+    <row r="71" spans="1:19" ht="94.5">
       <c r="A71" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B71" s="1">
-        <v>3</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D71" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>58</v>
+        <v>2014</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -3967,7 +4061,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
-      <c r="M71" s="9" t="s">
+      <c r="M71" s="1" t="s">
         <v>38</v>
       </c>
       <c r="N71" s="1"/>
@@ -3975,25 +4069,25 @@
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="S71" s="1"/>
     </row>
-    <row r="72" spans="1:20" ht="47.25">
+    <row r="72" spans="1:19" ht="63">
       <c r="A72" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B72" s="1">
-        <v>4</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D72" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>59</v>
+        <v>2013</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -4002,33 +4096,33 @@
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
-      <c r="M72" s="9" t="s">
-        <v>38</v>
+      <c r="M72" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="S72" s="1"/>
     </row>
-    <row r="73" spans="1:20" ht="47.25">
+    <row r="73" spans="1:19" ht="78.75">
       <c r="A73" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B73" s="1">
-        <v>5</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>55</v>
+        <v>3</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D73" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>40</v>
+        <v>2012</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -4045,25 +4139,25 @@
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" spans="1:20" ht="47.25">
+    <row r="74" spans="1:19" ht="78.75">
       <c r="A74" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B74" s="1">
-        <v>6</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>56</v>
+        <v>4</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="D74" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>60</v>
+        <v>2012</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -4080,25 +4174,25 @@
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" spans="1:20" ht="47.25">
+    <row r="75" spans="1:19" ht="94.5">
       <c r="A75" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B75" s="1">
-        <v>7</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="D75" s="1">
         <v>2010</v>
       </c>
-      <c r="E75" s="8" t="s">
-        <v>61</v>
+      <c r="E75" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -4115,25 +4209,25 @@
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S75" s="1"/>
     </row>
-    <row r="76" spans="1:20" ht="47.25">
+    <row r="76" spans="1:19" ht="94.5">
       <c r="A76" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B76" s="1">
-        <v>8</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="D76" s="1">
         <v>2010</v>
       </c>
-      <c r="E76" s="8" t="s">
-        <v>62</v>
+      <c r="E76" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -4150,25 +4244,25 @@
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S76" s="1"/>
     </row>
-    <row r="77" spans="1:20" ht="47.25">
+    <row r="77" spans="1:19" ht="94.5">
       <c r="A77" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B77" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D77" s="1">
         <v>2010</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -4185,25 +4279,25 @@
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
       <c r="R77" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S77" s="1"/>
     </row>
-    <row r="78" spans="1:20" ht="47.25">
+    <row r="78" spans="1:19" ht="94.5">
       <c r="A78" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B78" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D78" s="1">
         <v>2010</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -4220,86 +4314,98 @@
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S78" s="1"/>
+    </row>
+    <row r="79" spans="1:19" ht="94.5">
+      <c r="A79" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B79" s="1">
+        <v>9</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D79" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N79" s="1"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="1"/>
+      <c r="Q79" s="1"/>
+      <c r="R79" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S79" s="1"/>
+    </row>
+    <row r="80" spans="1:19" ht="78.75">
+      <c r="A80" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" s="1">
+        <v>10</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N80" s="1"/>
+      <c r="O80" s="1"/>
+      <c r="P80" s="1"/>
+      <c r="Q80" s="1"/>
+      <c r="R80" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S78" s="1"/>
-    </row>
-    <row r="79" spans="1:20" ht="110.25">
-      <c r="A79" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B79" s="1">
-        <v>1</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N79" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P79" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q79" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T79" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" ht="63">
-      <c r="A80" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B80" s="1">
-        <v>2</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q80" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" ht="63">
+      <c r="S80" s="1"/>
+    </row>
+    <row r="81" spans="1:22" ht="220.5">
       <c r="A81" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B81" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>74</v>
@@ -4308,24 +4414,24 @@
         <v>0</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" ht="78.75">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" ht="63">
       <c r="A82" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B82" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>73</v>
@@ -4337,294 +4443,354 @@
         <v>1</v>
       </c>
       <c r="T82" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" ht="63">
+      <c r="A83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="1">
+        <v>3</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" ht="78.75">
+      <c r="A84" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B84" s="1">
+        <v>4</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q84" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:22" ht="78.75">
-      <c r="A83" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B83" s="1">
-        <v>1</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D83" s="2">
-        <v>2020</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="S83" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U83" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" ht="31.5">
-      <c r="A84" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B84" s="1">
-        <v>2</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D84" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="S84" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U84" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" ht="31.5">
+    <row r="85" spans="1:22" ht="78.75">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B85" s="1">
-        <v>3</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="D85" s="2">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U85" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" ht="78.75">
+        <v>87</v>
+      </c>
+      <c r="U85" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" ht="63">
       <c r="A86" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B86" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D86" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="U86" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V86" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="47.25">
       <c r="A87" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B87" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="U87" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:22" ht="31.5">
+    <row r="88" spans="1:22" ht="78.75">
       <c r="A88" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B88" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="S88" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U88" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" ht="47.25">
+      <c r="A89" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B89" s="1">
+        <v>5</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2016</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="S89" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U89" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" ht="63">
+      <c r="A90" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B90" s="1">
+        <v>6</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="2">
         <v>2015</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E90" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="S88" s="2" t="s">
+      <c r="S90" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="U88" s="10" t="s">
+      <c r="U90" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:22" ht="78.75">
-      <c r="A89" s="1" t="s">
+    <row r="91" spans="1:22" ht="94.5">
+      <c r="A91" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B89" s="1">
-        <v>1</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D89" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R89" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S89" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U89" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="V89" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" ht="78.75">
-      <c r="A90" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B90" s="1">
-        <v>2</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D90" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="R90" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="S90" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U90" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="V90" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" ht="31.5">
-      <c r="A91" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="B91" s="1">
         <v>1</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D91" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>111</v>
+        <v>2018</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22">
+        <v>102</v>
+      </c>
+      <c r="U91" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="V91" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" ht="78.75">
       <c r="A92" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B92" s="1">
         <v>2</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D92" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U92" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" ht="94.5">
+      <c r="A93" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B93" s="1">
+        <v>1</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D93" s="2">
         <v>2019</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E93" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S93" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" ht="47.25">
+      <c r="A94" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B94" s="1">
+        <v>2</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E94" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="R92" s="2" t="s">
+      <c r="R94" s="2" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:K20">
-    <sortCondition ref="B10:B20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B12:K22">
+    <sortCondition ref="B12:B22"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J37" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
-    <hyperlink ref="K8" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
-    <hyperlink ref="K9" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
-    <hyperlink ref="K10" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
-    <hyperlink ref="K11" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
-    <hyperlink ref="K12" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
-    <hyperlink ref="K13" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
-    <hyperlink ref="K14" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
-    <hyperlink ref="K15" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
-    <hyperlink ref="K16" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
-    <hyperlink ref="K18" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
-    <hyperlink ref="K17" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
-    <hyperlink ref="R27" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
-    <hyperlink ref="S27" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
-    <hyperlink ref="K28" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
-    <hyperlink ref="R29" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W49" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R61" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R60" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R59" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R56" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R50" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
-    <hyperlink ref="K7" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
-    <hyperlink ref="J7" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
-    <hyperlink ref="R46" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
-    <hyperlink ref="R48" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
-    <hyperlink ref="R47" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
-    <hyperlink ref="K6" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
-    <hyperlink ref="K5" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
-    <hyperlink ref="K3" r:id="rId30" xr:uid="{2A765B15-3B0B-4BAF-95AD-4FC851D8343D}"/>
-    <hyperlink ref="K4" r:id="rId31" xr:uid="{7D61F22C-7D64-491C-BA97-44A28B404208}"/>
-    <hyperlink ref="K2" r:id="rId32" xr:uid="{824F3703-A805-4B51-BA57-B640C8BF73D3}"/>
+    <hyperlink ref="J39" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
+    <hyperlink ref="K10" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
+    <hyperlink ref="K11" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
+    <hyperlink ref="K12" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
+    <hyperlink ref="K13" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
+    <hyperlink ref="K14" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
+    <hyperlink ref="K15" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
+    <hyperlink ref="K16" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
+    <hyperlink ref="K17" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
+    <hyperlink ref="K18" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
+    <hyperlink ref="K20" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
+    <hyperlink ref="K19" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
+    <hyperlink ref="R28" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
+    <hyperlink ref="S28" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
+    <hyperlink ref="K29" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
+    <hyperlink ref="R30" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
+    <hyperlink ref="W51" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R63" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R62" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R61" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R58" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R52" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="K9" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
+    <hyperlink ref="J9" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
+    <hyperlink ref="R48" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
+    <hyperlink ref="R50" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
+    <hyperlink ref="R49" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="K8" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
+    <hyperlink ref="K7" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
+    <hyperlink ref="K5" r:id="rId30" xr:uid="{2A765B15-3B0B-4BAF-95AD-4FC851D8343D}"/>
+    <hyperlink ref="K6" r:id="rId31" xr:uid="{7D61F22C-7D64-491C-BA97-44A28B404208}"/>
+    <hyperlink ref="K4" r:id="rId32" xr:uid="{824F3703-A805-4B51-BA57-B640C8BF73D3}"/>
+    <hyperlink ref="K2" r:id="rId33" xr:uid="{E5CFF721-38D6-4448-93C3-951FBBF29F8D}"/>
+    <hyperlink ref="K3" r:id="rId34" xr:uid="{E1B605ED-C040-417B-B4C4-B1FC7C626113}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId33"/>
+  <pageSetup orientation="portrait" r:id="rId35"/>
 </worksheet>
 </file>